--- a/research/traditional_assets/database/data/brazil/brazil_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_oil_gas_distribution.xlsx
@@ -650,10 +650,10 @@
         <v>0.1892030039712185</v>
       </c>
       <c r="X2">
-        <v>0.1181164458554401</v>
+        <v>0.1181054877232777</v>
       </c>
       <c r="Y2">
-        <v>0.07108655811577835</v>
+        <v>0.07109751624794075</v>
       </c>
       <c r="Z2">
         <v>6.141363658064463</v>
@@ -662,10 +662,10 @@
         <v>0.1313224612629798</v>
       </c>
       <c r="AB2">
-        <v>0.08686477038472576</v>
+        <v>0.08685931058502742</v>
       </c>
       <c r="AC2">
-        <v>0.04445769087825407</v>
+        <v>0.04446315067795241</v>
       </c>
       <c r="AD2">
         <v>2817.3</v>
@@ -787,10 +787,10 @@
         <v>0.1892030039712185</v>
       </c>
       <c r="X3">
-        <v>0.1181164458554401</v>
+        <v>0.1181054877232777</v>
       </c>
       <c r="Y3">
-        <v>0.07108655811577835</v>
+        <v>0.07109751624794075</v>
       </c>
       <c r="Z3">
         <v>6.141363658064463</v>
@@ -799,10 +799,10 @@
         <v>0.1313224612629798</v>
       </c>
       <c r="AB3">
-        <v>0.08686477038472576</v>
+        <v>0.08685931058502742</v>
       </c>
       <c r="AC3">
-        <v>0.04445769087825407</v>
+        <v>0.04446315067795241</v>
       </c>
       <c r="AD3">
         <v>2817.3</v>
@@ -1139,49 +1139,49 @@
         <v>2.76782673084043</v>
       </c>
       <c r="F2">
-        <v>4.51521797362606</v>
+        <v>4.56466951531929</v>
       </c>
       <c r="G2">
         <v>2.95656606503961</v>
       </c>
       <c r="H2">
-        <v>2.76943376790178</v>
+        <v>2.8283578906231</v>
       </c>
       <c r="I2">
         <v>0.5017581812839</v>
       </c>
       <c r="J2">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="K2">
         <v>2799.3</v>
       </c>
       <c r="L2">
-        <v>3029.70440009882</v>
+        <v>3081.57574463744</v>
       </c>
       <c r="M2">
         <v>4910.35617735462</v>
       </c>
       <c r="N2">
-        <v>4962.33180345549</v>
+        <v>5070.38670976766</v>
       </c>
       <c r="O2">
         <v>2819.05617735462</v>
       </c>
       <c r="P2">
-        <v>2640.62740335667</v>
+        <v>2696.81096513022</v>
       </c>
       <c r="Q2">
-        <v>0.0868647703847258</v>
+        <v>0.0868593105850274</v>
       </c>
       <c r="R2">
-        <v>0.0864258684970487</v>
+        <v>0.0855367575275222</v>
       </c>
       <c r="S2">
         <v>0.0558321092239028</v>
       </c>
       <c r="T2">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.11811644585544</v>
+        <v>0.118105487723278</v>
       </c>
       <c r="X2">
-        <v>0.114668221060027</v>
+        <v>0.115697971346248</v>
       </c>
       <c r="Y2">
         <v>0.9423828948265131</v>
       </c>
       <c r="Z2">
-        <v>0.897447776316821</v>
+        <v>0.911004885713144</v>
       </c>
       <c r="AA2">
         <v>2817.3</v>
@@ -1236,7 +1236,7 @@
         <v>2799.3</v>
       </c>
       <c r="AK2">
-        <v>0.07673785915729414</v>
+        <v>0.07672623104708272</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08924222466295445</v>
+        <v>0.08923564184996283</v>
       </c>
       <c r="C2">
-        <v>5354.719912357346</v>
+        <v>5354.836507670298</v>
       </c>
       <c r="D2">
-        <v>4646.719912357346</v>
+        <v>4646.836507670298</v>
       </c>
       <c r="E2">
         <v>-2819.05617735462</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08924222466295445</v>
+        <v>0.08923564184996283</v>
       </c>
       <c r="T2">
         <v>0.5661120226706918</v>
       </c>
       <c r="U2">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V2">
         <v>0.34</v>
       </c>
       <c r="W2">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08914138219133944</v>
+        <v>0.08912558175991198</v>
       </c>
       <c r="C3">
-        <v>5309.142557916147</v>
+        <v>5310.231681104189</v>
       </c>
       <c r="D3">
-        <v>4657.326119689693</v>
+        <v>4658.415242877735</v>
       </c>
       <c r="E3">
         <v>-2762.872615581074</v>
@@ -1539,37 +1539,37 @@
         <v>985.9625</v>
       </c>
       <c r="M3">
-        <v>4.297711267101734</v>
+        <v>4.219054280618769</v>
       </c>
       <c r="N3">
-        <v>981.6647887328983</v>
+        <v>981.7434457193812</v>
       </c>
       <c r="O3">
-        <v>333.7660281691855</v>
+        <v>333.7927715445896</v>
       </c>
       <c r="P3">
-        <v>647.8987605637128</v>
+        <v>647.9506741747915</v>
       </c>
       <c r="Q3">
-        <v>853.7987605637128</v>
+        <v>853.8506741747915</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08953183949404081</v>
+        <v>0.08952521279562925</v>
       </c>
       <c r="T3">
         <v>0.5698861028218297</v>
       </c>
       <c r="U3">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V3">
         <v>0.34</v>
       </c>
       <c r="W3">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>229.4157142540913</v>
+        <v>233.6927743568632</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08904053971972442</v>
+        <v>0.08901552166986114</v>
       </c>
       <c r="C4">
-        <v>5263.61373189385</v>
+        <v>5265.684701206198</v>
       </c>
       <c r="D4">
-        <v>4667.980855440942</v>
+        <v>4670.05182475329</v>
       </c>
       <c r="E4">
         <v>-2706.689053807528</v>
@@ -1621,37 +1621,37 @@
         <v>985.9625</v>
       </c>
       <c r="M4">
-        <v>8.595422534203468</v>
+        <v>8.438108561237538</v>
       </c>
       <c r="N4">
-        <v>977.3670774657965</v>
+        <v>977.5243914387624</v>
       </c>
       <c r="O4">
-        <v>332.3048063383708</v>
+        <v>332.3582930891793</v>
       </c>
       <c r="P4">
-        <v>645.0622711274257</v>
+        <v>645.1660983495832</v>
       </c>
       <c r="Q4">
-        <v>850.9622711274257</v>
+        <v>851.0660983495832</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08982736483188404</v>
+        <v>0.08982069335243172</v>
       </c>
       <c r="T4">
         <v>0.5737372050168684</v>
       </c>
       <c r="U4">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V4">
         <v>0.34</v>
       </c>
       <c r="W4">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>114.7078571270456</v>
+        <v>116.8463871784316</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08893969724810941</v>
+        <v>0.0889054615798103</v>
       </c>
       <c r="C5">
-        <v>5218.133768114886</v>
+        <v>5221.196002559636</v>
       </c>
       <c r="D5">
-        <v>4678.684453435525</v>
+        <v>4681.746687880275</v>
       </c>
       <c r="E5">
         <v>-2650.505492033982</v>
@@ -1703,37 +1703,37 @@
         <v>985.9625</v>
       </c>
       <c r="M5">
-        <v>12.8931338013052</v>
+        <v>12.65716284185631</v>
       </c>
       <c r="N5">
-        <v>973.0693661986948</v>
+        <v>973.3053371581436</v>
       </c>
       <c r="O5">
-        <v>330.8435845075562</v>
+        <v>330.9238146337689</v>
       </c>
       <c r="P5">
-        <v>642.2257816911385</v>
+        <v>642.3815225243748</v>
       </c>
       <c r="Q5">
-        <v>848.1257816911385</v>
+        <v>848.2815225243747</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.0901289834756622</v>
+        <v>0.09012226629184868</v>
       </c>
       <c r="T5">
         <v>0.5776677113808771</v>
       </c>
       <c r="U5">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V5">
         <v>0.34</v>
       </c>
       <c r="W5">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>76.47190475136377</v>
+        <v>77.89759145228774</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08883885477649438</v>
+        <v>0.08879540148975944</v>
       </c>
       <c r="C6">
-        <v>5172.703003472543</v>
+        <v>5176.766024111934</v>
       </c>
       <c r="D6">
-        <v>4689.437250566728</v>
+        <v>4693.500271206119</v>
       </c>
       <c r="E6">
         <v>-2594.321930260435</v>
@@ -1785,37 +1785,37 @@
         <v>985.9625</v>
       </c>
       <c r="M6">
-        <v>17.19084506840694</v>
+        <v>16.87621712247508</v>
       </c>
       <c r="N6">
-        <v>968.771654931593</v>
+        <v>969.0862828775249</v>
       </c>
       <c r="O6">
-        <v>329.3823626767416</v>
+        <v>329.4893361783585</v>
       </c>
       <c r="P6">
-        <v>639.3892922548514</v>
+        <v>639.5969466991664</v>
       </c>
       <c r="Q6">
-        <v>845.2892922548514</v>
+        <v>845.4969466991664</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.0904368858411857</v>
+        <v>0.0904301220008368</v>
       </c>
       <c r="T6">
         <v>0.5816801032941359</v>
       </c>
       <c r="U6">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V6">
         <v>0.34</v>
       </c>
       <c r="W6">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>57.35392856352282</v>
+        <v>58.42319358921581</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08873801230487938</v>
+        <v>0.0886853413997086</v>
       </c>
       <c r="C7">
-        <v>5127.321777964296</v>
+        <v>5132.395209229529</v>
       </c>
       <c r="D7">
-        <v>4700.239586832027</v>
+        <v>4705.313018097259</v>
       </c>
       <c r="E7">
         <v>-2538.138368486889</v>
@@ -1867,37 +1867,37 @@
         <v>985.9625</v>
       </c>
       <c r="M7">
-        <v>21.48855633550867</v>
+        <v>21.09527140309385</v>
       </c>
       <c r="N7">
-        <v>964.4739436644913</v>
+        <v>964.8672285969061</v>
       </c>
       <c r="O7">
-        <v>327.9211408459271</v>
+        <v>328.0548577229481</v>
       </c>
       <c r="P7">
-        <v>636.5528028185643</v>
+        <v>636.812370873958</v>
       </c>
       <c r="Q7">
-        <v>842.4528028185642</v>
+        <v>842.712370873958</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09075127036177288</v>
+        <v>0.09074445888264575</v>
       </c>
       <c r="T7">
         <v>0.5857769666160948</v>
       </c>
       <c r="U7">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V7">
         <v>0.34</v>
       </c>
       <c r="W7">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.88314285081826</v>
+        <v>46.73855487137264</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08863716983326436</v>
+        <v>0.08857528130965776</v>
       </c>
       <c r="C8">
-        <v>5081.990434727666</v>
+        <v>5088.084005753646</v>
       </c>
       <c r="D8">
-        <v>4711.091805368943</v>
+        <v>4717.185376394923</v>
       </c>
       <c r="E8">
         <v>-2481.954806713343</v>
@@ -1949,37 +1949,37 @@
         <v>985.9625</v>
       </c>
       <c r="M8">
-        <v>25.7862676026104</v>
+        <v>25.31432568371261</v>
       </c>
       <c r="N8">
-        <v>960.1762323973895</v>
+        <v>960.6481743162874</v>
       </c>
       <c r="O8">
-        <v>326.4599190151125</v>
+        <v>326.6203792675377</v>
       </c>
       <c r="P8">
-        <v>633.7163133822771</v>
+        <v>634.0277950487497</v>
       </c>
       <c r="Q8">
-        <v>839.6163133822771</v>
+        <v>839.9277950487497</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09107234391471297</v>
+        <v>0.09106548378321659</v>
       </c>
       <c r="T8">
         <v>0.5899609972427764</v>
       </c>
       <c r="U8">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V8">
         <v>0.34</v>
       </c>
       <c r="W8">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.23595237568188</v>
+        <v>38.94879572614388</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08853632736164933</v>
+        <v>0.08846522121960691</v>
       </c>
       <c r="C9">
-        <v>5036.70932007653</v>
+        <v>5043.832866056883</v>
       </c>
       <c r="D9">
-        <v>4721.994252491354</v>
+        <v>4729.117798471707</v>
       </c>
       <c r="E9">
         <v>-2425.771244939797</v>
@@ -2031,37 +2031,37 @@
         <v>985.9625</v>
       </c>
       <c r="M9">
-        <v>30.08397886971214</v>
+        <v>29.53337996433139</v>
       </c>
       <c r="N9">
-        <v>955.8785211302878</v>
+        <v>956.4291200356686</v>
       </c>
       <c r="O9">
-        <v>324.9986971842979</v>
+        <v>325.1859008121273</v>
       </c>
       <c r="P9">
-        <v>630.87982394599</v>
+        <v>631.2432192235412</v>
       </c>
       <c r="Q9">
-        <v>836.77982394599</v>
+        <v>837.1432192235412</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09140032227524317</v>
+        <v>0.09139341244509003</v>
       </c>
       <c r="T9">
         <v>0.5942350070227198</v>
       </c>
       <c r="U9">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V9">
         <v>0.34</v>
       </c>
       <c r="W9">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.77367346487018</v>
+        <v>33.38468205098046</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.0884354848900343</v>
+        <v>0.08835516112955608</v>
       </c>
       <c r="C10">
-        <v>4991.478783537977</v>
+        <v>4999.642247100663</v>
       </c>
       <c r="D10">
-        <v>4732.947277726346</v>
+        <v>4741.110741289032</v>
       </c>
       <c r="E10">
         <v>-2369.58768316625</v>
@@ -2113,37 +2113,37 @@
         <v>985.9625</v>
       </c>
       <c r="M10">
-        <v>34.38169013681387</v>
+        <v>33.75243424495015</v>
       </c>
       <c r="N10">
-        <v>951.5808098631861</v>
+        <v>952.2100657550499</v>
       </c>
       <c r="O10">
-        <v>323.5374753534833</v>
+        <v>323.751422356717</v>
       </c>
       <c r="P10">
-        <v>628.0433345097028</v>
+        <v>628.4586433983329</v>
       </c>
       <c r="Q10">
-        <v>833.9433345097028</v>
+        <v>834.3586433983329</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.0917354306001327</v>
+        <v>0.09172846999091722</v>
       </c>
       <c r="T10">
         <v>0.5986019300587488</v>
       </c>
       <c r="U10">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V10">
         <v>0.34</v>
       </c>
       <c r="W10">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.67696428176141</v>
+        <v>29.21159679460791</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.0883346424184193</v>
+        <v>0.08824510103950521</v>
       </c>
       <c r="C11">
-        <v>4946.299177889647</v>
+        <v>4955.512610493576</v>
       </c>
       <c r="D11">
-        <v>4743.951233851562</v>
+        <v>4753.164666455492</v>
       </c>
       <c r="E11">
         <v>-2313.404121392704</v>
@@ -2195,37 +2195,37 @@
         <v>985.9625</v>
       </c>
       <c r="M11">
-        <v>38.67940140391561</v>
+        <v>37.97148852556892</v>
       </c>
       <c r="N11">
-        <v>947.2830985960844</v>
+        <v>947.991011474431</v>
       </c>
       <c r="O11">
-        <v>322.0762535226687</v>
+        <v>322.3169439013066</v>
       </c>
       <c r="P11">
-        <v>625.2068450734157</v>
+        <v>625.6740675731245</v>
       </c>
       <c r="Q11">
-        <v>831.1068450734157</v>
+        <v>831.5740675731245</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.0920779039431517</v>
+        <v>0.0920708914388505</v>
       </c>
       <c r="T11">
         <v>0.6030648294252402</v>
       </c>
       <c r="U11">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V11">
         <v>0.34</v>
       </c>
       <c r="W11">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.49063491712126</v>
+        <v>25.96586381742925</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08823379994680429</v>
+        <v>0.08813504094945437</v>
       </c>
       <c r="C12">
-        <v>4901.170859197623</v>
+        <v>4911.444422550593</v>
       </c>
       <c r="D12">
-        <v>4755.006476933085</v>
+        <v>4765.280040286055</v>
       </c>
       <c r="E12">
         <v>-2257.220559619158</v>
@@ -2277,37 +2277,37 @@
         <v>985.9625</v>
       </c>
       <c r="M12">
-        <v>42.97711267101734</v>
+        <v>42.19054280618769</v>
       </c>
       <c r="N12">
-        <v>942.9853873289826</v>
+        <v>943.7719571938123</v>
       </c>
       <c r="O12">
-        <v>320.6150316918541</v>
+        <v>320.8824654458962</v>
       </c>
       <c r="P12">
-        <v>622.3703556371286</v>
+        <v>622.8894917479161</v>
       </c>
       <c r="Q12">
-        <v>828.2703556371285</v>
+        <v>828.789491747916</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09242798780490445</v>
+        <v>0.09242092225229344</v>
       </c>
       <c r="T12">
         <v>0.6076269043332092</v>
       </c>
       <c r="U12">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V12">
         <v>0.34</v>
       </c>
       <c r="W12">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.94157142540913</v>
+        <v>23.36927743568632</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08813295747518926</v>
+        <v>0.08802498085940352</v>
       </c>
       <c r="C13">
-        <v>4856.094186854824</v>
+        <v>4867.438154353217</v>
       </c>
       <c r="D13">
-        <v>4766.113366363833</v>
+        <v>4777.457333862226</v>
       </c>
       <c r="E13">
         <v>-2201.036997845612</v>
@@ -2359,37 +2359,37 @@
         <v>985.9625</v>
       </c>
       <c r="M13">
-        <v>47.27482393811907</v>
+        <v>46.40959708680646</v>
       </c>
       <c r="N13">
-        <v>938.6876760618809</v>
+        <v>939.5529029131935</v>
       </c>
       <c r="O13">
-        <v>319.1538098610395</v>
+        <v>319.4479869904858</v>
       </c>
       <c r="P13">
-        <v>619.5338662008414</v>
+        <v>620.1049159227077</v>
       </c>
       <c r="Q13">
-        <v>825.4338662008414</v>
+        <v>826.0049159227077</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09278593871973029</v>
+        <v>0.09277881892671261</v>
       </c>
       <c r="T13">
         <v>0.6122914977784358</v>
       </c>
       <c r="U13">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V13">
         <v>0.34</v>
       </c>
       <c r="W13">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.85597402309921</v>
+        <v>21.24479766880575</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08803211500357426</v>
+        <v>0.0879149207693527</v>
       </c>
       <c r="C14">
-        <v>4811.069523619954</v>
+        <v>4823.494281810527</v>
       </c>
       <c r="D14">
-        <v>4777.272264902509</v>
+        <v>4789.697023093082</v>
       </c>
       <c r="E14">
         <v>-2144.853436072066</v>
@@ -2441,37 +2441,37 @@
         <v>985.9625</v>
       </c>
       <c r="M14">
-        <v>51.5725352052208</v>
+        <v>50.62865136742523</v>
       </c>
       <c r="N14">
-        <v>934.3899647947792</v>
+        <v>935.3338486325747</v>
       </c>
       <c r="O14">
-        <v>317.692588030225</v>
+        <v>318.0135085350754</v>
       </c>
       <c r="P14">
-        <v>616.6973767645543</v>
+        <v>617.3203400974993</v>
       </c>
       <c r="Q14">
-        <v>822.5973767645543</v>
+        <v>823.2203400974993</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09315202488262037</v>
+        <v>0.0931448496164595</v>
       </c>
       <c r="T14">
         <v>0.6170621047110542</v>
       </c>
       <c r="U14">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V14">
         <v>0.34</v>
       </c>
       <c r="W14">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.11797618784094</v>
+        <v>19.47439786307194</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08793127253195925</v>
+        <v>0.08780486067930184</v>
       </c>
       <c r="C15">
-        <v>4766.097235656999</v>
+        <v>4779.613285721192</v>
       </c>
       <c r="D15">
-        <v>4788.4835387131</v>
+        <v>4801.999588777293</v>
       </c>
       <c r="E15">
         <v>-2088.66987429852</v>
@@ -2523,37 +2523,37 @@
         <v>985.9625</v>
       </c>
       <c r="M15">
-        <v>55.87024647232254</v>
+        <v>54.847705648044</v>
       </c>
       <c r="N15">
-        <v>930.0922535276775</v>
+        <v>931.114794351956</v>
       </c>
       <c r="O15">
-        <v>316.2313661994104</v>
+        <v>316.5790300796651</v>
       </c>
       <c r="P15">
-        <v>613.8608873282672</v>
+        <v>614.5357642722909</v>
       </c>
       <c r="Q15">
-        <v>819.7608873282671</v>
+        <v>820.4357642722908</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09352652681936997</v>
+        <v>0.09351929480482124</v>
       </c>
       <c r="T15">
         <v>0.6219423807685601</v>
       </c>
       <c r="U15">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V15">
         <v>0.34</v>
       </c>
       <c r="W15">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.6473626349301</v>
+        <v>17.97636725822025</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08783043006034423</v>
+        <v>0.08769480058925098</v>
       </c>
       <c r="C16">
-        <v>4721.177692575275</v>
+        <v>4735.795651836406</v>
       </c>
       <c r="D16">
-        <v>4799.747557404921</v>
+        <v>4814.365516666053</v>
       </c>
       <c r="E16">
         <v>-2032.486312524973</v>
@@ -2605,37 +2605,37 @@
         <v>985.9625</v>
       </c>
       <c r="M16">
-        <v>60.16795773942428</v>
+        <v>59.06675992866278</v>
       </c>
       <c r="N16">
-        <v>925.7945422605757</v>
+        <v>926.8957400713372</v>
       </c>
       <c r="O16">
-        <v>314.7701443685958</v>
+        <v>315.1445516242547</v>
       </c>
       <c r="P16">
-        <v>611.0243978919799</v>
+        <v>611.7511884470825</v>
       </c>
       <c r="Q16">
-        <v>816.9243978919799</v>
+        <v>817.6511884470825</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09390973810348585</v>
+        <v>0.0939024480208193</v>
       </c>
       <c r="T16">
         <v>0.626936151618101</v>
       </c>
       <c r="U16">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V16">
         <v>0.34</v>
       </c>
       <c r="W16">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.38683673243509</v>
+        <v>16.69234102549023</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.0877295875887292</v>
+        <v>0.08758474049920016</v>
       </c>
       <c r="C17">
-        <v>4676.311267470047</v>
+        <v>4692.041870923838</v>
       </c>
       <c r="D17">
-        <v>4811.06469407324</v>
+        <v>4826.795297527032</v>
       </c>
       <c r="E17">
         <v>-1976.302750751427</v>
@@ -2687,37 +2687,37 @@
         <v>985.9625</v>
       </c>
       <c r="M17">
-        <v>64.46566900652601</v>
+        <v>63.28581420928154</v>
       </c>
       <c r="N17">
-        <v>921.496830993474</v>
+        <v>922.6766857907185</v>
       </c>
       <c r="O17">
-        <v>313.3089225377811</v>
+        <v>313.7100731688443</v>
       </c>
       <c r="P17">
-        <v>608.1879084556929</v>
+        <v>608.9666126218742</v>
       </c>
       <c r="Q17">
-        <v>814.0879084556929</v>
+        <v>814.8666126218742</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09430196612369857</v>
+        <v>0.09429461660660557</v>
       </c>
       <c r="T17">
         <v>0.6320474229582195</v>
       </c>
       <c r="U17">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V17">
         <v>0.34</v>
       </c>
       <c r="W17">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.29438095027275</v>
+        <v>15.57951829045755</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08762874511711417</v>
+        <v>0.0874746804091493</v>
       </c>
       <c r="C18">
-        <v>4631.498336963724</v>
+        <v>4648.352438832564</v>
       </c>
       <c r="D18">
-        <v>4822.435325340463</v>
+        <v>4839.289427209304</v>
       </c>
       <c r="E18">
         <v>-1920.119188977881</v>
@@ -2769,37 +2769,37 @@
         <v>985.9625</v>
       </c>
       <c r="M18">
-        <v>68.76338027362775</v>
+        <v>67.5048684899003</v>
       </c>
       <c r="N18">
-        <v>917.1991197263723</v>
+        <v>918.4576315100996</v>
       </c>
       <c r="O18">
-        <v>311.8477007069666</v>
+        <v>312.2755947134339</v>
       </c>
       <c r="P18">
-        <v>605.3514190194057</v>
+        <v>606.1820367966657</v>
       </c>
       <c r="Q18">
-        <v>811.2514190194057</v>
+        <v>812.0820367966656</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09470353290629729</v>
+        <v>0.09469612253967244</v>
       </c>
       <c r="T18">
         <v>0.6372803912350073</v>
       </c>
       <c r="U18">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V18">
         <v>0.34</v>
       </c>
       <c r="W18">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.33848214088071</v>
+        <v>14.60579839730395</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08752790264549914</v>
+        <v>0.08736462031909845</v>
       </c>
       <c r="C19">
-        <v>4586.739281247637</v>
+        <v>4604.727856558978</v>
       </c>
       <c r="D19">
-        <v>4833.859831397923</v>
+        <v>4851.848406709263</v>
       </c>
       <c r="E19">
         <v>-1863.935627204335</v>
@@ -2851,37 +2851,37 @@
         <v>985.9625</v>
       </c>
       <c r="M19">
-        <v>73.06109154072948</v>
+        <v>71.72392277051908</v>
       </c>
       <c r="N19">
-        <v>912.9014084592704</v>
+        <v>914.2385772294809</v>
       </c>
       <c r="O19">
-        <v>310.386478876152</v>
+        <v>310.8411162580235</v>
       </c>
       <c r="P19">
-        <v>602.5149295831185</v>
+        <v>603.3974609714573</v>
       </c>
       <c r="Q19">
-        <v>808.4149295831185</v>
+        <v>809.2974609714573</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09511477599691046</v>
+        <v>0.09510730331449997</v>
       </c>
       <c r="T19">
         <v>0.6426394551329226</v>
       </c>
       <c r="U19">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V19">
         <v>0.34</v>
       </c>
       <c r="W19">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.49504201494655</v>
+        <v>13.74663378569784</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08742706017388416</v>
+        <v>0.08725456022904762</v>
       </c>
       <c r="C20">
-        <v>4542.034484124411</v>
+        <v>4561.168630313776</v>
       </c>
       <c r="D20">
-        <v>4845.338596048243</v>
+        <v>4864.472742237607</v>
       </c>
       <c r="E20">
         <v>-1807.752065430788</v>
@@ -2933,37 +2933,37 @@
         <v>985.9625</v>
       </c>
       <c r="M20">
-        <v>77.35880280783121</v>
+        <v>75.94297705113785</v>
       </c>
       <c r="N20">
-        <v>908.6036971921687</v>
+        <v>910.0195229488621</v>
       </c>
       <c r="O20">
-        <v>308.9252570453374</v>
+        <v>309.4066378026131</v>
       </c>
       <c r="P20">
-        <v>599.6784401468313</v>
+        <v>600.612885146249</v>
       </c>
       <c r="Q20">
-        <v>805.5784401468313</v>
+        <v>806.512885146249</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09553604940680688</v>
+        <v>0.09552851288871354</v>
       </c>
       <c r="T20">
         <v>0.6481292279063969</v>
       </c>
       <c r="U20">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V20">
         <v>0.34</v>
       </c>
       <c r="W20">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.74531745856063</v>
+        <v>12.98293190871462</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08746415770226915</v>
+        <v>0.08733260013899675</v>
       </c>
       <c r="C21">
-        <v>4481.621826786441</v>
+        <v>4496.026812821168</v>
       </c>
       <c r="D21">
-        <v>4841.109500483818</v>
+        <v>4855.514486518547</v>
       </c>
       <c r="E21">
         <v>-1751.568503657242</v>
@@ -3015,37 +3015,37 @@
         <v>985.9625</v>
       </c>
       <c r="M21">
-        <v>82.83075051600005</v>
+        <v>81.76326284230268</v>
       </c>
       <c r="N21">
-        <v>903.1317494839999</v>
+        <v>904.1992371576973</v>
       </c>
       <c r="O21">
-        <v>307.06479482456</v>
+        <v>307.4277406336171</v>
       </c>
       <c r="P21">
-        <v>596.0669546594399</v>
+        <v>596.7714965240802</v>
       </c>
       <c r="Q21">
-        <v>801.9669546594399</v>
+        <v>802.6714965240802</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09596772462929333</v>
+        <v>0.09596012269932744</v>
       </c>
       <c r="T21">
         <v>0.6537545506248952</v>
       </c>
       <c r="U21">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V21">
         <v>0.34</v>
       </c>
       <c r="W21">
-        <v>0.0512121092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.90333896358389</v>
+        <v>12.05874699376457</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08737057523065413</v>
+        <v>0.08723244004894593</v>
       </c>
       <c r="C22">
-        <v>4436.120818647377</v>
+        <v>4451.346713410662</v>
       </c>
       <c r="D22">
-        <v>4851.792054118301</v>
+        <v>4867.017948881587</v>
       </c>
       <c r="E22">
         <v>-1695.384941883696</v>
@@ -3097,37 +3097,37 @@
         <v>985.9625</v>
       </c>
       <c r="M22">
-        <v>87.1902637010527</v>
+        <v>86.06659246558176</v>
       </c>
       <c r="N22">
-        <v>898.7722362989473</v>
+        <v>899.8959075344183</v>
       </c>
       <c r="O22">
-        <v>305.5825603416421</v>
+        <v>305.9646085617022</v>
       </c>
       <c r="P22">
-        <v>593.1896759573052</v>
+        <v>593.931298972716</v>
       </c>
       <c r="Q22">
-        <v>799.0896759573052</v>
+        <v>799.831298972716</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09641019173234194</v>
+        <v>0.09640252275520669</v>
       </c>
       <c r="T22">
         <v>0.659520506411356</v>
       </c>
       <c r="U22">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V22">
         <v>0.34</v>
       </c>
       <c r="W22">
-        <v>0.0512121092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.3081720154047</v>
+        <v>11.45580964407634</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08727699275903909</v>
+        <v>0.08713227995889508</v>
       </c>
       <c r="C23">
-        <v>4390.667059728067</v>
+        <v>4406.721250393709</v>
       </c>
       <c r="D23">
-        <v>4862.521856972538</v>
+        <v>4878.576047638179</v>
       </c>
       <c r="E23">
         <v>-1639.20138011015</v>
@@ -3179,37 +3179,37 @@
         <v>985.9625</v>
       </c>
       <c r="M23">
-        <v>91.54977688610533</v>
+        <v>90.36992208886086</v>
       </c>
       <c r="N23">
-        <v>894.4127231138947</v>
+        <v>895.5925779111391</v>
       </c>
       <c r="O23">
-        <v>304.1003258587242</v>
+        <v>304.5014764897873</v>
       </c>
       <c r="P23">
-        <v>590.3123972551705</v>
+        <v>591.0911014213518</v>
       </c>
       <c r="Q23">
-        <v>796.2123972551705</v>
+        <v>796.9911014213518</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.0968638605342019</v>
+        <v>0.09685612281250061</v>
       </c>
       <c r="T23">
         <v>0.6654324357620308</v>
       </c>
       <c r="U23">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V23">
         <v>0.34</v>
       </c>
       <c r="W23">
-        <v>0.0512121092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.76968763371876</v>
+        <v>10.91029489912033</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08718341028742409</v>
+        <v>0.08703211986884422</v>
       </c>
       <c r="C24">
-        <v>4345.260864200141</v>
+        <v>4362.150813945193</v>
       </c>
       <c r="D24">
-        <v>4873.299223218157</v>
+        <v>4890.18917296321</v>
       </c>
       <c r="E24">
         <v>-1583.017818336604</v>
@@ -3261,37 +3261,37 @@
         <v>985.9625</v>
       </c>
       <c r="M24">
-        <v>95.90929007115797</v>
+        <v>94.67325171213994</v>
       </c>
       <c r="N24">
-        <v>890.053209928842</v>
+        <v>891.28924828786</v>
       </c>
       <c r="O24">
-        <v>302.6180913758063</v>
+        <v>303.0383444178725</v>
       </c>
       <c r="P24">
-        <v>587.4351185530356</v>
+        <v>588.2509038699875</v>
       </c>
       <c r="Q24">
-        <v>793.3351185530356</v>
+        <v>794.1509038699875</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.0973291618694429</v>
+        <v>0.09732135364049437</v>
       </c>
       <c r="T24">
         <v>0.6714959530447744</v>
       </c>
       <c r="U24">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V24">
         <v>0.34</v>
       </c>
       <c r="W24">
-        <v>0.0512121092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.28015637764063</v>
+        <v>10.41437240370577</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08708982781580905</v>
+        <v>0.08693195977879337</v>
       </c>
       <c r="C25">
-        <v>4299.902549026763</v>
+        <v>4317.635797964007</v>
       </c>
       <c r="D25">
-        <v>4884.124469818326</v>
+        <v>4901.85771875557</v>
       </c>
       <c r="E25">
         <v>-1526.834256563057</v>
@@ -3343,37 +3343,37 @@
         <v>985.9625</v>
       </c>
       <c r="M25">
-        <v>100.2688032562106</v>
+        <v>98.97658133541904</v>
       </c>
       <c r="N25">
-        <v>885.6936967437894</v>
+        <v>886.9859186645809</v>
       </c>
       <c r="O25">
-        <v>301.1358568928884</v>
+        <v>301.5752123459575</v>
       </c>
       <c r="P25">
-        <v>584.557839850901</v>
+        <v>585.4107063186234</v>
       </c>
       <c r="Q25">
-        <v>790.457839850901</v>
+        <v>791.3107063186234</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09780654895365118</v>
+        <v>0.09779866838609835</v>
       </c>
       <c r="T25">
         <v>0.6777169642829138</v>
       </c>
       <c r="U25">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V25">
         <v>0.34</v>
       </c>
       <c r="W25">
-        <v>0.0512121092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.833193056873649</v>
+        <v>9.961573603544645</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08734472534419403</v>
+        <v>0.08710107968874252</v>
       </c>
       <c r="C26">
-        <v>4214.345682709341</v>
+        <v>4241.782181088251</v>
       </c>
       <c r="D26">
-        <v>4854.751165274451</v>
+        <v>4882.18766365336</v>
       </c>
       <c r="E26">
         <v>-1470.650694789511</v>
@@ -3425,37 +3425,37 @@
         <v>985.9625</v>
       </c>
       <c r="M26">
-        <v>107.5948085029065</v>
+        <v>105.5722002790588</v>
       </c>
       <c r="N26">
-        <v>878.3676914970936</v>
+        <v>880.3902997209411</v>
       </c>
       <c r="O26">
-        <v>298.6450151090118</v>
+        <v>299.33270190512</v>
       </c>
       <c r="P26">
-        <v>579.7226763880817</v>
+        <v>581.0575978158211</v>
       </c>
       <c r="Q26">
-        <v>785.6226763880817</v>
+        <v>786.957597815821</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09829649885586496</v>
+        <v>0.09828854404606034</v>
       </c>
       <c r="T26">
         <v>0.6841016863431096</v>
       </c>
       <c r="U26">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V26">
         <v>0.34</v>
       </c>
       <c r="W26">
-        <v>0.0526641092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.163662389652993</v>
+        <v>9.339224695457773</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08726566287257903</v>
+        <v>0.0870121395986917</v>
       </c>
       <c r="C27">
-        <v>4167.235074945894</v>
+        <v>4195.923371530858</v>
       </c>
       <c r="D27">
-        <v>4863.824119284549</v>
+        <v>4892.512415869513</v>
       </c>
       <c r="E27">
         <v>-1414.467133015965</v>
@@ -3507,37 +3507,37 @@
         <v>985.9625</v>
       </c>
       <c r="M27">
-        <v>112.0779255238609</v>
+        <v>109.9710419573529</v>
       </c>
       <c r="N27">
-        <v>873.8845744761391</v>
+        <v>875.9914580426471</v>
       </c>
       <c r="O27">
-        <v>297.1207553218873</v>
+        <v>297.8370957345001</v>
       </c>
       <c r="P27">
-        <v>576.7638191542517</v>
+        <v>578.154362308147</v>
       </c>
       <c r="Q27">
-        <v>782.6638191542517</v>
+        <v>784.054362308147</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09879951408880444</v>
+        <v>0.09879148305695465</v>
       </c>
       <c r="T27">
         <v>0.690656667658244</v>
       </c>
       <c r="U27">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V27">
         <v>0.34</v>
       </c>
       <c r="W27">
-        <v>0.0526641092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.797115894066874</v>
+        <v>8.965655707639463</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08718660040096401</v>
+        <v>0.08692319950864083</v>
       </c>
       <c r="C28">
-        <v>4120.158443229093</v>
+        <v>4150.108323676236</v>
       </c>
       <c r="D28">
-        <v>4872.931049341294</v>
+        <v>4902.880929788437</v>
       </c>
       <c r="E28">
         <v>-1358.283571242419</v>
@@ -3589,37 +3589,37 @@
         <v>985.9625</v>
       </c>
       <c r="M28">
-        <v>116.5610425448153</v>
+        <v>114.369883635647</v>
       </c>
       <c r="N28">
-        <v>869.4014574551846</v>
+        <v>871.5926163643529</v>
       </c>
       <c r="O28">
-        <v>295.5964955347628</v>
+        <v>296.34148956388</v>
       </c>
       <c r="P28">
-        <v>573.8049619204219</v>
+        <v>575.2511268004729</v>
       </c>
       <c r="Q28">
-        <v>779.7049619204219</v>
+        <v>781.1511268004729</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09931612432803957</v>
+        <v>0.09930801501408934</v>
       </c>
       <c r="T28">
         <v>0.6973888106305441</v>
       </c>
       <c r="U28">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V28">
         <v>0.34</v>
       </c>
       <c r="W28">
-        <v>0.0526641092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.458765282756609</v>
+        <v>8.620822795807175</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08710753792934899</v>
+        <v>0.08683425941858999</v>
       </c>
       <c r="C29">
-        <v>4073.115978765226</v>
+        <v>4104.337316342762</v>
       </c>
       <c r="D29">
-        <v>4882.072146650974</v>
+        <v>4913.293484228509</v>
       </c>
       <c r="E29">
         <v>-1302.100009468872</v>
@@ -3671,37 +3671,37 @@
         <v>985.9625</v>
       </c>
       <c r="M29">
-        <v>121.0441595657698</v>
+        <v>118.7687253139412</v>
       </c>
       <c r="N29">
-        <v>864.9183404342302</v>
+        <v>867.1937746860588</v>
       </c>
       <c r="O29">
-        <v>294.0722357476383</v>
+        <v>294.84588339326</v>
       </c>
       <c r="P29">
-        <v>570.846104686592</v>
+        <v>572.3478912927987</v>
       </c>
       <c r="Q29">
-        <v>776.7461046865919</v>
+        <v>778.2478912927987</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09984688827245922</v>
+        <v>0.09983869853169347</v>
       </c>
       <c r="T29">
         <v>0.7043053958760579</v>
       </c>
       <c r="U29">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V29">
         <v>0.34</v>
       </c>
       <c r="W29">
-        <v>0.0526641092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.145477679691549</v>
+        <v>8.301533062629129</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08702847545773398</v>
+        <v>0.08674531932853916</v>
       </c>
       <c r="C30">
-        <v>4026.107874198</v>
+        <v>4058.610630722438</v>
       </c>
       <c r="D30">
-        <v>4891.247603857294</v>
+        <v>4923.750360381732</v>
       </c>
       <c r="E30">
         <v>-1245.916447695326</v>
@@ -3753,37 +3753,37 @@
         <v>985.9625</v>
       </c>
       <c r="M30">
-        <v>125.5272765867242</v>
+        <v>123.1675669922353</v>
       </c>
       <c r="N30">
-        <v>860.4352234132757</v>
+        <v>862.7949330077647</v>
       </c>
       <c r="O30">
-        <v>292.5479759605138</v>
+        <v>293.35027722264</v>
       </c>
       <c r="P30">
-        <v>567.8872474527619</v>
+        <v>569.4446557851247</v>
       </c>
       <c r="Q30">
-        <v>773.7872474527619</v>
+        <v>775.3446557851247</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1003923956597794</v>
+        <v>0.10038412325812</v>
       </c>
       <c r="T30">
         <v>0.7114141084895027</v>
       </c>
       <c r="U30">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V30">
         <v>0.34</v>
       </c>
       <c r="W30">
-        <v>0.0526641092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.854567762559706</v>
+        <v>8.005049738963805</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08723651298611895</v>
+        <v>0.0866563792384883</v>
       </c>
       <c r="C31">
-        <v>3945.854537261822</v>
+        <v>4012.928550406199</v>
       </c>
       <c r="D31">
-        <v>4867.177828694662</v>
+        <v>4934.251841839039</v>
       </c>
       <c r="E31">
         <v>-1189.73288592178</v>
@@ -3835,45 +3835,45 @@
         <v>985.9625</v>
       </c>
       <c r="M31">
-        <v>132.4543785448279</v>
+        <v>127.5664086705294</v>
       </c>
       <c r="N31">
-        <v>853.508121455172</v>
+        <v>858.3960913294707</v>
       </c>
       <c r="O31">
-        <v>290.1927612947585</v>
+        <v>291.85467105202</v>
       </c>
       <c r="P31">
-        <v>563.3153601604135</v>
+        <v>566.5414202774507</v>
       </c>
       <c r="Q31">
-        <v>769.2153601604135</v>
+        <v>772.4414202774507</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1009532694523763</v>
+        <v>0.1009449120613472</v>
       </c>
       <c r="T31">
         <v>0.7187230665286783</v>
       </c>
       <c r="U31">
-        <v>0.08129410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V31">
         <v>0.34</v>
       </c>
       <c r="W31">
-        <v>0.0536541092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.443789407583159</v>
+        <v>7.729013541068503</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08716735051450394</v>
+        <v>0.08672583914843746</v>
       </c>
       <c r="C32">
-        <v>3897.64668821822</v>
+        <v>3948.539778379127</v>
       </c>
       <c r="D32">
-        <v>4875.153541424606</v>
+        <v>4926.046631585513</v>
       </c>
       <c r="E32">
         <v>-1133.549324148234</v>
@@ -3917,37 +3917,37 @@
         <v>985.9625</v>
       </c>
       <c r="M32">
-        <v>137.0217709084427</v>
+        <v>133.3136558313886</v>
       </c>
       <c r="N32">
-        <v>848.9407290915573</v>
+        <v>852.6488441686113</v>
       </c>
       <c r="O32">
-        <v>288.6398478911295</v>
+        <v>289.9006070173278</v>
       </c>
       <c r="P32">
-        <v>560.3008812004277</v>
+        <v>562.7482371512834</v>
       </c>
       <c r="Q32">
-        <v>766.2008812004277</v>
+        <v>768.6482371512834</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1015301682104759</v>
+        <v>0.1015217234018095</v>
       </c>
       <c r="T32">
         <v>0.7262408519404019</v>
       </c>
       <c r="U32">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V32">
         <v>0.34</v>
       </c>
       <c r="W32">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.195663093997053</v>
+        <v>7.395810233026822</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08709818804288892</v>
+        <v>0.08664217905838661</v>
       </c>
       <c r="C33">
-        <v>3849.465021248152</v>
+        <v>3902.242242411398</v>
       </c>
       <c r="D33">
-        <v>4883.155436228084</v>
+        <v>4935.93265739133</v>
       </c>
       <c r="E33">
         <v>-1077.365762374688</v>
@@ -3999,37 +3999,37 @@
         <v>985.9625</v>
       </c>
       <c r="M33">
-        <v>141.5891632720574</v>
+        <v>137.7574443591016</v>
       </c>
       <c r="N33">
-        <v>844.3733367279426</v>
+        <v>848.2050556408984</v>
       </c>
       <c r="O33">
-        <v>287.0869344875005</v>
+        <v>288.3897189179055</v>
       </c>
       <c r="P33">
-        <v>557.2864022404422</v>
+        <v>559.8153367229929</v>
       </c>
       <c r="Q33">
-        <v>763.1864022404421</v>
+        <v>765.7153367229929</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1021237886717088</v>
+        <v>0.1021152539115605</v>
       </c>
       <c r="T33">
         <v>0.7339765441756535</v>
       </c>
       <c r="U33">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V33">
         <v>0.34</v>
       </c>
       <c r="W33">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.963544929674568</v>
+        <v>7.157235709380797</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.0870290255712739</v>
+        <v>0.08655851896833577</v>
       </c>
       <c r="C34">
-        <v>3801.3096654864</v>
+        <v>3855.984466538617</v>
       </c>
       <c r="D34">
-        <v>4891.183642239879</v>
+        <v>4945.858443292096</v>
       </c>
       <c r="E34">
         <v>-1021.182200601141</v>
@@ -4081,37 +4081,37 @@
         <v>985.9625</v>
       </c>
       <c r="M34">
-        <v>146.1565556356722</v>
+        <v>142.2012328868146</v>
       </c>
       <c r="N34">
-        <v>839.8059443643278</v>
+        <v>843.7612671131855</v>
       </c>
       <c r="O34">
-        <v>285.5340210838715</v>
+        <v>286.8788308184831</v>
       </c>
       <c r="P34">
-        <v>554.2719232804563</v>
+        <v>556.8824362947023</v>
       </c>
       <c r="Q34">
-        <v>760.1719232804563</v>
+        <v>762.7824362947023</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1027348685582721</v>
+        <v>0.1027262412010101</v>
       </c>
       <c r="T34">
         <v>0.7419397567707655</v>
       </c>
       <c r="U34">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V34">
         <v>0.34</v>
       </c>
       <c r="W34">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.745934150622237</v>
+        <v>6.933572093462645</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08695986309965889</v>
+        <v>0.08647485887828492</v>
       </c>
       <c r="C35">
-        <v>3753.180750918375</v>
+        <v>3809.766691107706</v>
       </c>
       <c r="D35">
-        <v>4899.2382894454</v>
+        <v>4955.824229634731</v>
       </c>
       <c r="E35">
         <v>-964.9986388275952</v>
@@ -4163,37 +4163,37 @@
         <v>985.9625</v>
       </c>
       <c r="M35">
-        <v>150.7239479992869</v>
+        <v>146.6450214145275</v>
       </c>
       <c r="N35">
-        <v>835.2385520007131</v>
+        <v>839.3174785854725</v>
       </c>
       <c r="O35">
-        <v>283.9811076802425</v>
+        <v>285.3679427190607</v>
       </c>
       <c r="P35">
-        <v>551.2574443204705</v>
+        <v>553.9495358664118</v>
       </c>
       <c r="Q35">
-        <v>757.1574443204705</v>
+        <v>759.8495358664118</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1033641896354791</v>
+        <v>0.1033554669170104</v>
       </c>
       <c r="T35">
         <v>0.7501406772045376</v>
       </c>
       <c r="U35">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V35">
         <v>0.34</v>
       </c>
       <c r="W35">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.541511903633685</v>
+        <v>6.723463848206203</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08689070062804387</v>
+        <v>0.08639119878823408</v>
       </c>
       <c r="C36">
-        <v>3705.078408387122</v>
+        <v>3763.58915840666</v>
       </c>
       <c r="D36">
-        <v>4907.319508687693</v>
+        <v>4965.830258707231</v>
       </c>
       <c r="E36">
         <v>-908.815077054049</v>
@@ -4245,37 +4245,37 @@
         <v>985.9625</v>
       </c>
       <c r="M36">
-        <v>155.2913403629017</v>
+        <v>151.0888099422405</v>
       </c>
       <c r="N36">
-        <v>830.6711596370983</v>
+        <v>834.8736900577595</v>
       </c>
       <c r="O36">
-        <v>282.4281942766135</v>
+        <v>283.8570546196382</v>
       </c>
       <c r="P36">
-        <v>548.2429653604848</v>
+        <v>551.0166354381213</v>
       </c>
       <c r="Q36">
-        <v>754.1429653604848</v>
+        <v>756.9166354381213</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.104012581048359</v>
+        <v>0.1040037600789502</v>
       </c>
       <c r="T36">
         <v>0.7585901103787271</v>
       </c>
       <c r="U36">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V36">
         <v>0.34</v>
       </c>
       <c r="W36">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.349114494703282</v>
+        <v>6.525714911494255</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08682153815642885</v>
+        <v>0.08630753869818324</v>
       </c>
       <c r="C37">
-        <v>3657.002769600403</v>
+        <v>3717.452112684205</v>
       </c>
       <c r="D37">
-        <v>4915.42743167452</v>
+        <v>4975.876774758322</v>
       </c>
       <c r="E37">
         <v>-852.6315152805028</v>
@@ -4327,37 +4327,37 @@
         <v>985.9625</v>
       </c>
       <c r="M37">
-        <v>159.8587327265165</v>
+        <v>155.5325984699534</v>
       </c>
       <c r="N37">
-        <v>826.1037672734835</v>
+        <v>830.4299015300465</v>
       </c>
       <c r="O37">
-        <v>280.8752808729844</v>
+        <v>282.3461665202158</v>
       </c>
       <c r="P37">
-        <v>545.2284864004992</v>
+        <v>548.0837350098307</v>
       </c>
       <c r="Q37">
-        <v>751.1284864004991</v>
+        <v>753.9837350098306</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1046809229662506</v>
+        <v>0.1046720007227958</v>
       </c>
       <c r="T37">
         <v>0.7672995261121224</v>
       </c>
       <c r="U37">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V37">
         <v>0.34</v>
       </c>
       <c r="W37">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.167711223426045</v>
+        <v>6.339265914022991</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08708501568481383</v>
+        <v>0.08622387860813238</v>
       </c>
       <c r="C38">
-        <v>3570.074194302133</v>
+        <v>3671.355800169659</v>
       </c>
       <c r="D38">
-        <v>4884.682418149796</v>
+        <v>4985.964024017322</v>
       </c>
       <c r="E38">
         <v>-796.4479535069568</v>
@@ -4409,45 +4409,45 @@
         <v>985.9625</v>
       </c>
       <c r="M38">
-        <v>167.2577766035179</v>
+        <v>159.9763869976663</v>
       </c>
       <c r="N38">
-        <v>818.704723396482</v>
+        <v>825.9861130023337</v>
       </c>
       <c r="O38">
-        <v>278.3596059548039</v>
+        <v>280.8352784207935</v>
       </c>
       <c r="P38">
-        <v>540.3451174416781</v>
+        <v>545.1508345815403</v>
       </c>
       <c r="Q38">
-        <v>746.2451174416781</v>
+        <v>751.0508345815402</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1053701505690763</v>
+        <v>0.1053611238867615</v>
       </c>
       <c r="T38">
         <v>0.7762811110871861</v>
       </c>
       <c r="U38">
-        <v>0.08269410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V38">
         <v>0.34</v>
       </c>
       <c r="W38">
-        <v>0.0545781092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y38">
-        <v>5.894867910011798</v>
+        <v>6.16317519418902</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08702509321319882</v>
+        <v>0.08638441851808154</v>
       </c>
       <c r="C39">
-        <v>3520.849108055715</v>
+        <v>3595.851186593749</v>
       </c>
       <c r="D39">
-        <v>4891.640893676925</v>
+        <v>4966.642972214959</v>
       </c>
       <c r="E39">
         <v>-740.2643917334103</v>
@@ -4491,37 +4491,37 @@
         <v>985.9625</v>
       </c>
       <c r="M39">
-        <v>171.9038259536157</v>
+        <v>166.4989673110005</v>
       </c>
       <c r="N39">
-        <v>814.0586740463843</v>
+        <v>819.4635326889995</v>
       </c>
       <c r="O39">
-        <v>276.7799491757707</v>
+        <v>278.6176011142599</v>
       </c>
       <c r="P39">
-        <v>537.2787248706136</v>
+        <v>540.8459315747397</v>
       </c>
       <c r="Q39">
-        <v>743.1787248706136</v>
+        <v>746.7459315747396</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1060812584132616</v>
+        <v>0.1060721239765675</v>
       </c>
       <c r="T39">
         <v>0.7855478257439981</v>
       </c>
       <c r="U39">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V39">
         <v>0.34</v>
       </c>
       <c r="W39">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.735547155687154</v>
+        <v>5.921733425279077</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.0869651707415838</v>
+        <v>0.08630735842803071</v>
       </c>
       <c r="C40">
-        <v>3471.64387548787</v>
+        <v>3548.923119414746</v>
       </c>
       <c r="D40">
-        <v>4898.619222882626</v>
+        <v>4975.898466809502</v>
       </c>
       <c r="E40">
         <v>-684.0808299598643</v>
@@ -4573,37 +4573,37 @@
         <v>985.9625</v>
       </c>
       <c r="M40">
-        <v>176.5498753037133</v>
+        <v>170.998939400487</v>
       </c>
       <c r="N40">
-        <v>809.4126246962867</v>
+        <v>814.9635605995129</v>
       </c>
       <c r="O40">
-        <v>275.2002923967375</v>
+        <v>277.0876106038344</v>
       </c>
       <c r="P40">
-        <v>534.2123322995492</v>
+        <v>537.8759499956784</v>
       </c>
       <c r="Q40">
-        <v>740.1123322995492</v>
+        <v>743.7759499956784</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1068153052201625</v>
+        <v>0.1068060595531413</v>
       </c>
       <c r="T40">
         <v>0.795113466680062</v>
       </c>
       <c r="U40">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V40">
         <v>0.34</v>
       </c>
       <c r="W40">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.584611704221705</v>
+        <v>5.765898335140152</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08690524826996879</v>
+        <v>0.08623029833797985</v>
       </c>
       <c r="C41">
-        <v>3422.458581688716</v>
+        <v>3502.02961244738</v>
       </c>
       <c r="D41">
-        <v>4905.617490857018</v>
+        <v>4985.188521615682</v>
       </c>
       <c r="E41">
         <v>-627.8972681863179</v>
@@ -4655,37 +4655,37 @@
         <v>985.9625</v>
       </c>
       <c r="M41">
-        <v>181.1959246538111</v>
+        <v>175.4989114899735</v>
       </c>
       <c r="N41">
-        <v>804.7665753461889</v>
+        <v>810.4635885100265</v>
       </c>
       <c r="O41">
-        <v>273.6206356177042</v>
+        <v>275.557620093409</v>
       </c>
       <c r="P41">
-        <v>531.1459397284847</v>
+        <v>534.9059684166175</v>
       </c>
       <c r="Q41">
-        <v>737.0459397284847</v>
+        <v>740.8059684166175</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1075734191354864</v>
+        <v>0.1075640585912422</v>
       </c>
       <c r="T41">
         <v>0.8049927351878001</v>
       </c>
       <c r="U41">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V41">
         <v>0.34</v>
       </c>
       <c r="W41">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.441416532318583</v>
+        <v>5.618054788085277</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08684532579835376</v>
+        <v>0.086153238247929</v>
       </c>
       <c r="C42">
-        <v>3373.293312235315</v>
+        <v>3455.170859626562</v>
       </c>
       <c r="D42">
-        <v>4912.635783177163</v>
+        <v>4994.51333056841</v>
       </c>
       <c r="E42">
         <v>-571.7137064127719</v>
@@ -4737,37 +4737,37 @@
         <v>985.9625</v>
       </c>
       <c r="M42">
-        <v>185.8419740039088</v>
+        <v>179.99888357946</v>
       </c>
       <c r="N42">
-        <v>800.1205259960911</v>
+        <v>805.96361642054</v>
       </c>
       <c r="O42">
-        <v>272.040978838671</v>
+        <v>274.0276295829836</v>
       </c>
       <c r="P42">
-        <v>528.0795471574202</v>
+        <v>531.9359868375564</v>
       </c>
       <c r="Q42">
-        <v>733.9795471574201</v>
+        <v>737.8359868375563</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1083568035146544</v>
+        <v>0.1083473242639465</v>
       </c>
       <c r="T42">
         <v>0.8152013126457962</v>
       </c>
       <c r="U42">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V42">
         <v>0.34</v>
       </c>
       <c r="W42">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.305381119010619</v>
+        <v>5.477603418383146</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08678540332673874</v>
+        <v>0.08607617815787816</v>
       </c>
       <c r="C43">
-        <v>3324.148153195151</v>
+        <v>3408.34705634095</v>
       </c>
       <c r="D43">
-        <v>4919.674185910546</v>
+        <v>5003.873089056345</v>
       </c>
       <c r="E43">
         <v>-515.5301446392255</v>
@@ -4819,37 +4819,37 @@
         <v>985.9625</v>
       </c>
       <c r="M43">
-        <v>190.4880233540065</v>
+        <v>184.4988556689465</v>
       </c>
       <c r="N43">
-        <v>795.4744766459935</v>
+        <v>801.4636443310535</v>
       </c>
       <c r="O43">
-        <v>270.4613220596378</v>
+        <v>272.4976390725582</v>
       </c>
       <c r="P43">
-        <v>525.0131545863558</v>
+        <v>528.9660052584952</v>
       </c>
       <c r="Q43">
-        <v>730.9131545863557</v>
+        <v>734.8660052584952</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1091667432965061</v>
+        <v>0.1091571413153865</v>
       </c>
       <c r="T43">
         <v>0.8257559435769447</v>
       </c>
       <c r="U43">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V43">
         <v>0.34</v>
       </c>
       <c r="W43">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.175981579522555</v>
+        <v>5.344003335007947</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08672548085512376</v>
+        <v>0.08599911806782731</v>
       </c>
       <c r="C44">
-        <v>3275.023191129664</v>
+        <v>3361.558399446592</v>
       </c>
       <c r="D44">
-        <v>4926.732785618605</v>
+        <v>5013.267993935533</v>
       </c>
       <c r="E44">
         <v>-459.3465828656795</v>
@@ -4901,37 +4901,37 @@
         <v>985.9625</v>
       </c>
       <c r="M44">
-        <v>195.1340727041042</v>
+        <v>188.998827758433</v>
       </c>
       <c r="N44">
-        <v>790.8284272958957</v>
+        <v>796.963672241567</v>
       </c>
       <c r="O44">
-        <v>268.8816652806046</v>
+        <v>270.9676485621328</v>
       </c>
       <c r="P44">
-        <v>521.9467620152911</v>
+        <v>525.9960236794342</v>
       </c>
       <c r="Q44">
-        <v>727.8467620152911</v>
+        <v>731.8960236794342</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1100046120363527</v>
+        <v>0.1099948830927382</v>
       </c>
       <c r="T44">
         <v>0.8366745272988224</v>
       </c>
       <c r="U44">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V44">
         <v>0.34</v>
       </c>
       <c r="W44">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.052743922867256</v>
+        <v>5.216765160364901</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08666555838350873</v>
+        <v>0.08592205797777647</v>
       </c>
       <c r="C45">
-        <v>3225.918513097793</v>
+        <v>3314.805087280727</v>
       </c>
       <c r="D45">
-        <v>4933.811669360281</v>
+        <v>5022.698243543214</v>
       </c>
       <c r="E45">
         <v>-403.163021092133</v>
@@ -4983,37 +4983,37 @@
         <v>985.9625</v>
       </c>
       <c r="M45">
-        <v>199.780122054202</v>
+        <v>193.4987998479195</v>
       </c>
       <c r="N45">
-        <v>786.182377945798</v>
+        <v>792.4637001520805</v>
       </c>
       <c r="O45">
-        <v>267.3020085015713</v>
+        <v>269.4376580517074</v>
       </c>
       <c r="P45">
-        <v>518.8803694442266</v>
+        <v>523.0260421003732</v>
       </c>
       <c r="Q45">
-        <v>724.7803694442266</v>
+        <v>728.9260421003731</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1108718796793518</v>
+        <v>0.110862019318418</v>
       </c>
       <c r="T45">
         <v>0.8479762192214678</v>
       </c>
       <c r="U45">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V45">
         <v>0.34</v>
       </c>
       <c r="W45">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.935238250242436</v>
+        <v>5.095445040356414</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.0866056359118937</v>
+        <v>0.08584499788772562</v>
       </c>
       <c r="C46">
-        <v>3176.834206659547</v>
+        <v>3268.08731967574</v>
       </c>
       <c r="D46">
-        <v>4940.91092469558</v>
+        <v>5032.164037711773</v>
       </c>
       <c r="E46">
         <v>-346.979459318587</v>
@@ -5065,37 +5065,37 @@
         <v>985.9625</v>
       </c>
       <c r="M46">
-        <v>204.4261714042997</v>
+        <v>197.998771937406</v>
       </c>
       <c r="N46">
-        <v>781.5363285957003</v>
+        <v>787.963728062594</v>
       </c>
       <c r="O46">
-        <v>265.7223517225381</v>
+        <v>267.907667541282</v>
       </c>
       <c r="P46">
-        <v>515.8139768731621</v>
+        <v>520.056060521312</v>
       </c>
       <c r="Q46">
-        <v>721.7139768731621</v>
+        <v>725.956060521312</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1117701211667437</v>
+        <v>0.111760124695015</v>
       </c>
       <c r="T46">
         <v>0.8596815429984934</v>
       </c>
       <c r="U46">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V46">
         <v>0.34</v>
       </c>
       <c r="W46">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.823073744555108</v>
+        <v>4.979639471257405</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08654571344027868</v>
+        <v>0.08576793779767479</v>
       </c>
       <c r="C47">
-        <v>3127.770359879618</v>
+        <v>3221.405297973276</v>
       </c>
       <c r="D47">
-        <v>4948.030639689197</v>
+        <v>5041.665577782856</v>
       </c>
       <c r="E47">
         <v>-290.7958975450406</v>
@@ -5147,37 +5147,37 @@
         <v>985.9625</v>
       </c>
       <c r="M47">
-        <v>209.0722207543974</v>
+        <v>202.4987440268925</v>
       </c>
       <c r="N47">
-        <v>776.8902792456025</v>
+        <v>783.4637559731075</v>
       </c>
       <c r="O47">
-        <v>264.1426949435049</v>
+        <v>266.3776770308565</v>
       </c>
       <c r="P47">
-        <v>512.7475843020977</v>
+        <v>517.0860789422509</v>
       </c>
       <c r="Q47">
-        <v>718.6475843020977</v>
+        <v>722.9860789422509</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1127010259809499</v>
+        <v>0.1126908884489428</v>
       </c>
       <c r="T47">
         <v>0.8718125149128655</v>
       </c>
       <c r="U47">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V47">
         <v>0.34</v>
       </c>
       <c r="W47">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.715894328009439</v>
+        <v>4.868980816340573</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08648579096866367</v>
+        <v>0.08569087770762393</v>
       </c>
       <c r="C48">
-        <v>3078.727061331034</v>
+        <v>3174.759225038533</v>
       </c>
       <c r="D48">
-        <v>4955.170902914159</v>
+        <v>5051.203066621659</v>
       </c>
       <c r="E48">
         <v>-234.6123357714946</v>
@@ -5229,37 +5229,37 @@
         <v>985.9625</v>
       </c>
       <c r="M48">
-        <v>213.7182701044951</v>
+        <v>206.998716116379</v>
       </c>
       <c r="N48">
-        <v>772.2442298955049</v>
+        <v>778.963783883621</v>
       </c>
       <c r="O48">
-        <v>262.5630381644717</v>
+        <v>264.8476865204311</v>
       </c>
       <c r="P48">
-        <v>509.6811917310332</v>
+        <v>514.1160973631899</v>
       </c>
       <c r="Q48">
-        <v>715.5811917310332</v>
+        <v>720.0160973631898</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1136664087512377</v>
+        <v>0.1136561249344975</v>
       </c>
       <c r="T48">
         <v>0.8843927820833252</v>
       </c>
       <c r="U48">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V48">
         <v>0.34</v>
       </c>
       <c r="W48">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.613374886096191</v>
+        <v>4.763133407289692</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08642586849704866</v>
+        <v>0.0856138176175731</v>
       </c>
       <c r="C49">
-        <v>3029.704400098818</v>
+        <v>3128.14930527467</v>
       </c>
       <c r="D49">
-        <v>4962.33180345549</v>
+        <v>5060.776708631342</v>
       </c>
       <c r="E49">
         <v>-178.4287739979482</v>
@@ -5311,37 +5311,37 @@
         <v>985.9625</v>
       </c>
       <c r="M49">
-        <v>218.3643194545929</v>
+        <v>211.4986882058655</v>
       </c>
       <c r="N49">
-        <v>767.5981805454071</v>
+        <v>774.4638117941345</v>
       </c>
       <c r="O49">
-        <v>260.9833813854384</v>
+        <v>263.3176960100058</v>
       </c>
       <c r="P49">
-        <v>506.6147991599687</v>
+        <v>511.1461157841287</v>
       </c>
       <c r="Q49">
-        <v>712.5147991599687</v>
+        <v>717.0461157841287</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1146682210600271</v>
+        <v>0.114657785438375</v>
       </c>
       <c r="T49">
         <v>0.8974477763168213</v>
       </c>
       <c r="U49">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V49">
         <v>0.34</v>
       </c>
       <c r="W49">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.515217973626058</v>
+        <v>4.661790143304804</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08718962602543363</v>
+        <v>0.08553675752752224</v>
       </c>
       <c r="C50">
-        <v>2883.770945564082</v>
+        <v>3081.575744637438</v>
       </c>
       <c r="D50">
-        <v>4872.5819106943</v>
+        <v>5070.386709767656</v>
       </c>
       <c r="E50">
         <v>-122.2452122244022</v>
@@ -5393,45 +5393,45 @@
         <v>985.9625</v>
       </c>
       <c r="M50">
-        <v>230.0220773140291</v>
+        <v>215.998660295352</v>
       </c>
       <c r="N50">
-        <v>755.9404226859708</v>
+        <v>769.963839704648</v>
       </c>
       <c r="O50">
-        <v>257.0197437132301</v>
+        <v>261.7877054995803</v>
       </c>
       <c r="P50">
-        <v>498.9206789727407</v>
+        <v>508.1761342050676</v>
       </c>
       <c r="Q50">
-        <v>704.8206789727408</v>
+        <v>714.0761342050675</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1157085646114621</v>
+        <v>0.1156979713462479</v>
       </c>
       <c r="T50">
         <v>0.911004885713144</v>
       </c>
       <c r="U50">
-        <v>0.08529410488470121</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V50">
         <v>0.34</v>
       </c>
       <c r="W50">
-        <v>0.05629410922390279</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.286382035642393</v>
+        <v>4.564669515319288</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08714686355381862</v>
+        <v>0.0862681974374714</v>
       </c>
       <c r="C51">
-        <v>2832.526560782469</v>
+        <v>2935.620700549124</v>
       </c>
       <c r="D51">
-        <v>4877.521087686233</v>
+        <v>4980.615227452888</v>
       </c>
       <c r="E51">
         <v>-66.06165045085618</v>
@@ -5475,37 +5475,37 @@
         <v>985.9625</v>
       </c>
       <c r="M51">
-        <v>234.814203924738</v>
+        <v>227.3811187020979</v>
       </c>
       <c r="N51">
-        <v>751.1482960752619</v>
+        <v>758.581381297902</v>
       </c>
       <c r="O51">
-        <v>255.3904206655891</v>
+        <v>257.9176696412867</v>
       </c>
       <c r="P51">
-        <v>495.7578754096728</v>
+        <v>500.6637116566153</v>
       </c>
       <c r="Q51">
-        <v>701.6578754096728</v>
+        <v>706.5637116566153</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1167897059492279</v>
+        <v>0.116778948858351</v>
       </c>
       <c r="T51">
         <v>0.9250936464583422</v>
       </c>
       <c r="U51">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V51">
         <v>0.34</v>
       </c>
       <c r="W51">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.198904851241528</v>
+        <v>4.336166985314875</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08710410108220359</v>
+        <v>0.08620763734742054</v>
       </c>
       <c r="C52">
-        <v>2781.292199525873</v>
+        <v>2886.748954952172</v>
       </c>
       <c r="D52">
-        <v>4882.470288203183</v>
+        <v>4987.927043629482</v>
       </c>
       <c r="E52">
         <v>-9.878088677309734</v>
@@ -5557,37 +5557,37 @@
         <v>985.9625</v>
       </c>
       <c r="M52">
-        <v>239.606330535447</v>
+        <v>232.0215496960183</v>
       </c>
       <c r="N52">
-        <v>746.356169464553</v>
+        <v>753.9409503039817</v>
       </c>
       <c r="O52">
-        <v>253.761097617948</v>
+        <v>256.3399231033538</v>
       </c>
       <c r="P52">
-        <v>492.5950718466049</v>
+        <v>497.6010272006279</v>
       </c>
       <c r="Q52">
-        <v>698.4950718466049</v>
+        <v>703.501027200628</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1179140929405044</v>
+        <v>0.1179031654709383</v>
       </c>
       <c r="T52">
         <v>0.9397459576333483</v>
       </c>
       <c r="U52">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V52">
         <v>0.34</v>
       </c>
       <c r="W52">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.114926754216697</v>
+        <v>4.249443645608579</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08706133861058858</v>
+        <v>0.0861470772573697</v>
       </c>
       <c r="C53">
-        <v>2730.067892337774</v>
+        <v>2837.898709212105</v>
       </c>
       <c r="D53">
-        <v>4887.429542788631</v>
+        <v>4995.260359662961</v>
       </c>
       <c r="E53">
         <v>46.30547309623671</v>
@@ -5639,37 +5639,37 @@
         <v>985.9625</v>
       </c>
       <c r="M53">
-        <v>244.3984571461559</v>
+        <v>236.6619806899387</v>
       </c>
       <c r="N53">
-        <v>741.5640428538441</v>
+        <v>749.3005193100613</v>
       </c>
       <c r="O53">
-        <v>252.131774570307</v>
+        <v>254.7621765654209</v>
       </c>
       <c r="P53">
-        <v>489.432268283537</v>
+        <v>494.5383427446404</v>
       </c>
       <c r="Q53">
-        <v>695.332268283537</v>
+        <v>700.4383427446404</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1190843732783636</v>
+        <v>0.1190732684758761</v>
       </c>
       <c r="T53">
         <v>0.9549963223257018</v>
       </c>
       <c r="U53">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V53">
         <v>0.34</v>
       </c>
       <c r="W53">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.034241915898722</v>
+        <v>4.166121221184881</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08794521613897356</v>
+        <v>0.08608651716731885</v>
       </c>
       <c r="C54">
-        <v>2573.384996544067</v>
+        <v>2789.070058296668</v>
       </c>
       <c r="D54">
-        <v>4786.93020876847</v>
+        <v>5002.615270521071</v>
       </c>
       <c r="E54">
         <v>102.4890348697827</v>
@@ -5721,45 +5721,45 @@
         <v>985.9625</v>
       </c>
       <c r="M54">
-        <v>257.0787558298708</v>
+        <v>241.302411683859</v>
       </c>
       <c r="N54">
-        <v>728.8837441701291</v>
+        <v>744.6600883161409</v>
       </c>
       <c r="O54">
-        <v>247.8204730178439</v>
+        <v>253.1844300274879</v>
       </c>
       <c r="P54">
-        <v>481.0632711522852</v>
+        <v>491.475658288653</v>
       </c>
       <c r="Q54">
-        <v>686.9632711522852</v>
+        <v>697.375658288653</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1203034152969669</v>
+        <v>0.1202921257726862</v>
       </c>
       <c r="T54">
         <v>0.9708821188802365</v>
       </c>
       <c r="U54">
-        <v>0.08799410488470122</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V54">
         <v>0.34</v>
       </c>
       <c r="W54">
-        <v>0.0580761092239028</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.835254674456604</v>
+        <v>4.086003505392863</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08792027366735855</v>
+        <v>0.08602595707726801</v>
       </c>
       <c r="C55">
-        <v>2519.980759202344</v>
+        <v>2740.263097733739</v>
       </c>
       <c r="D55">
-        <v>4789.709533200293</v>
+        <v>5009.991871731689</v>
       </c>
       <c r="E55">
         <v>158.6725966433291</v>
@@ -5803,45 +5803,45 @@
         <v>985.9625</v>
       </c>
       <c r="M55">
-        <v>262.0225780573683</v>
+        <v>245.9428426777794</v>
       </c>
       <c r="N55">
-        <v>723.9399219426316</v>
+        <v>740.0196573222206</v>
       </c>
       <c r="O55">
-        <v>246.1395734604948</v>
+        <v>251.606683489555</v>
       </c>
       <c r="P55">
-        <v>477.8003484821368</v>
+        <v>488.4129738326656</v>
       </c>
       <c r="Q55">
-        <v>683.7003484821369</v>
+        <v>694.3129738326655</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1215743314440214</v>
+        <v>0.1215628493374458</v>
       </c>
       <c r="T55">
         <v>0.9874439067775173</v>
       </c>
       <c r="U55">
-        <v>0.08799410488470122</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V55">
         <v>0.34</v>
       </c>
       <c r="W55">
-        <v>0.0580761092239028</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.76289137871214</v>
+        <v>4.008909099630735</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08789533119574353</v>
+        <v>0.08721279698721716</v>
       </c>
       <c r="C56">
-        <v>2466.579751125118</v>
+        <v>2543.368029706994</v>
       </c>
       <c r="D56">
-        <v>4792.492086896613</v>
+        <v>4869.280365478489</v>
       </c>
       <c r="E56">
         <v>214.8561584168751</v>
@@ -5885,37 +5885,37 @@
         <v>985.9625</v>
       </c>
       <c r="M56">
-        <v>266.9664002848658</v>
+        <v>261.2019668468999</v>
       </c>
       <c r="N56">
-        <v>718.9960997151342</v>
+        <v>724.7605331531</v>
       </c>
       <c r="O56">
-        <v>244.4586739031456</v>
+        <v>246.418581272054</v>
       </c>
       <c r="P56">
-        <v>474.5374258119886</v>
+        <v>478.341951881046</v>
       </c>
       <c r="Q56">
-        <v>680.4374258119885</v>
+        <v>684.2419518810459</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1229005048148609</v>
+        <v>0.1228888217528471</v>
       </c>
       <c r="T56">
         <v>1.004725772409463</v>
       </c>
       <c r="U56">
-        <v>0.08799410488470122</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V56">
         <v>0.34</v>
       </c>
       <c r="W56">
-        <v>0.0580761092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.693208205032286</v>
+        <v>3.774713153587809</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08787038872412851</v>
+        <v>0.08717533689716631</v>
       </c>
       <c r="C57">
-        <v>2413.181977943724</v>
+        <v>2491.504820720963</v>
       </c>
       <c r="D57">
-        <v>4795.277875488766</v>
+        <v>4873.600718266005</v>
       </c>
       <c r="E57">
         <v>271.0397201904216</v>
@@ -5967,37 +5967,37 @@
         <v>985.9625</v>
       </c>
       <c r="M57">
-        <v>271.9102225123634</v>
+        <v>266.0390403070278</v>
       </c>
       <c r="N57">
-        <v>714.0522774876366</v>
+        <v>719.9234596929722</v>
       </c>
       <c r="O57">
-        <v>242.7777743457965</v>
+        <v>244.7739762956106</v>
       </c>
       <c r="P57">
-        <v>471.2745031418401</v>
+        <v>475.1494833973616</v>
       </c>
       <c r="Q57">
-        <v>677.1745031418401</v>
+        <v>681.0494833973617</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1242856192244044</v>
+        <v>0.1242737262755995</v>
       </c>
       <c r="T57">
         <v>1.022775720958383</v>
       </c>
       <c r="U57">
-        <v>0.08799410488470122</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V57">
         <v>0.34</v>
       </c>
       <c r="W57">
-        <v>0.0580761092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.626058964940789</v>
+        <v>3.706082005340757</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0878454462525135</v>
+        <v>0.08713787680711549</v>
       </c>
       <c r="C58">
-        <v>2359.787445302604</v>
+        <v>2439.649285158002</v>
       </c>
       <c r="D58">
-        <v>4798.066904621192</v>
+        <v>4877.928744476591</v>
       </c>
       <c r="E58">
         <v>327.223281963968</v>
@@ -6049,37 +6049,37 @@
         <v>985.9625</v>
       </c>
       <c r="M58">
-        <v>276.8540447398609</v>
+        <v>270.8761137671556</v>
       </c>
       <c r="N58">
-        <v>709.1084552601391</v>
+        <v>715.0863862328445</v>
       </c>
       <c r="O58">
-        <v>241.0968747884473</v>
+        <v>243.1293713191671</v>
       </c>
       <c r="P58">
-        <v>468.0115804716918</v>
+        <v>471.9570149136773</v>
       </c>
       <c r="Q58">
-        <v>673.9115804716918</v>
+        <v>677.8570149136773</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1257336933798362</v>
+        <v>0.1257215810039316</v>
       </c>
       <c r="T58">
         <v>1.041646121714073</v>
       </c>
       <c r="U58">
-        <v>0.08799410488470122</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V58">
         <v>0.34</v>
       </c>
       <c r="W58">
-        <v>0.0580761092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.561307911995418</v>
+        <v>3.6399019695311</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08958864378089848</v>
+        <v>0.08710041671706462</v>
       </c>
       <c r="C59">
-        <v>2116.187069429409</v>
+        <v>2387.801443479561</v>
       </c>
       <c r="D59">
-        <v>4610.650090521543</v>
+        <v>4882.264464571695</v>
       </c>
       <c r="E59">
         <v>383.406843737514</v>
@@ -6131,45 +6131,45 @@
         <v>985.9625</v>
       </c>
       <c r="M59">
-        <v>296.8494431664914</v>
+        <v>275.7131872272834</v>
       </c>
       <c r="N59">
-        <v>689.1130568335086</v>
+        <v>710.2493127727166</v>
       </c>
       <c r="O59">
-        <v>234.298439323393</v>
+        <v>241.4847663427237</v>
       </c>
       <c r="P59">
-        <v>454.8146175101157</v>
+        <v>468.7645464299929</v>
       </c>
       <c r="Q59">
-        <v>660.7146175101157</v>
+        <v>674.6645464299929</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1272491198215672</v>
+        <v>0.1272367778126512</v>
       </c>
       <c r="T59">
         <v>1.061394215528167</v>
       </c>
       <c r="U59">
-        <v>0.09269410488470123</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V59">
         <v>0.34</v>
       </c>
       <c r="W59">
-        <v>0.0611781092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.321422770690567</v>
+        <v>3.576044040241081</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08959472130928346</v>
+        <v>0.08706295662701379</v>
       </c>
       <c r="C60">
-        <v>2059.37570135421</v>
+        <v>2335.961316219882</v>
       </c>
       <c r="D60">
-        <v>4610.02228421989</v>
+        <v>4886.607899085561</v>
       </c>
       <c r="E60">
         <v>439.5904055110595</v>
@@ -6213,45 +6213,45 @@
         <v>985.9625</v>
       </c>
       <c r="M60">
-        <v>302.0573281343246</v>
+        <v>280.550260687411</v>
       </c>
       <c r="N60">
-        <v>683.9051718656754</v>
+        <v>705.412239312589</v>
       </c>
       <c r="O60">
-        <v>232.5277584343296</v>
+        <v>239.8401613662803</v>
       </c>
       <c r="P60">
-        <v>451.3774134313458</v>
+        <v>465.5720779463087</v>
       </c>
       <c r="Q60">
-        <v>657.2774134313457</v>
+        <v>671.4720779463087</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1288367094271901</v>
+        <v>0.1288241268503575</v>
       </c>
       <c r="T60">
         <v>1.082082694761979</v>
       </c>
       <c r="U60">
-        <v>0.09269410488470123</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V60">
         <v>0.34</v>
       </c>
       <c r="W60">
-        <v>0.0611781092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.264156860851075</v>
+        <v>3.514388108512788</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08960079883766844</v>
+        <v>0.08811581653696293</v>
       </c>
       <c r="C61">
-        <v>2002.564504225442</v>
+        <v>2160.572450880269</v>
       </c>
       <c r="D61">
-        <v>4609.394648864668</v>
+        <v>4767.402595519495</v>
       </c>
       <c r="E61">
         <v>495.773967284606</v>
@@ -6295,37 +6295,37 @@
         <v>985.9625</v>
       </c>
       <c r="M61">
-        <v>307.2652131021578</v>
+        <v>294.6688585525287</v>
       </c>
       <c r="N61">
-        <v>678.6972868978422</v>
+        <v>691.2936414474713</v>
       </c>
       <c r="O61">
-        <v>230.7570775452664</v>
+        <v>235.0398380921403</v>
       </c>
       <c r="P61">
-        <v>447.9402093525758</v>
+        <v>456.253803355331</v>
       </c>
       <c r="Q61">
-        <v>653.8402093525758</v>
+        <v>662.153803355331</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1305017424282092</v>
+        <v>0.1304889075484397</v>
       </c>
       <c r="T61">
         <v>1.103780368104758</v>
       </c>
       <c r="U61">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V61">
         <v>0.34</v>
       </c>
       <c r="W61">
-        <v>0.0611781092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.208832168294277</v>
+        <v>3.346001694387528</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08960687636605344</v>
+        <v>0.0880968364469121</v>
       </c>
       <c r="C62">
-        <v>1945.753477973295</v>
+        <v>2106.486324637217</v>
       </c>
       <c r="D62">
-        <v>4608.767184386067</v>
+        <v>4769.50003104999</v>
       </c>
       <c r="E62">
         <v>551.9575290581524</v>
@@ -6377,37 +6377,37 @@
         <v>985.9625</v>
       </c>
       <c r="M62">
-        <v>312.473098069991</v>
+        <v>299.6632459856224</v>
       </c>
       <c r="N62">
-        <v>673.4894019300091</v>
+        <v>686.2992540143775</v>
       </c>
       <c r="O62">
-        <v>228.9863966562031</v>
+        <v>233.3417463648884</v>
       </c>
       <c r="P62">
-        <v>444.503005273806</v>
+        <v>452.9575076494891</v>
       </c>
       <c r="Q62">
-        <v>650.403005273806</v>
+        <v>658.8575076494891</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1322500270792794</v>
+        <v>0.132236927281426</v>
       </c>
       <c r="T62">
         <v>1.126562925114677</v>
       </c>
       <c r="U62">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V62">
         <v>0.34</v>
       </c>
       <c r="W62">
-        <v>0.0611781092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.155351632156039</v>
+        <v>3.290234999481069</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08961295389443841</v>
+        <v>0.08807785635686126</v>
       </c>
       <c r="C63">
-        <v>1888.942622527996</v>
+        <v>2052.40204475475</v>
       </c>
       <c r="D63">
-        <v>4608.139890714315</v>
+        <v>4771.599312941069</v>
       </c>
       <c r="E63">
         <v>608.1410908316984</v>
@@ -6459,37 +6459,37 @@
         <v>985.9625</v>
       </c>
       <c r="M63">
-        <v>317.6809830378241</v>
+        <v>304.6576334187161</v>
       </c>
       <c r="N63">
-        <v>668.2815169621758</v>
+        <v>681.3048665812839</v>
       </c>
       <c r="O63">
-        <v>227.2157157671398</v>
+        <v>231.6436546376366</v>
       </c>
       <c r="P63">
-        <v>441.065801195036</v>
+        <v>449.6612119436473</v>
       </c>
       <c r="Q63">
-        <v>646.965801195036</v>
+        <v>655.5612119436473</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1340879673534813</v>
+        <v>0.1340745890520014</v>
       </c>
       <c r="T63">
         <v>1.150513818381514</v>
       </c>
       <c r="U63">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V63">
         <v>0.34</v>
       </c>
       <c r="W63">
-        <v>0.0611781092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.103624556219055</v>
+        <v>3.236296720801052</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08961903142282339</v>
+        <v>0.0880588762668104</v>
       </c>
       <c r="C64">
-        <v>1832.131937819809</v>
+        <v>1998.319613671951</v>
       </c>
       <c r="D64">
-        <v>4607.512767779674</v>
+        <v>4773.700443631816</v>
       </c>
       <c r="E64">
         <v>664.3246526052449</v>
@@ -6541,37 +6541,37 @@
         <v>985.9625</v>
       </c>
       <c r="M64">
-        <v>322.8888680056573</v>
+        <v>309.6520208518099</v>
       </c>
       <c r="N64">
-        <v>663.0736319943426</v>
+        <v>676.3104791481901</v>
       </c>
       <c r="O64">
-        <v>225.4450348780765</v>
+        <v>229.9455629103846</v>
       </c>
       <c r="P64">
-        <v>437.6285971162661</v>
+        <v>446.3649162378055</v>
       </c>
       <c r="Q64">
-        <v>643.528597116266</v>
+        <v>652.2649162378054</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1360226413263254</v>
+        <v>0.1360089698631333</v>
       </c>
       <c r="T64">
         <v>1.175725284978184</v>
       </c>
       <c r="U64">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V64">
         <v>0.34</v>
       </c>
       <c r="W64">
-        <v>0.0611781092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.053566095634876</v>
+        <v>3.184098386594583</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08962510895120837</v>
+        <v>0.08803989617675956</v>
       </c>
       <c r="C65">
-        <v>1775.321423779036</v>
+        <v>1944.2390338322</v>
       </c>
       <c r="D65">
-        <v>4606.885815512447</v>
+        <v>4775.803425565611</v>
       </c>
       <c r="E65">
         <v>720.5082143787909</v>
@@ -6623,37 +6623,37 @@
         <v>985.9625</v>
       </c>
       <c r="M65">
-        <v>328.0967529734905</v>
+        <v>314.6464082849035</v>
       </c>
       <c r="N65">
-        <v>657.8657470265096</v>
+        <v>671.3160917150965</v>
       </c>
       <c r="O65">
-        <v>223.6743539890133</v>
+        <v>228.2474711831328</v>
       </c>
       <c r="P65">
-        <v>434.1913930374963</v>
+        <v>443.0686205319637</v>
       </c>
       <c r="Q65">
-        <v>640.0913930374962</v>
+        <v>648.9686205319637</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1380618922706746</v>
+        <v>0.1380479117991913</v>
       </c>
       <c r="T65">
         <v>1.202299533553053</v>
       </c>
       <c r="U65">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V65">
         <v>0.34</v>
       </c>
       <c r="W65">
-        <v>0.0611781092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.005096792529561</v>
+        <v>3.133557142362923</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.09355950647959335</v>
+        <v>0.08802091608670871</v>
       </c>
       <c r="C66">
-        <v>1346.177735190586</v>
+        <v>1890.160307683188</v>
       </c>
       <c r="D66">
-        <v>4233.925688697544</v>
+        <v>4777.908261190146</v>
       </c>
       <c r="E66">
         <v>776.6917761523373</v>
@@ -6705,45 +6705,45 @@
         <v>985.9625</v>
       </c>
       <c r="M66">
-        <v>366.7450939089384</v>
+        <v>319.6407957179973</v>
       </c>
       <c r="N66">
-        <v>619.2174060910615</v>
+        <v>666.3217042820027</v>
       </c>
       <c r="O66">
-        <v>210.5339180709609</v>
+        <v>226.5493794558809</v>
       </c>
       <c r="P66">
-        <v>408.6834880201006</v>
+        <v>439.7723248261217</v>
       </c>
       <c r="Q66">
-        <v>614.5834880201006</v>
+        <v>645.6723248261217</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1402144349341544</v>
+        <v>0.1402001282872526</v>
       </c>
       <c r="T66">
         <v>1.23035012927097</v>
       </c>
       <c r="U66">
-        <v>0.1019941048847012</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V66">
         <v>0.34</v>
       </c>
       <c r="W66">
-        <v>0.0673161092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.688413604913311</v>
+        <v>3.084595312013502</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.09362696400797835</v>
+        <v>0.08800193599665787</v>
       </c>
       <c r="C67">
-        <v>1284.125391575446</v>
+        <v>1836.083437676924</v>
       </c>
       <c r="D67">
-        <v>4228.05690685595</v>
+        <v>4780.014952957427</v>
       </c>
       <c r="E67">
         <v>832.8753379258833</v>
@@ -6787,45 +6787,45 @@
         <v>985.9625</v>
       </c>
       <c r="M67">
-        <v>372.4754860012655</v>
+        <v>324.635183151091</v>
       </c>
       <c r="N67">
-        <v>613.4870139987345</v>
+        <v>661.327316848909</v>
       </c>
       <c r="O67">
-        <v>208.5855847595697</v>
+        <v>224.8512877286291</v>
       </c>
       <c r="P67">
-        <v>404.9014292391647</v>
+        <v>436.4760291202799</v>
       </c>
       <c r="Q67">
-        <v>610.8014292391647</v>
+        <v>642.3760291202799</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1424899800355472</v>
+        <v>0.1424753285746316</v>
       </c>
       <c r="T67">
         <v>1.260003616172769</v>
       </c>
       <c r="U67">
-        <v>0.1019941048847012</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V67">
         <v>0.34</v>
       </c>
       <c r="W67">
-        <v>0.0673161092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.647053395606953</v>
+        <v>3.037139999520987</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.09369442153636333</v>
+        <v>0.09138063590660703</v>
       </c>
       <c r="C68">
-        <v>1222.089295257455</v>
+        <v>1432.021318878315</v>
       </c>
       <c r="D68">
-        <v>4222.204372311505</v>
+        <v>4432.136395932364</v>
       </c>
       <c r="E68">
         <v>889.0588996994297</v>
@@ -6869,37 +6869,37 @@
         <v>985.9625</v>
       </c>
       <c r="M68">
-        <v>378.2058780935927</v>
+        <v>358.5528681852063</v>
       </c>
       <c r="N68">
-        <v>607.7566219064073</v>
+        <v>627.4096318147937</v>
       </c>
       <c r="O68">
-        <v>206.6372514481785</v>
+        <v>213.3192748170299</v>
       </c>
       <c r="P68">
-        <v>401.1193704582288</v>
+        <v>414.0903569977638</v>
       </c>
       <c r="Q68">
-        <v>607.0193704582288</v>
+        <v>619.9903569977638</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1448993807311396</v>
+        <v>0.1448843641730329</v>
       </c>
       <c r="T68">
         <v>1.291401425833496</v>
       </c>
       <c r="U68">
-        <v>0.1019941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V68">
         <v>0.34</v>
       </c>
       <c r="W68">
-        <v>0.0673161092239028</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.606946525976545</v>
+        <v>2.74983855237413</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.09376187906474831</v>
+        <v>0.09141313581655619</v>
       </c>
       <c r="C69">
-        <v>1160.069378860677</v>
+        <v>1372.737197129794</v>
       </c>
       <c r="D69">
-        <v>4216.368017688274</v>
+        <v>4429.03583595739</v>
       </c>
       <c r="E69">
         <v>945.2424614729762</v>
@@ -6951,37 +6951,37 @@
         <v>985.9625</v>
       </c>
       <c r="M69">
-        <v>383.9362701859199</v>
+        <v>363.9854874001336</v>
       </c>
       <c r="N69">
-        <v>602.0262298140801</v>
+        <v>621.9770125998664</v>
       </c>
       <c r="O69">
-        <v>204.6889181367873</v>
+        <v>211.4721842839546</v>
       </c>
       <c r="P69">
-        <v>397.3373116772929</v>
+        <v>410.5048283159118</v>
       </c>
       <c r="Q69">
-        <v>603.2373116772928</v>
+        <v>616.4048283159118</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1474548057113134</v>
+        <v>0.147439401928913</v>
       </c>
       <c r="T69">
         <v>1.324702133049419</v>
       </c>
       <c r="U69">
-        <v>0.1019941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V69">
         <v>0.34</v>
       </c>
       <c r="W69">
-        <v>0.0673161092239028</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.568036876335103</v>
+        <v>2.708796185920785</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09382933659313328</v>
+        <v>0.09144563572650533</v>
       </c>
       <c r="C70">
-        <v>1098.065575381202</v>
+        <v>1313.457410424591</v>
       </c>
       <c r="D70">
-        <v>4210.547775982344</v>
+        <v>4425.939611025733</v>
       </c>
       <c r="E70">
         <v>1001.426023246522</v>
@@ -7033,37 +7033,37 @@
         <v>985.9625</v>
       </c>
       <c r="M70">
-        <v>389.666662278247</v>
+        <v>369.418106615061</v>
       </c>
       <c r="N70">
-        <v>596.2958377217529</v>
+        <v>616.544393384939</v>
       </c>
       <c r="O70">
-        <v>202.740584825396</v>
+        <v>209.6250937508793</v>
       </c>
       <c r="P70">
-        <v>393.5552528963569</v>
+        <v>406.9192996340597</v>
       </c>
       <c r="Q70">
-        <v>599.4552528963569</v>
+        <v>612.8192996340597</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1501699447527481</v>
+        <v>0.1501541295445357</v>
       </c>
       <c r="T70">
         <v>1.360084134466337</v>
       </c>
       <c r="U70">
-        <v>0.1019941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V70">
         <v>0.34</v>
       </c>
       <c r="W70">
-        <v>0.0673161092239028</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.530271628153705</v>
+        <v>2.668960947892538</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09603717412151827</v>
+        <v>0.09147813563645449</v>
       </c>
       <c r="C71">
-        <v>859.8754670765584</v>
+        <v>1254.1819496775</v>
       </c>
       <c r="D71">
-        <v>4028.541229451247</v>
+        <v>4422.847712052188</v>
       </c>
       <c r="E71">
         <v>1057.609585020069</v>
@@ -7115,45 +7115,45 @@
         <v>985.9625</v>
       </c>
       <c r="M71">
-        <v>413.6173834537352</v>
+        <v>374.8507258299884</v>
       </c>
       <c r="N71">
-        <v>572.3451165462648</v>
+        <v>611.1117741700116</v>
       </c>
       <c r="O71">
-        <v>194.59733962573</v>
+        <v>207.778003217804</v>
       </c>
       <c r="P71">
-        <v>377.7477769205348</v>
+        <v>403.3337709522076</v>
       </c>
       <c r="Q71">
-        <v>583.6477769205347</v>
+        <v>609.2337709522076</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1530602540549205</v>
+        <v>0.1530440008772953</v>
       </c>
       <c r="T71">
         <v>1.397748845652089</v>
       </c>
       <c r="U71">
-        <v>0.1066941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V71">
         <v>0.34</v>
       </c>
       <c r="W71">
-        <v>0.07041810922390279</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.383754985748281</v>
+        <v>2.63028035444482</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09613565164990324</v>
+        <v>0.09151063554640364</v>
       </c>
       <c r="C72">
-        <v>795.9396205654439</v>
+        <v>1194.910805828695</v>
       </c>
       <c r="D72">
-        <v>4020.788944713678</v>
+        <v>4419.760129976929</v>
       </c>
       <c r="E72">
         <v>1113.793146793615</v>
@@ -7197,45 +7197,45 @@
         <v>985.9625</v>
       </c>
       <c r="M72">
-        <v>419.611838286398</v>
+        <v>380.2833450449157</v>
       </c>
       <c r="N72">
-        <v>566.350661713602</v>
+        <v>605.6791549550842</v>
       </c>
       <c r="O72">
-        <v>192.5592249826247</v>
+        <v>205.9309126847286</v>
       </c>
       <c r="P72">
-        <v>373.7914367309773</v>
+        <v>399.7482422703555</v>
       </c>
       <c r="Q72">
-        <v>579.6914367309773</v>
+        <v>605.6482422703555</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1561432506439043</v>
+        <v>0.1561265302989056</v>
       </c>
       <c r="T72">
         <v>1.437924537583557</v>
       </c>
       <c r="U72">
-        <v>0.1066941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V72">
         <v>0.34</v>
       </c>
       <c r="W72">
-        <v>0.07041810922390279</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.349701343094734</v>
+        <v>2.592704920809894</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.09623412917828822</v>
+        <v>0.09154313545635279</v>
       </c>
       <c r="C73">
-        <v>732.0335528196456</v>
+        <v>1135.643969843623</v>
       </c>
       <c r="D73">
-        <v>4013.066438741426</v>
+        <v>4416.676855765404</v>
       </c>
       <c r="E73">
         <v>1169.976708567161</v>
@@ -7279,45 +7279,45 @@
         <v>985.9625</v>
       </c>
       <c r="M73">
-        <v>425.6062931190609</v>
+        <v>385.7159642598431</v>
       </c>
       <c r="N73">
-        <v>560.3562068809391</v>
+        <v>600.2465357401568</v>
       </c>
       <c r="O73">
-        <v>190.5211103395193</v>
+        <v>204.0838221516533</v>
       </c>
       <c r="P73">
-        <v>369.8350965414198</v>
+        <v>396.1627135885035</v>
       </c>
       <c r="Q73">
-        <v>575.7350965414198</v>
+        <v>602.0627135885035</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1594388676873008</v>
+        <v>0.1594216479564889</v>
       </c>
       <c r="T73">
         <v>1.480870966889609</v>
       </c>
       <c r="U73">
-        <v>0.1066941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V73">
         <v>0.34</v>
       </c>
       <c r="W73">
-        <v>0.07041810922390279</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.316606957980724</v>
+        <v>2.556187950094261</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09633260670667321</v>
+        <v>0.09157563536630195</v>
       </c>
       <c r="C74">
-        <v>668.1570925848182</v>
+        <v>1076.381432712928</v>
       </c>
       <c r="D74">
-        <v>4005.373540280145</v>
+        <v>4413.597880408254</v>
       </c>
       <c r="E74">
         <v>1226.160270340707</v>
@@ -7361,45 +7361,45 @@
         <v>985.9625</v>
       </c>
       <c r="M74">
-        <v>431.6007479517236</v>
+        <v>391.1485834747705</v>
       </c>
       <c r="N74">
-        <v>554.3617520482763</v>
+        <v>594.8139165252295</v>
       </c>
       <c r="O74">
-        <v>188.482995696414</v>
+        <v>202.236731618578</v>
       </c>
       <c r="P74">
-        <v>365.8787563518624</v>
+        <v>392.5771849066515</v>
       </c>
       <c r="Q74">
-        <v>571.7787563518623</v>
+        <v>598.4771849066515</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1629698859480829</v>
+        <v>0.1629521311610426</v>
       </c>
       <c r="T74">
         <v>1.526884998288951</v>
       </c>
       <c r="U74">
-        <v>0.1066941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V74">
         <v>0.34</v>
       </c>
       <c r="W74">
-        <v>0.07041810922390279</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.284431861342103</v>
+        <v>2.520685339676286</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.0964310842350582</v>
+        <v>0.09348715527625109</v>
       </c>
       <c r="C75">
-        <v>604.3100699172646</v>
+        <v>846.3584098130586</v>
       </c>
       <c r="D75">
-        <v>3997.710079386137</v>
+        <v>4239.758419281931</v>
       </c>
       <c r="E75">
         <v>1282.343832114253</v>
@@ -7443,37 +7443,37 @@
         <v>985.9625</v>
       </c>
       <c r="M75">
-        <v>437.5952027843865</v>
+        <v>412.5766627266264</v>
       </c>
       <c r="N75">
-        <v>548.3672972156135</v>
+        <v>573.3858372733737</v>
       </c>
       <c r="O75">
-        <v>186.4448810533086</v>
+        <v>194.9511846729471</v>
       </c>
       <c r="P75">
-        <v>361.9224161623049</v>
+        <v>378.4346526004266</v>
       </c>
       <c r="Q75">
-        <v>567.8224161623049</v>
+        <v>584.3346526004266</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.166762461117071</v>
+        <v>0.1667441316400076</v>
       </c>
       <c r="T75">
         <v>1.576307476458615</v>
       </c>
       <c r="U75">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V75">
         <v>0.34</v>
       </c>
       <c r="W75">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.25313827420043</v>
+        <v>2.389767985140012</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09652956176344318</v>
+        <v>0.09354539518620025</v>
       </c>
       <c r="C76">
-        <v>540.4923161714032</v>
+        <v>785.0930462189835</v>
       </c>
       <c r="D76">
-        <v>3990.075887413823</v>
+        <v>4234.676617461403</v>
       </c>
       <c r="E76">
         <v>1338.527393887799</v>
@@ -7525,37 +7525,37 @@
         <v>985.9625</v>
       </c>
       <c r="M76">
-        <v>443.5896576170493</v>
+        <v>418.2283978324706</v>
       </c>
       <c r="N76">
-        <v>542.3728423829507</v>
+        <v>567.7341021675294</v>
       </c>
       <c r="O76">
-        <v>184.4067664102033</v>
+        <v>193.02959473696</v>
       </c>
       <c r="P76">
-        <v>357.9660759727474</v>
+        <v>374.7045074305694</v>
       </c>
       <c r="Q76">
-        <v>563.8660759727475</v>
+        <v>580.6045074305694</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1708467728375197</v>
+        <v>0.1708278244635084</v>
       </c>
       <c r="T76">
         <v>1.629531683718253</v>
       </c>
       <c r="U76">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V76">
         <v>0.34</v>
       </c>
       <c r="W76">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.222690459684209</v>
+        <v>2.35747382317866</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.09662803929182817</v>
+        <v>0.0936036350961494</v>
       </c>
       <c r="C77">
-        <v>476.7036639874186</v>
+        <v>723.8398502017335</v>
       </c>
       <c r="D77">
-        <v>3982.470797003384</v>
+        <v>4229.606983217699</v>
       </c>
       <c r="E77">
         <v>1394.710955661345</v>
@@ -7607,37 +7607,37 @@
         <v>985.9625</v>
       </c>
       <c r="M77">
-        <v>449.5841124497122</v>
+        <v>423.8801329383148</v>
       </c>
       <c r="N77">
-        <v>536.3783875502878</v>
+        <v>562.0823670616852</v>
       </c>
       <c r="O77">
-        <v>182.3686517670979</v>
+        <v>191.108004800973</v>
       </c>
       <c r="P77">
-        <v>354.00973578319</v>
+        <v>370.9743622607122</v>
       </c>
       <c r="Q77">
-        <v>559.9097357831899</v>
+        <v>576.8743622607121</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1752578294956043</v>
+        <v>0.1752382127128892</v>
       </c>
       <c r="T77">
         <v>1.687013827558661</v>
       </c>
       <c r="U77">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V77">
         <v>0.34</v>
       </c>
       <c r="W77">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.193054586888419</v>
+        <v>2.326040838869611</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.09672651682021315</v>
+        <v>0.09366187500609856</v>
       </c>
       <c r="C78">
-        <v>412.9439472790127</v>
+        <v>662.5987781135282</v>
       </c>
       <c r="D78">
-        <v>3974.894642068524</v>
+        <v>4224.54947290304</v>
       </c>
       <c r="E78">
         <v>1450.894517434891</v>
@@ -7689,37 +7689,37 @@
         <v>985.9625</v>
       </c>
       <c r="M78">
-        <v>455.5785672823749</v>
+        <v>429.531868044159</v>
       </c>
       <c r="N78">
-        <v>530.383932717625</v>
+        <v>556.430631955841</v>
       </c>
       <c r="O78">
-        <v>180.3305371239925</v>
+        <v>189.1864148649859</v>
       </c>
       <c r="P78">
-        <v>350.0533955936326</v>
+        <v>367.244217090855</v>
       </c>
       <c r="Q78">
-        <v>555.9533955936325</v>
+        <v>573.144217090855</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1800364742085293</v>
+        <v>0.1800161333163852</v>
       </c>
       <c r="T78">
         <v>1.749286150052438</v>
       </c>
       <c r="U78">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V78">
         <v>0.34</v>
       </c>
       <c r="W78">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.164198605481992</v>
+        <v>2.295435038358169</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.09682499434859812</v>
+        <v>0.0937201149160477</v>
       </c>
       <c r="C79">
-        <v>349.2130012213211</v>
+        <v>601.3697865151098</v>
       </c>
       <c r="D79">
-        <v>3967.34725778438</v>
+        <v>4219.504043078168</v>
       </c>
       <c r="E79">
         <v>1507.078079208438</v>
@@ -7771,37 +7771,37 @@
         <v>985.9625</v>
       </c>
       <c r="M79">
-        <v>461.5730221150379</v>
+        <v>435.1836031500033</v>
       </c>
       <c r="N79">
-        <v>524.3894778849622</v>
+        <v>550.7788968499967</v>
       </c>
       <c r="O79">
-        <v>178.2924224808872</v>
+        <v>187.2648249289989</v>
       </c>
       <c r="P79">
-        <v>346.097055404075</v>
+        <v>363.5140719209978</v>
       </c>
       <c r="Q79">
-        <v>551.997055404075</v>
+        <v>569.4140719209978</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1852306532443173</v>
+        <v>0.1852095252767068</v>
       </c>
       <c r="T79">
         <v>1.81697345711089</v>
       </c>
       <c r="U79">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V79">
         <v>0.34</v>
       </c>
       <c r="W79">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.136092130086122</v>
+        <v>2.265624193704166</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.09692347187698311</v>
+        <v>0.09377835482599686</v>
       </c>
       <c r="C80">
-        <v>285.510662238964</v>
+        <v>540.1528321744909</v>
       </c>
       <c r="D80">
-        <v>3959.828480575569</v>
+        <v>4214.470650511095</v>
       </c>
       <c r="E80">
         <v>1563.261640981984</v>
@@ -7853,37 +7853,37 @@
         <v>985.9625</v>
       </c>
       <c r="M80">
-        <v>467.5674769477007</v>
+        <v>440.8353382558474</v>
       </c>
       <c r="N80">
-        <v>518.3950230522993</v>
+        <v>545.1271617441525</v>
       </c>
       <c r="O80">
-        <v>176.2543078377818</v>
+        <v>185.3432349930119</v>
       </c>
       <c r="P80">
-        <v>342.1407152145175</v>
+        <v>359.7839267511407</v>
       </c>
       <c r="Q80">
-        <v>548.0407152145175</v>
+        <v>565.6839267511407</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1908970303742679</v>
+        <v>0.1908750437788758</v>
       </c>
       <c r="T80">
         <v>1.890814155720111</v>
       </c>
       <c r="U80">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V80">
         <v>0.34</v>
       </c>
       <c r="W80">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.108706333546556</v>
+        <v>2.236577729682318</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.0970219494053681</v>
+        <v>0.09383659473594602</v>
       </c>
       <c r="C81">
-        <v>221.8367679942257</v>
+        <v>478.9478720657244</v>
       </c>
       <c r="D81">
-        <v>3952.338148104376</v>
+        <v>4209.449252175875</v>
       </c>
       <c r="E81">
         <v>1619.44520275553</v>
@@ -7935,37 +7935,37 @@
         <v>985.9625</v>
       </c>
       <c r="M81">
-        <v>473.5619317803635</v>
+        <v>446.4870733616916</v>
       </c>
       <c r="N81">
-        <v>512.4005682196365</v>
+        <v>539.4754266383084</v>
       </c>
       <c r="O81">
-        <v>174.2161931946764</v>
+        <v>183.4216450570248</v>
       </c>
       <c r="P81">
-        <v>338.1843750249601</v>
+        <v>356.0537815812835</v>
       </c>
       <c r="Q81">
-        <v>544.0843750249601</v>
+        <v>561.9537815812835</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1971030624689757</v>
+        <v>0.1970801354717277</v>
       </c>
       <c r="T81">
         <v>1.971687301815924</v>
       </c>
       <c r="U81">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V81">
         <v>0.34</v>
       </c>
       <c r="W81">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.08201384831179</v>
+        <v>2.20826661918001</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.09712042693375308</v>
+        <v>0.09389483464589517</v>
       </c>
       <c r="C82">
-        <v>158.1911573753678</v>
+        <v>417.7548633676734</v>
       </c>
       <c r="D82">
-        <v>3944.876099259064</v>
+        <v>4204.43980525137</v>
       </c>
       <c r="E82">
         <v>1675.628764529076</v>
@@ -8017,37 +8017,37 @@
         <v>985.9625</v>
       </c>
       <c r="M82">
-        <v>479.5563866130263</v>
+        <v>452.1388084675357</v>
       </c>
       <c r="N82">
-        <v>506.4061133869737</v>
+        <v>533.8236915324642</v>
       </c>
       <c r="O82">
-        <v>172.1780785515711</v>
+        <v>181.5000551210378</v>
       </c>
       <c r="P82">
-        <v>334.2280348354026</v>
+        <v>352.3236364114264</v>
       </c>
       <c r="Q82">
-        <v>540.1280348354026</v>
+        <v>558.2236364114264</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2039296977731543</v>
+        <v>0.2039057363338647</v>
       </c>
       <c r="T82">
         <v>2.060647762521318</v>
       </c>
       <c r="U82">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V82">
         <v>0.34</v>
       </c>
       <c r="W82">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.055988675207893</v>
+        <v>2.18066328644026</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09721890446213806</v>
+        <v>0.09395307455584433</v>
       </c>
       <c r="C83">
-        <v>94.5736704850824</v>
+        <v>356.5737634627922</v>
       </c>
       <c r="D83">
-        <v>3937.442174142326</v>
+        <v>4199.442267120035</v>
       </c>
       <c r="E83">
         <v>1731.812326302623</v>
@@ -8099,37 +8099,37 @@
         <v>985.9625</v>
       </c>
       <c r="M83">
-        <v>485.5508414456892</v>
+        <v>457.79054357338</v>
       </c>
       <c r="N83">
-        <v>500.4116585543108</v>
+        <v>528.17195642662</v>
       </c>
       <c r="O83">
-        <v>170.1399639084657</v>
+        <v>179.5784651850508</v>
       </c>
       <c r="P83">
-        <v>330.2716946458451</v>
+        <v>348.5934912415692</v>
       </c>
       <c r="Q83">
-        <v>536.171694645845</v>
+        <v>554.4934912415691</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2114749262672463</v>
+        <v>0.2114498214972793</v>
       </c>
       <c r="T83">
         <v>2.158972482248334</v>
       </c>
       <c r="U83">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V83">
         <v>0.34</v>
       </c>
       <c r="W83">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.030606098970758</v>
+        <v>2.153741517471862</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09731738199052303</v>
+        <v>0.09401131446579349</v>
       </c>
       <c r="C84">
-        <v>30.98414862906975</v>
+        <v>295.4045299359268</v>
       </c>
       <c r="D84">
-        <v>3930.036214059859</v>
+        <v>4194.456595366716</v>
       </c>
       <c r="E84">
         <v>1787.995888076169</v>
@@ -8181,37 +8181,37 @@
         <v>985.9625</v>
       </c>
       <c r="M84">
-        <v>491.545296278352</v>
+        <v>463.4422786792242</v>
       </c>
       <c r="N84">
-        <v>494.417203721648</v>
+        <v>522.5202213207758</v>
       </c>
       <c r="O84">
-        <v>168.1018492653603</v>
+        <v>177.6568752490638</v>
       </c>
       <c r="P84">
-        <v>326.3153544562877</v>
+        <v>344.863346071712</v>
       </c>
       <c r="Q84">
-        <v>532.2153544562876</v>
+        <v>550.763346071712</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2198585134829042</v>
+        <v>0.2198321383455178</v>
       </c>
       <c r="T84">
         <v>2.268222170833906</v>
       </c>
       <c r="U84">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V84">
         <v>0.34</v>
       </c>
       <c r="W84">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.005842609958919</v>
+        <v>2.127476377014888</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.106344999518908</v>
+        <v>0.09406955437574263</v>
       </c>
       <c r="C85">
-        <v>-603.181310781757</v>
+        <v>234.2471205731081</v>
       </c>
       <c r="D85">
-        <v>3352.054316422578</v>
+        <v>4189.482747777443</v>
       </c>
       <c r="E85">
         <v>1844.179449849715</v>
@@ -8263,45 +8263,45 @@
         <v>985.9625</v>
       </c>
       <c r="M85">
-        <v>573.5504918344456</v>
+        <v>469.0940137850684</v>
       </c>
       <c r="N85">
-        <v>412.4120081655544</v>
+        <v>516.8684862149316</v>
       </c>
       <c r="O85">
-        <v>140.2200827762885</v>
+        <v>175.7352853130768</v>
       </c>
       <c r="P85">
-        <v>272.1919253892659</v>
+        <v>341.1332009018549</v>
       </c>
       <c r="Q85">
-        <v>478.0919253892659</v>
+        <v>547.0332009018548</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2292284050768748</v>
+        <v>0.2292006101170784</v>
       </c>
       <c r="T85">
         <v>2.390324763958957</v>
       </c>
       <c r="U85">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V85">
         <v>0.34</v>
       </c>
       <c r="W85">
-        <v>0.0811761092239028</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y85">
-        <v>1.719050918858939</v>
+        <v>2.101844131508685</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.106551057047293</v>
+        <v>0.09412779428569179</v>
       </c>
       <c r="C86">
-        <v>-670.5795979303048</v>
+        <v>173.1014933603565</v>
       </c>
       <c r="D86">
-        <v>3340.839591047577</v>
+        <v>4184.520682338238</v>
       </c>
       <c r="E86">
         <v>1900.363011623261</v>
@@ -8345,45 +8345,45 @@
         <v>985.9625</v>
       </c>
       <c r="M86">
-        <v>580.4607387240171</v>
+        <v>474.7457488909125</v>
       </c>
       <c r="N86">
-        <v>405.5017612759829</v>
+        <v>511.2167511090875</v>
       </c>
       <c r="O86">
-        <v>137.8705988338342</v>
+        <v>173.8136953770897</v>
       </c>
       <c r="P86">
-        <v>267.6311624421487</v>
+        <v>337.4030557319977</v>
       </c>
       <c r="Q86">
-        <v>473.5311624421487</v>
+        <v>543.3030557319977</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2397695331200916</v>
+        <v>0.239740140860084</v>
       </c>
       <c r="T86">
         <v>2.527690181224639</v>
       </c>
       <c r="U86">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V86">
         <v>0.34</v>
       </c>
       <c r="W86">
-        <v>0.0811761092239028</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.698586026967761</v>
+        <v>2.076822177562153</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.106757114575678</v>
+        <v>0.09418603419564094</v>
       </c>
       <c r="C87">
-        <v>-737.9030947105098</v>
+        <v>111.9676064825107</v>
       </c>
       <c r="D87">
-        <v>3329.699656040917</v>
+        <v>4179.570357233938</v>
       </c>
       <c r="E87">
         <v>1956.546573396807</v>
@@ -8427,45 +8427,45 @@
         <v>985.9625</v>
       </c>
       <c r="M87">
-        <v>587.3709856135887</v>
+        <v>480.3974839967567</v>
       </c>
       <c r="N87">
-        <v>398.5915143864113</v>
+        <v>505.5650160032433</v>
       </c>
       <c r="O87">
-        <v>135.5211148913799</v>
+        <v>171.8921054411027</v>
       </c>
       <c r="P87">
-        <v>263.0703994950314</v>
+        <v>333.6729105621405</v>
       </c>
       <c r="Q87">
-        <v>468.9703994950314</v>
+        <v>539.5729105621406</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2517161449024041</v>
+        <v>0.2516849423688238</v>
       </c>
       <c r="T87">
         <v>2.683370987459079</v>
       </c>
       <c r="U87">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V87">
         <v>0.34</v>
       </c>
       <c r="W87">
-        <v>0.0811761092239028</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.678602661944611</v>
+        <v>2.052388975473186</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.106963172104063</v>
+        <v>0.0942442741055901</v>
       </c>
       <c r="C88">
-        <v>-805.1525467950432</v>
+        <v>50.84541832204013</v>
       </c>
       <c r="D88">
-        <v>3318.633765729931</v>
+        <v>4174.631730847014</v>
       </c>
       <c r="E88">
         <v>2012.730135170354</v>
@@ -8509,45 +8509,45 @@
         <v>985.9625</v>
       </c>
       <c r="M88">
-        <v>594.2812325031605</v>
+        <v>486.049219102601</v>
       </c>
       <c r="N88">
-        <v>391.6812674968395</v>
+        <v>499.913280897399</v>
       </c>
       <c r="O88">
-        <v>133.1716309489254</v>
+        <v>169.9705155051157</v>
       </c>
       <c r="P88">
-        <v>258.5096365479141</v>
+        <v>329.9427653922833</v>
       </c>
       <c r="Q88">
-        <v>464.409636547914</v>
+        <v>535.8427653922834</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2653694155107612</v>
+        <v>0.2653361440930978</v>
       </c>
       <c r="T88">
         <v>2.861291908869867</v>
       </c>
       <c r="U88">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V88">
         <v>0.34</v>
       </c>
       <c r="W88">
-        <v>0.0811761092239028</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y88">
-        <v>1.659084026340604</v>
+        <v>2.028523987386289</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.107169229632448</v>
+        <v>0.09430251401553924</v>
       </c>
       <c r="C89">
-        <v>-872.3286899767654</v>
+        <v>-10.265112542108</v>
       </c>
       <c r="D89">
-        <v>3307.641184321755</v>
+        <v>4169.704761756412</v>
       </c>
       <c r="E89">
         <v>2068.9136969439</v>
@@ -8591,45 +8591,45 @@
         <v>985.9625</v>
       </c>
       <c r="M89">
-        <v>601.191479392732</v>
+        <v>491.7009542084452</v>
       </c>
       <c r="N89">
-        <v>384.7710206072679</v>
+        <v>494.2615457915548</v>
       </c>
       <c r="O89">
-        <v>130.8221470064711</v>
+        <v>168.0489255691286</v>
       </c>
       <c r="P89">
-        <v>253.9488736007968</v>
+        <v>326.2126202224262</v>
       </c>
       <c r="Q89">
-        <v>459.8488736007968</v>
+        <v>532.1126202224261</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2811231892896348</v>
+        <v>0.2810875306980294</v>
       </c>
       <c r="T89">
         <v>3.06658527972847</v>
       </c>
       <c r="U89">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V89">
         <v>0.34</v>
       </c>
       <c r="W89">
-        <v>0.0811761092239028</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.640014095003356</v>
+        <v>2.005207619715182</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1073752871608329</v>
+        <v>0.1026081139254884</v>
       </c>
       <c r="C90">
-        <v>-939.4322503318172</v>
+        <v>-667.1504210444755</v>
       </c>
       <c r="D90">
-        <v>3296.721185740249</v>
+        <v>3569.003015027591</v>
       </c>
       <c r="E90">
         <v>2125.097258717446</v>
@@ -8673,37 +8673,37 @@
         <v>985.9625</v>
       </c>
       <c r="M90">
-        <v>608.1017262823036</v>
+        <v>567.5596681065127</v>
       </c>
       <c r="N90">
-        <v>377.8607737176964</v>
+        <v>418.4028318934872</v>
       </c>
       <c r="O90">
-        <v>128.4726630640168</v>
+        <v>142.2569628437857</v>
       </c>
       <c r="P90">
-        <v>249.3881106536796</v>
+        <v>276.1458690497016</v>
       </c>
       <c r="Q90">
-        <v>455.2881106536796</v>
+        <v>482.0458690497015</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.299502592031654</v>
+        <v>0.2994641484037829</v>
       </c>
       <c r="T90">
         <v>3.30609421239684</v>
       </c>
       <c r="U90">
-        <v>0.1229941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V90">
         <v>0.34</v>
       </c>
       <c r="W90">
-        <v>0.0811761092239028</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.6213775711965</v>
+        <v>1.737196202276597</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1075813446892179</v>
+        <v>0.1027600738354376</v>
       </c>
       <c r="C91">
-        <v>-1006.463944379486</v>
+        <v>-732.7164125283452</v>
       </c>
       <c r="D91">
-        <v>3285.873053466126</v>
+        <v>3559.620585317267</v>
       </c>
       <c r="E91">
         <v>2181.280820490992</v>
@@ -8755,37 +8755,37 @@
         <v>985.9625</v>
       </c>
       <c r="M91">
-        <v>615.0119731718753</v>
+        <v>574.0092097895413</v>
       </c>
       <c r="N91">
-        <v>370.9505268281247</v>
+        <v>411.9532902104587</v>
       </c>
       <c r="O91">
-        <v>126.1231791215624</v>
+        <v>140.064118671556</v>
       </c>
       <c r="P91">
-        <v>244.8273477065623</v>
+        <v>271.8891715389027</v>
       </c>
       <c r="Q91">
-        <v>450.7273477065622</v>
+        <v>477.7891715389027</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3212237043631312</v>
+        <v>0.3211819693287644</v>
       </c>
       <c r="T91">
         <v>3.589150223732186</v>
       </c>
       <c r="U91">
-        <v>0.1229941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V91">
         <v>0.34</v>
       </c>
       <c r="W91">
-        <v>0.0811761092239028</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.603159845677438</v>
+        <v>1.717677143824051</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1077874022176029</v>
+        <v>0.1029120337453867</v>
       </c>
       <c r="C92">
-        <v>-1073.42447923893</v>
+        <v>-798.2332030590878</v>
       </c>
       <c r="D92">
-        <v>3275.096080380229</v>
+        <v>3550.287356560071</v>
       </c>
       <c r="E92">
         <v>2237.464382264539</v>
@@ -8837,37 +8837,37 @@
         <v>985.9625</v>
       </c>
       <c r="M92">
-        <v>621.922220061447</v>
+        <v>580.4587514725699</v>
       </c>
       <c r="N92">
-        <v>364.040279938553</v>
+        <v>405.50374852743</v>
       </c>
       <c r="O92">
-        <v>123.773695179108</v>
+        <v>137.8712744993262</v>
       </c>
       <c r="P92">
-        <v>240.266584759445</v>
+        <v>267.6324740281038</v>
       </c>
       <c r="Q92">
-        <v>446.166584759445</v>
+        <v>473.5324740281038</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.347289039160904</v>
+        <v>0.347243354438742</v>
       </c>
       <c r="T92">
         <v>3.928817437334601</v>
       </c>
       <c r="U92">
-        <v>0.1229941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V92">
         <v>0.34</v>
       </c>
       <c r="W92">
-        <v>0.0811761092239028</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.585346958503244</v>
+        <v>1.698591842226006</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1079934597459879</v>
+        <v>0.1030639936553359</v>
       </c>
       <c r="C93">
-        <v>-1140.314552782819</v>
+        <v>-863.7011786353241</v>
       </c>
       <c r="D93">
-        <v>3264.389568609886</v>
+        <v>3541.00294275738</v>
       </c>
       <c r="E93">
         <v>2293.647944038085</v>
@@ -8919,37 +8919,37 @@
         <v>985.9625</v>
       </c>
       <c r="M93">
-        <v>628.8324669510185</v>
+        <v>586.9082931555985</v>
       </c>
       <c r="N93">
-        <v>357.1300330489814</v>
+        <v>399.0542068444015</v>
       </c>
       <c r="O93">
-        <v>121.4242112366537</v>
+        <v>135.6784303270965</v>
       </c>
       <c r="P93">
-        <v>235.7058218123277</v>
+        <v>263.375776517305</v>
       </c>
       <c r="Q93">
-        <v>441.6058218123277</v>
+        <v>469.275776517305</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3791466705804039</v>
+        <v>0.3790961584620482</v>
       </c>
       <c r="T93">
         <v>4.343966253959776</v>
       </c>
       <c r="U93">
-        <v>0.1229941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V93">
         <v>0.34</v>
       </c>
       <c r="W93">
-        <v>0.0811761092239028</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.567925563354857</v>
+        <v>1.67992599780594</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1081995172743729</v>
+        <v>0.103215953565285</v>
       </c>
       <c r="C94">
-        <v>-1207.13485378799</v>
+        <v>-929.1207212284835</v>
       </c>
       <c r="D94">
-        <v>3253.752829378261</v>
+        <v>3531.766961937768</v>
       </c>
       <c r="E94">
         <v>2349.831505811631</v>
@@ -9001,37 +9001,37 @@
         <v>985.9625</v>
       </c>
       <c r="M94">
-        <v>635.7427138405902</v>
+        <v>593.357834838627</v>
       </c>
       <c r="N94">
-        <v>350.2197861594098</v>
+        <v>392.604665161373</v>
       </c>
       <c r="O94">
-        <v>119.0747272941993</v>
+        <v>133.4855861548668</v>
       </c>
       <c r="P94">
-        <v>231.1450588652104</v>
+        <v>259.1190790065061</v>
       </c>
       <c r="Q94">
-        <v>437.0450588652104</v>
+        <v>465.0190790065061</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.418968709854779</v>
+        <v>0.4189121634911809</v>
       </c>
       <c r="T94">
         <v>4.862902274741245</v>
       </c>
       <c r="U94">
-        <v>0.1229941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V94">
         <v>0.34</v>
       </c>
       <c r="W94">
-        <v>0.0811761092239028</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.550882894187956</v>
+        <v>1.661665932612397</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1084055748027579</v>
+        <v>0.1033679134752342</v>
       </c>
       <c r="C95">
-        <v>-1273.886062083154</v>
+        <v>-994.4922088351832</v>
       </c>
       <c r="D95">
-        <v>3243.185182856644</v>
+        <v>3522.579036104615</v>
       </c>
       <c r="E95">
         <v>2406.015067585178</v>
@@ -9083,37 +9083,37 @@
         <v>985.9625</v>
       </c>
       <c r="M95">
-        <v>642.6529607301619</v>
+        <v>599.8073765216557</v>
       </c>
       <c r="N95">
-        <v>343.3095392698381</v>
+        <v>386.1551234783443</v>
       </c>
       <c r="O95">
-        <v>116.725243351745</v>
+        <v>131.2927419826371</v>
       </c>
       <c r="P95">
-        <v>226.5842959180931</v>
+        <v>254.8623814957072</v>
       </c>
       <c r="Q95">
-        <v>432.4842959180931</v>
+        <v>460.7623814957072</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4701684746361182</v>
+        <v>0.4701041699572086</v>
       </c>
       <c r="T95">
         <v>5.530105730031704</v>
       </c>
       <c r="U95">
-        <v>0.1229941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V95">
         <v>0.34</v>
       </c>
       <c r="W95">
-        <v>0.0811761092239028</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.534206734035397</v>
+        <v>1.643798556992909</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1086116323311428</v>
+        <v>0.1035198733851833</v>
       </c>
       <c r="C96">
-        <v>-1340.568848693723</v>
+        <v>-1059.8160155288</v>
       </c>
       <c r="D96">
-        <v>3232.685958019621</v>
+        <v>3513.438791184545</v>
       </c>
       <c r="E96">
         <v>2462.198629358724</v>
@@ -9165,37 +9165,37 @@
         <v>985.9625</v>
       </c>
       <c r="M96">
-        <v>649.5632076197335</v>
+        <v>606.2569182046842</v>
       </c>
       <c r="N96">
-        <v>336.3992923802665</v>
+        <v>379.7055817953158</v>
       </c>
       <c r="O96">
-        <v>114.3757594092906</v>
+        <v>129.0998978104074</v>
       </c>
       <c r="P96">
-        <v>222.0235329709759</v>
+        <v>250.6056839849084</v>
       </c>
       <c r="Q96">
-        <v>427.9235329709759</v>
+        <v>456.5056839849084</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.538434827677904</v>
+        <v>0.5383601785785789</v>
       </c>
       <c r="T96">
         <v>6.41971033708565</v>
       </c>
       <c r="U96">
-        <v>0.1229941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V96">
         <v>0.34</v>
       </c>
       <c r="W96">
-        <v>0.0811761092239028</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.517885385800978</v>
+        <v>1.626311338301495</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1088176898595278</v>
+        <v>0.1036718332951325</v>
       </c>
       <c r="C97">
-        <v>-1407.183875983863</v>
+        <v>-1125.092511510238</v>
       </c>
       <c r="D97">
-        <v>3222.254492503027</v>
+        <v>3504.345856976652</v>
       </c>
       <c r="E97">
         <v>2518.38219113227</v>
@@ -9247,37 +9247,37 @@
         <v>985.9625</v>
       </c>
       <c r="M97">
-        <v>656.4734545093052</v>
+        <v>612.7064598877126</v>
       </c>
       <c r="N97">
-        <v>329.4890454906948</v>
+        <v>373.2560401122873</v>
       </c>
       <c r="O97">
-        <v>112.0262754668363</v>
+        <v>126.9070536381777</v>
       </c>
       <c r="P97">
-        <v>217.4627700238586</v>
+        <v>246.3489864741096</v>
       </c>
       <c r="Q97">
-        <v>423.3627700238586</v>
+        <v>452.2489864741096</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.634007721936404</v>
+        <v>0.6339185906484974</v>
       </c>
       <c r="T97">
         <v>7.665156786961177</v>
       </c>
       <c r="U97">
-        <v>0.1229941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V97">
         <v>0.34</v>
       </c>
       <c r="W97">
-        <v>0.0811761092239028</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.50190764489781</v>
+        <v>1.609192271582532</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.152707518921077</v>
+        <v>0.1038237932050816</v>
       </c>
       <c r="C98">
-        <v>-2775.930919177538</v>
+        <v>-1190.322063157911</v>
       </c>
       <c r="D98">
-        <v>1909.691011082898</v>
+        <v>3495.299867102525</v>
       </c>
       <c r="E98">
         <v>2574.565752905816</v>
@@ -9329,45 +9329,45 @@
         <v>985.9625</v>
       </c>
       <c r="M98">
-        <v>1016.126575637909</v>
+        <v>619.1560015707412</v>
       </c>
       <c r="N98">
-        <v>-30.16407563790926</v>
+        <v>366.8064984292588</v>
       </c>
       <c r="O98">
-        <v>-10.25578571688915</v>
+        <v>124.714209465948</v>
       </c>
       <c r="P98">
-        <v>-19.90828992102011</v>
+        <v>242.0922889633108</v>
       </c>
       <c r="Q98">
-        <v>185.9917100789798</v>
+        <v>447.9922889633108</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.7878901810039397</v>
+        <v>0.7772562087533732</v>
       </c>
       <c r="T98">
-        <v>9.670457179197996</v>
+        <v>9.53332646177444</v>
       </c>
       <c r="U98">
-        <v>0.1883941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V98">
-        <v>0.3299069801314362</v>
+        <v>0.34</v>
       </c>
       <c r="W98">
-        <v>0.1262415746676244</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.9703146474454005</v>
+        <v>1.592429852086881</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1541334599699241</v>
+        <v>0.1039757531150308</v>
       </c>
       <c r="C99">
-        <v>-2857.057637852693</v>
+        <v>-1255.505033076948</v>
       </c>
       <c r="D99">
-        <v>1884.747854181289</v>
+        <v>3486.300458957034</v>
       </c>
       <c r="E99">
         <v>2630.749314679362</v>
@@ -9411,45 +9411,45 @@
         <v>985.9625</v>
       </c>
       <c r="M99">
-        <v>1026.711227467471</v>
+        <v>625.6055432537697</v>
       </c>
       <c r="N99">
-        <v>-40.74872746747076</v>
+        <v>360.3569567462303</v>
       </c>
       <c r="O99">
-        <v>-13.85456733894006</v>
+        <v>122.5213652937183</v>
       </c>
       <c r="P99">
-        <v>-26.8941601285307</v>
+        <v>237.8355914525119</v>
       </c>
       <c r="Q99">
-        <v>179.0058398714693</v>
+        <v>443.7355914525119</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.03525357467192</v>
+        <v>1.016152238928169</v>
       </c>
       <c r="T99">
-        <v>12.89394290559733</v>
+        <v>12.64694258646324</v>
       </c>
       <c r="U99">
-        <v>0.1883941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V99">
-        <v>0.3265058772434832</v>
+        <v>0.34</v>
       </c>
       <c r="W99">
-        <v>0.1268823224018211</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.9603114036573036</v>
+        <v>1.576013049488047</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1555594010187711</v>
+        <v>0.10412771302498</v>
       </c>
       <c r="C100">
-        <v>-2937.541174383631</v>
+        <v>-1320.641780147644</v>
       </c>
       <c r="D100">
-        <v>1860.447879423896</v>
+        <v>3477.347273659884</v>
       </c>
       <c r="E100">
         <v>2686.932876452908</v>
@@ -9493,45 +9493,45 @@
         <v>985.9625</v>
       </c>
       <c r="M100">
-        <v>1037.295879297032</v>
+        <v>632.0550849367983</v>
       </c>
       <c r="N100">
-        <v>-51.33337929703237</v>
+        <v>353.9074150632017</v>
       </c>
       <c r="O100">
-        <v>-17.453348960991</v>
+        <v>120.3285211214886</v>
       </c>
       <c r="P100">
-        <v>-33.88003033604136</v>
+        <v>233.5788939417131</v>
       </c>
       <c r="Q100">
-        <v>172.0199696639586</v>
+        <v>439.4788939417131</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.52998036200788</v>
+        <v>1.493944299277759</v>
       </c>
       <c r="T100">
-        <v>19.34091435839599</v>
+        <v>18.87417483584085</v>
       </c>
       <c r="U100">
-        <v>0.1883941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V100">
-        <v>0.3231741846185497</v>
+        <v>0.34</v>
       </c>
       <c r="W100">
-        <v>0.1275099936516464</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.9505123077016168</v>
+        <v>1.559931283676945</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.156985342067618</v>
+        <v>0.1042796729349291</v>
       </c>
       <c r="C101">
-        <v>-3017.406089668672</v>
+        <v>-1385.732659573171</v>
       </c>
       <c r="D101">
-        <v>1836.766525912403</v>
+        <v>3468.439956007903</v>
       </c>
       <c r="E101">
         <v>2743.116438226455</v>
@@ -9575,45 +9575,45 @@
         <v>985.9625</v>
       </c>
       <c r="M101">
-        <v>1047.880531126594</v>
+        <v>638.5046266198269</v>
       </c>
       <c r="N101">
-        <v>-61.91803112659397</v>
+        <v>347.4578733801731</v>
       </c>
       <c r="O101">
-        <v>-21.05213058304195</v>
+        <v>118.1356769492589</v>
       </c>
       <c r="P101">
-        <v>-40.86590054355202</v>
+        <v>229.3221964309142</v>
       </c>
       <c r="Q101">
-        <v>165.034099456448</v>
+        <v>435.2221964309142</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.014160724015759</v>
+        <v>2.927320480326531</v>
       </c>
       <c r="T101">
-        <v>38.68182871679198</v>
+        <v>37.55587158397365</v>
       </c>
       <c r="U101">
-        <v>0.1883941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V101">
-        <v>0.3199097989153321</v>
+        <v>0.34</v>
       </c>
       <c r="W101">
-        <v>0.1281249846742025</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.9409111732803883</v>
+        <v>1.544174402023642</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/brazil/brazil_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_oil_gas_distribution.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08923564184996283</v>
+        <v>0.08912558175991198</v>
       </c>
       <c r="C2">
-        <v>5354.836507670298</v>
+        <v>5310.231681104189</v>
       </c>
       <c r="D2">
-        <v>4646.836507670298</v>
+        <v>4658.415242877735</v>
       </c>
       <c r="E2">
-        <v>-2819.05617735462</v>
+        <v>-2762.872615581074</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>56.18356177354621</v>
       </c>
       <c r="G2">
         <v>708</v>
@@ -1457,28 +1457,28 @@
         <v>985.9625</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.219054280618769</v>
       </c>
       <c r="N2">
-        <v>985.9625</v>
+        <v>981.7434457193812</v>
       </c>
       <c r="O2">
-        <v>335.22725</v>
+        <v>333.7927715445896</v>
       </c>
       <c r="P2">
-        <v>650.73525</v>
+        <v>647.9506741747915</v>
       </c>
       <c r="Q2">
-        <v>856.6352499999999</v>
+        <v>853.8506741747915</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08923564184996283</v>
+        <v>0.08952521279562925</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5698861028218297</v>
       </c>
       <c r="U2">
         <v>0.07509410488470122</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>233.6927743568632</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08912558175991198</v>
+        <v>0.08901552166986114</v>
       </c>
       <c r="C3">
-        <v>5310.231681104189</v>
+        <v>5265.684701206198</v>
       </c>
       <c r="D3">
-        <v>4658.415242877735</v>
+        <v>4670.05182475329</v>
       </c>
       <c r="E3">
-        <v>-2762.872615581074</v>
+        <v>-2706.689053807528</v>
       </c>
       <c r="F3">
-        <v>56.18356177354621</v>
+        <v>112.3671235470924</v>
       </c>
       <c r="G3">
         <v>708</v>
@@ -1539,28 +1539,28 @@
         <v>985.9625</v>
       </c>
       <c r="M3">
-        <v>4.219054280618769</v>
+        <v>8.438108561237538</v>
       </c>
       <c r="N3">
-        <v>981.7434457193812</v>
+        <v>977.5243914387624</v>
       </c>
       <c r="O3">
-        <v>333.7927715445896</v>
+        <v>332.3582930891793</v>
       </c>
       <c r="P3">
-        <v>647.9506741747915</v>
+        <v>645.1660983495832</v>
       </c>
       <c r="Q3">
-        <v>853.8506741747915</v>
+        <v>851.0660983495832</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08952521279562925</v>
+        <v>0.08982069335243172</v>
       </c>
       <c r="T3">
-        <v>0.5698861028218297</v>
+        <v>0.5737372050168684</v>
       </c>
       <c r="U3">
         <v>0.07509410488470122</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>233.6927743568632</v>
+        <v>116.8463871784316</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08901552166986114</v>
+        <v>0.0889054615798103</v>
       </c>
       <c r="C4">
-        <v>5265.684701206198</v>
+        <v>5221.196002559636</v>
       </c>
       <c r="D4">
-        <v>4670.05182475329</v>
+        <v>4681.746687880275</v>
       </c>
       <c r="E4">
-        <v>-2706.689053807528</v>
+        <v>-2650.505492033982</v>
       </c>
       <c r="F4">
-        <v>112.3671235470924</v>
+        <v>168.5506853206386</v>
       </c>
       <c r="G4">
         <v>708</v>
@@ -1621,28 +1621,28 @@
         <v>985.9625</v>
       </c>
       <c r="M4">
-        <v>8.438108561237538</v>
+        <v>12.65716284185631</v>
       </c>
       <c r="N4">
-        <v>977.5243914387624</v>
+        <v>973.3053371581436</v>
       </c>
       <c r="O4">
-        <v>332.3582930891793</v>
+        <v>330.9238146337689</v>
       </c>
       <c r="P4">
-        <v>645.1660983495832</v>
+        <v>642.3815225243748</v>
       </c>
       <c r="Q4">
-        <v>851.0660983495832</v>
+        <v>848.2815225243747</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08982069335243172</v>
+        <v>0.09012226629184868</v>
       </c>
       <c r="T4">
-        <v>0.5737372050168684</v>
+        <v>0.5776677113808771</v>
       </c>
       <c r="U4">
         <v>0.07509410488470122</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>116.8463871784316</v>
+        <v>77.89759145228774</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0889054615798103</v>
+        <v>0.08879540148975944</v>
       </c>
       <c r="C5">
-        <v>5221.196002559636</v>
+        <v>5176.766024111934</v>
       </c>
       <c r="D5">
-        <v>4681.746687880275</v>
+        <v>4693.500271206119</v>
       </c>
       <c r="E5">
-        <v>-2650.505492033982</v>
+        <v>-2594.321930260435</v>
       </c>
       <c r="F5">
-        <v>168.5506853206386</v>
+        <v>224.7342470941848</v>
       </c>
       <c r="G5">
         <v>708</v>
@@ -1703,28 +1703,28 @@
         <v>985.9625</v>
       </c>
       <c r="M5">
-        <v>12.65716284185631</v>
+        <v>16.87621712247508</v>
       </c>
       <c r="N5">
-        <v>973.3053371581436</v>
+        <v>969.0862828775249</v>
       </c>
       <c r="O5">
-        <v>330.9238146337689</v>
+        <v>329.4893361783585</v>
       </c>
       <c r="P5">
-        <v>642.3815225243748</v>
+        <v>639.5969466991664</v>
       </c>
       <c r="Q5">
-        <v>848.2815225243747</v>
+        <v>845.4969466991664</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09012226629184868</v>
+        <v>0.0904301220008368</v>
       </c>
       <c r="T5">
-        <v>0.5776677113808771</v>
+        <v>0.5816801032941359</v>
       </c>
       <c r="U5">
         <v>0.07509410488470122</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>77.89759145228774</v>
+        <v>58.42319358921581</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08879540148975944</v>
+        <v>0.0886853413997086</v>
       </c>
       <c r="C6">
-        <v>5176.766024111934</v>
+        <v>5132.395209229529</v>
       </c>
       <c r="D6">
-        <v>4693.500271206119</v>
+        <v>4705.313018097259</v>
       </c>
       <c r="E6">
-        <v>-2594.321930260435</v>
+        <v>-2538.138368486889</v>
       </c>
       <c r="F6">
-        <v>224.7342470941848</v>
+        <v>280.917808867731</v>
       </c>
       <c r="G6">
         <v>708</v>
@@ -1785,28 +1785,28 @@
         <v>985.9625</v>
       </c>
       <c r="M6">
-        <v>16.87621712247508</v>
+        <v>21.09527140309385</v>
       </c>
       <c r="N6">
-        <v>969.0862828775249</v>
+        <v>964.8672285969061</v>
       </c>
       <c r="O6">
-        <v>329.4893361783585</v>
+        <v>328.0548577229481</v>
       </c>
       <c r="P6">
-        <v>639.5969466991664</v>
+        <v>636.812370873958</v>
       </c>
       <c r="Q6">
-        <v>845.4969466991664</v>
+        <v>842.712370873958</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0904301220008368</v>
+        <v>0.09074445888264575</v>
       </c>
       <c r="T6">
-        <v>0.5816801032941359</v>
+        <v>0.5857769666160948</v>
       </c>
       <c r="U6">
         <v>0.07509410488470122</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>58.42319358921581</v>
+        <v>46.73855487137264</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0886853413997086</v>
+        <v>0.08857528130965776</v>
       </c>
       <c r="C7">
-        <v>5132.395209229529</v>
+        <v>5088.084005753646</v>
       </c>
       <c r="D7">
-        <v>4705.313018097259</v>
+        <v>4717.185376394923</v>
       </c>
       <c r="E7">
-        <v>-2538.138368486889</v>
+        <v>-2481.954806713343</v>
       </c>
       <c r="F7">
-        <v>280.917808867731</v>
+        <v>337.1013706412773</v>
       </c>
       <c r="G7">
         <v>708</v>
@@ -1867,28 +1867,28 @@
         <v>985.9625</v>
       </c>
       <c r="M7">
-        <v>21.09527140309385</v>
+        <v>25.31432568371262</v>
       </c>
       <c r="N7">
-        <v>964.8672285969061</v>
+        <v>960.6481743162874</v>
       </c>
       <c r="O7">
-        <v>328.0548577229481</v>
+        <v>326.6203792675377</v>
       </c>
       <c r="P7">
-        <v>636.812370873958</v>
+        <v>634.0277950487497</v>
       </c>
       <c r="Q7">
-        <v>842.712370873958</v>
+        <v>839.9277950487497</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09074445888264575</v>
+        <v>0.09106548378321659</v>
       </c>
       <c r="T7">
-        <v>0.5857769666160948</v>
+        <v>0.5899609972427764</v>
       </c>
       <c r="U7">
         <v>0.07509410488470122</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.73855487137264</v>
+        <v>38.94879572614386</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08857528130965776</v>
+        <v>0.08846522121960691</v>
       </c>
       <c r="C8">
-        <v>5088.084005753646</v>
+        <v>5043.832866056883</v>
       </c>
       <c r="D8">
-        <v>4717.185376394923</v>
+        <v>4729.117798471707</v>
       </c>
       <c r="E8">
-        <v>-2481.954806713343</v>
+        <v>-2425.771244939797</v>
       </c>
       <c r="F8">
-        <v>337.1013706412772</v>
+        <v>393.2849324148234</v>
       </c>
       <c r="G8">
         <v>708</v>
@@ -1949,28 +1949,28 @@
         <v>985.9625</v>
       </c>
       <c r="M8">
-        <v>25.31432568371261</v>
+        <v>29.53337996433138</v>
       </c>
       <c r="N8">
-        <v>960.6481743162874</v>
+        <v>956.4291200356686</v>
       </c>
       <c r="O8">
-        <v>326.6203792675377</v>
+        <v>325.1859008121273</v>
       </c>
       <c r="P8">
-        <v>634.0277950487497</v>
+        <v>631.2432192235412</v>
       </c>
       <c r="Q8">
-        <v>839.9277950487497</v>
+        <v>837.1432192235412</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09106548378321659</v>
+        <v>0.09139341244509001</v>
       </c>
       <c r="T8">
-        <v>0.5899609972427764</v>
+        <v>0.5942350070227197</v>
       </c>
       <c r="U8">
         <v>0.07509410488470122</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.94879572614388</v>
+        <v>33.38468205098047</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08846522121960691</v>
+        <v>0.08835516112955608</v>
       </c>
       <c r="C9">
-        <v>5043.832866056883</v>
+        <v>4999.642247100663</v>
       </c>
       <c r="D9">
-        <v>4729.117798471707</v>
+        <v>4741.110741289032</v>
       </c>
       <c r="E9">
-        <v>-2425.771244939797</v>
+        <v>-2369.58768316625</v>
       </c>
       <c r="F9">
-        <v>393.2849324148235</v>
+        <v>449.4684941883697</v>
       </c>
       <c r="G9">
         <v>708</v>
@@ -2031,28 +2031,28 @@
         <v>985.9625</v>
       </c>
       <c r="M9">
-        <v>29.53337996433139</v>
+        <v>33.75243424495015</v>
       </c>
       <c r="N9">
-        <v>956.4291200356686</v>
+        <v>952.2100657550499</v>
       </c>
       <c r="O9">
-        <v>325.1859008121273</v>
+        <v>323.751422356717</v>
       </c>
       <c r="P9">
-        <v>631.2432192235412</v>
+        <v>628.4586433983329</v>
       </c>
       <c r="Q9">
-        <v>837.1432192235412</v>
+        <v>834.3586433983329</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09139341244509003</v>
+        <v>0.09172846999091722</v>
       </c>
       <c r="T9">
-        <v>0.5942350070227198</v>
+        <v>0.5986019300587488</v>
       </c>
       <c r="U9">
         <v>0.07509410488470122</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.38468205098046</v>
+        <v>29.21159679460791</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08835516112955608</v>
+        <v>0.08824510103950521</v>
       </c>
       <c r="C10">
-        <v>4999.642247100663</v>
+        <v>4955.512610493576</v>
       </c>
       <c r="D10">
-        <v>4741.110741289032</v>
+        <v>4753.164666455492</v>
       </c>
       <c r="E10">
-        <v>-2369.58768316625</v>
+        <v>-2313.404121392704</v>
       </c>
       <c r="F10">
-        <v>449.4684941883697</v>
+        <v>505.6520559619158</v>
       </c>
       <c r="G10">
         <v>708</v>
@@ -2113,28 +2113,28 @@
         <v>985.9625</v>
       </c>
       <c r="M10">
-        <v>33.75243424495015</v>
+        <v>37.97148852556892</v>
       </c>
       <c r="N10">
-        <v>952.2100657550499</v>
+        <v>947.991011474431</v>
       </c>
       <c r="O10">
-        <v>323.751422356717</v>
+        <v>322.3169439013066</v>
       </c>
       <c r="P10">
-        <v>628.4586433983329</v>
+        <v>625.6740675731245</v>
       </c>
       <c r="Q10">
-        <v>834.3586433983329</v>
+        <v>831.5740675731245</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09172846999091722</v>
+        <v>0.0920708914388505</v>
       </c>
       <c r="T10">
-        <v>0.5986019300587488</v>
+        <v>0.6030648294252402</v>
       </c>
       <c r="U10">
         <v>0.07509410488470122</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.21159679460791</v>
+        <v>25.96586381742925</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08824510103950521</v>
+        <v>0.08813504094945437</v>
       </c>
       <c r="C11">
-        <v>4955.512610493576</v>
+        <v>4911.444422550593</v>
       </c>
       <c r="D11">
-        <v>4753.164666455492</v>
+        <v>4765.280040286055</v>
       </c>
       <c r="E11">
-        <v>-2313.404121392704</v>
+        <v>-2257.220559619158</v>
       </c>
       <c r="F11">
-        <v>505.6520559619158</v>
+        <v>561.8356177354621</v>
       </c>
       <c r="G11">
         <v>708</v>
@@ -2195,28 +2195,28 @@
         <v>985.9625</v>
       </c>
       <c r="M11">
-        <v>37.97148852556892</v>
+        <v>42.19054280618769</v>
       </c>
       <c r="N11">
-        <v>947.991011474431</v>
+        <v>943.7719571938123</v>
       </c>
       <c r="O11">
-        <v>322.3169439013066</v>
+        <v>320.8824654458962</v>
       </c>
       <c r="P11">
-        <v>625.6740675731245</v>
+        <v>622.8894917479161</v>
       </c>
       <c r="Q11">
-        <v>831.5740675731245</v>
+        <v>828.789491747916</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0920708914388505</v>
+        <v>0.09242092225229344</v>
       </c>
       <c r="T11">
-        <v>0.6030648294252402</v>
+        <v>0.6076269043332092</v>
       </c>
       <c r="U11">
         <v>0.07509410488470122</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.96586381742925</v>
+        <v>23.36927743568632</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08813504094945437</v>
+        <v>0.08802498085940352</v>
       </c>
       <c r="C12">
-        <v>4911.444422550593</v>
+        <v>4867.438154353217</v>
       </c>
       <c r="D12">
-        <v>4765.280040286055</v>
+        <v>4777.457333862226</v>
       </c>
       <c r="E12">
-        <v>-2257.220559619158</v>
+        <v>-2201.036997845612</v>
       </c>
       <c r="F12">
-        <v>561.8356177354621</v>
+        <v>618.0191795090083</v>
       </c>
       <c r="G12">
         <v>708</v>
@@ -2277,28 +2277,28 @@
         <v>985.9625</v>
       </c>
       <c r="M12">
-        <v>42.19054280618769</v>
+        <v>46.40959708680646</v>
       </c>
       <c r="N12">
-        <v>943.7719571938123</v>
+        <v>939.5529029131935</v>
       </c>
       <c r="O12">
-        <v>320.8824654458962</v>
+        <v>319.4479869904858</v>
       </c>
       <c r="P12">
-        <v>622.8894917479161</v>
+        <v>620.1049159227077</v>
       </c>
       <c r="Q12">
-        <v>828.789491747916</v>
+        <v>826.0049159227077</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09242092225229344</v>
+        <v>0.09277881892671261</v>
       </c>
       <c r="T12">
-        <v>0.6076269043332092</v>
+        <v>0.6122914977784358</v>
       </c>
       <c r="U12">
         <v>0.07509410488470122</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.36927743568632</v>
+        <v>21.24479766880575</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08802498085940352</v>
+        <v>0.0879149207693527</v>
       </c>
       <c r="C13">
-        <v>4867.438154353217</v>
+        <v>4823.494281810527</v>
       </c>
       <c r="D13">
-        <v>4777.457333862226</v>
+        <v>4789.697023093082</v>
       </c>
       <c r="E13">
-        <v>-2201.036997845612</v>
+        <v>-2144.853436072066</v>
       </c>
       <c r="F13">
-        <v>618.0191795090083</v>
+        <v>674.2027412825545</v>
       </c>
       <c r="G13">
         <v>708</v>
@@ -2359,28 +2359,28 @@
         <v>985.9625</v>
       </c>
       <c r="M13">
-        <v>46.40959708680646</v>
+        <v>50.62865136742523</v>
       </c>
       <c r="N13">
-        <v>939.5529029131935</v>
+        <v>935.3338486325747</v>
       </c>
       <c r="O13">
-        <v>319.4479869904858</v>
+        <v>318.0135085350754</v>
       </c>
       <c r="P13">
-        <v>620.1049159227077</v>
+        <v>617.3203400974993</v>
       </c>
       <c r="Q13">
-        <v>826.0049159227077</v>
+        <v>823.2203400974993</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09277881892671261</v>
+        <v>0.0931448496164595</v>
       </c>
       <c r="T13">
-        <v>0.6122914977784358</v>
+        <v>0.6170621047110542</v>
       </c>
       <c r="U13">
         <v>0.07509410488470122</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.24479766880575</v>
+        <v>19.47439786307194</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0879149207693527</v>
+        <v>0.08780486067930184</v>
       </c>
       <c r="C14">
-        <v>4823.494281810527</v>
+        <v>4779.613285721192</v>
       </c>
       <c r="D14">
-        <v>4789.697023093082</v>
+        <v>4801.999588777293</v>
       </c>
       <c r="E14">
-        <v>-2144.853436072066</v>
+        <v>-2088.66987429852</v>
       </c>
       <c r="F14">
-        <v>674.2027412825545</v>
+        <v>730.3863030561007</v>
       </c>
       <c r="G14">
         <v>708</v>
@@ -2441,28 +2441,28 @@
         <v>985.9625</v>
       </c>
       <c r="M14">
-        <v>50.62865136742523</v>
+        <v>54.847705648044</v>
       </c>
       <c r="N14">
-        <v>935.3338486325747</v>
+        <v>931.114794351956</v>
       </c>
       <c r="O14">
-        <v>318.0135085350754</v>
+        <v>316.5790300796651</v>
       </c>
       <c r="P14">
-        <v>617.3203400974993</v>
+        <v>614.5357642722909</v>
       </c>
       <c r="Q14">
-        <v>823.2203400974993</v>
+        <v>820.4357642722908</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0931448496164595</v>
+        <v>0.09351929480482124</v>
       </c>
       <c r="T14">
-        <v>0.6170621047110542</v>
+        <v>0.6219423807685601</v>
       </c>
       <c r="U14">
         <v>0.07509410488470122</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.47439786307194</v>
+        <v>17.97636725822025</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08780486067930184</v>
+        <v>0.08769480058925098</v>
       </c>
       <c r="C15">
-        <v>4779.613285721192</v>
+        <v>4735.795651836406</v>
       </c>
       <c r="D15">
-        <v>4801.999588777293</v>
+        <v>4814.365516666053</v>
       </c>
       <c r="E15">
-        <v>-2088.66987429852</v>
+        <v>-2032.486312524973</v>
       </c>
       <c r="F15">
-        <v>730.3863030561007</v>
+        <v>786.569864829647</v>
       </c>
       <c r="G15">
         <v>708</v>
@@ -2523,28 +2523,28 @@
         <v>985.9625</v>
       </c>
       <c r="M15">
-        <v>54.847705648044</v>
+        <v>59.06675992866278</v>
       </c>
       <c r="N15">
-        <v>931.114794351956</v>
+        <v>926.8957400713372</v>
       </c>
       <c r="O15">
-        <v>316.5790300796651</v>
+        <v>315.1445516242547</v>
       </c>
       <c r="P15">
-        <v>614.5357642722909</v>
+        <v>611.7511884470825</v>
       </c>
       <c r="Q15">
-        <v>820.4357642722908</v>
+        <v>817.6511884470825</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09351929480482124</v>
+        <v>0.0939024480208193</v>
       </c>
       <c r="T15">
-        <v>0.6219423807685601</v>
+        <v>0.626936151618101</v>
       </c>
       <c r="U15">
         <v>0.07509410488470122</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.97636725822025</v>
+        <v>16.69234102549023</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08769480058925098</v>
+        <v>0.08758474049920016</v>
       </c>
       <c r="C16">
-        <v>4735.795651836406</v>
+        <v>4692.041870923838</v>
       </c>
       <c r="D16">
-        <v>4814.365516666053</v>
+        <v>4826.795297527032</v>
       </c>
       <c r="E16">
-        <v>-2032.486312524973</v>
+        <v>-1976.302750751427</v>
       </c>
       <c r="F16">
-        <v>786.569864829647</v>
+        <v>842.7534266031932</v>
       </c>
       <c r="G16">
         <v>708</v>
@@ -2605,28 +2605,28 @@
         <v>985.9625</v>
       </c>
       <c r="M16">
-        <v>59.06675992866278</v>
+        <v>63.28581420928155</v>
       </c>
       <c r="N16">
-        <v>926.8957400713372</v>
+        <v>922.6766857907185</v>
       </c>
       <c r="O16">
-        <v>315.1445516242547</v>
+        <v>313.7100731688443</v>
       </c>
       <c r="P16">
-        <v>611.7511884470825</v>
+        <v>608.9666126218742</v>
       </c>
       <c r="Q16">
-        <v>817.6511884470825</v>
+        <v>814.8666126218742</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0939024480208193</v>
+        <v>0.09429461660660557</v>
       </c>
       <c r="T16">
-        <v>0.626936151618101</v>
+        <v>0.6320474229582195</v>
       </c>
       <c r="U16">
         <v>0.07509410488470122</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.69234102549023</v>
+        <v>15.57951829045755</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08758474049920016</v>
+        <v>0.0874746804091493</v>
       </c>
       <c r="C17">
-        <v>4692.041870923838</v>
+        <v>4648.352438832564</v>
       </c>
       <c r="D17">
-        <v>4826.795297527032</v>
+        <v>4839.289427209304</v>
       </c>
       <c r="E17">
-        <v>-1976.302750751427</v>
+        <v>-1920.119188977881</v>
       </c>
       <c r="F17">
-        <v>842.7534266031931</v>
+        <v>898.9369883767394</v>
       </c>
       <c r="G17">
         <v>708</v>
@@ -2687,28 +2687,28 @@
         <v>985.9625</v>
       </c>
       <c r="M17">
-        <v>63.28581420928154</v>
+        <v>67.5048684899003</v>
       </c>
       <c r="N17">
-        <v>922.6766857907185</v>
+        <v>918.4576315100996</v>
       </c>
       <c r="O17">
-        <v>313.7100731688443</v>
+        <v>312.2755947134339</v>
       </c>
       <c r="P17">
-        <v>608.9666126218742</v>
+        <v>606.1820367966657</v>
       </c>
       <c r="Q17">
-        <v>814.8666126218742</v>
+        <v>812.0820367966656</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09429461660660557</v>
+        <v>0.09469612253967244</v>
       </c>
       <c r="T17">
-        <v>0.6320474229582195</v>
+        <v>0.6372803912350073</v>
       </c>
       <c r="U17">
         <v>0.07509410488470122</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.57951829045755</v>
+        <v>14.60579839730395</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0874746804091493</v>
+        <v>0.08736462031909845</v>
       </c>
       <c r="C18">
-        <v>4648.352438832564</v>
+        <v>4604.727856558978</v>
       </c>
       <c r="D18">
-        <v>4839.289427209304</v>
+        <v>4851.848406709263</v>
       </c>
       <c r="E18">
-        <v>-1920.119188977881</v>
+        <v>-1863.935627204335</v>
       </c>
       <c r="F18">
-        <v>898.9369883767394</v>
+        <v>955.1205501502856</v>
       </c>
       <c r="G18">
         <v>708</v>
@@ -2769,28 +2769,28 @@
         <v>985.9625</v>
       </c>
       <c r="M18">
-        <v>67.5048684899003</v>
+        <v>71.72392277051908</v>
       </c>
       <c r="N18">
-        <v>918.4576315100996</v>
+        <v>914.2385772294809</v>
       </c>
       <c r="O18">
-        <v>312.2755947134339</v>
+        <v>310.8411162580235</v>
       </c>
       <c r="P18">
-        <v>606.1820367966657</v>
+        <v>603.3974609714573</v>
       </c>
       <c r="Q18">
-        <v>812.0820367966656</v>
+        <v>809.2974609714573</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09469612253967244</v>
+        <v>0.09510730331449997</v>
       </c>
       <c r="T18">
-        <v>0.6372803912350073</v>
+        <v>0.6426394551329226</v>
       </c>
       <c r="U18">
         <v>0.07509410488470122</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.60579839730395</v>
+        <v>13.74663378569784</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08736462031909845</v>
+        <v>0.08725456022904761</v>
       </c>
       <c r="C19">
-        <v>4604.727856558978</v>
+        <v>4561.168630313776</v>
       </c>
       <c r="D19">
-        <v>4851.848406709263</v>
+        <v>4864.472742237608</v>
       </c>
       <c r="E19">
-        <v>-1863.935627204335</v>
+        <v>-1807.752065430788</v>
       </c>
       <c r="F19">
-        <v>955.1205501502856</v>
+        <v>1011.304111923832</v>
       </c>
       <c r="G19">
         <v>708</v>
@@ -2851,28 +2851,28 @@
         <v>985.9625</v>
       </c>
       <c r="M19">
-        <v>71.72392277051908</v>
+        <v>75.94297705113786</v>
       </c>
       <c r="N19">
-        <v>914.2385772294809</v>
+        <v>910.0195229488621</v>
       </c>
       <c r="O19">
-        <v>310.8411162580235</v>
+        <v>309.4066378026131</v>
       </c>
       <c r="P19">
-        <v>603.3974609714573</v>
+        <v>600.612885146249</v>
       </c>
       <c r="Q19">
-        <v>809.2974609714573</v>
+        <v>806.512885146249</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09510730331449997</v>
+        <v>0.09552851288871354</v>
       </c>
       <c r="T19">
-        <v>0.6426394551329226</v>
+        <v>0.6481292279063969</v>
       </c>
       <c r="U19">
         <v>0.07509410488470122</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.74663378569784</v>
+        <v>12.98293190871462</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08725456022904762</v>
+        <v>0.08733260013899675</v>
       </c>
       <c r="C20">
-        <v>4561.168630313776</v>
+        <v>4496.026812821168</v>
       </c>
       <c r="D20">
-        <v>4864.472742237607</v>
+        <v>4855.514486518547</v>
       </c>
       <c r="E20">
-        <v>-1807.752065430788</v>
+        <v>-1751.568503657242</v>
       </c>
       <c r="F20">
-        <v>1011.304111923832</v>
+        <v>1067.487673697378</v>
       </c>
       <c r="G20">
         <v>708</v>
@@ -2933,45 +2933,45 @@
         <v>985.9625</v>
       </c>
       <c r="M20">
-        <v>75.94297705113785</v>
+        <v>81.76326284230268</v>
       </c>
       <c r="N20">
-        <v>910.0195229488621</v>
+        <v>904.1992371576973</v>
       </c>
       <c r="O20">
-        <v>309.4066378026131</v>
+        <v>307.4277406336171</v>
       </c>
       <c r="P20">
-        <v>600.612885146249</v>
+        <v>596.7714965240802</v>
       </c>
       <c r="Q20">
-        <v>806.512885146249</v>
+        <v>802.6714965240802</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09552851288871354</v>
+        <v>0.09596012269932744</v>
       </c>
       <c r="T20">
-        <v>0.6481292279063969</v>
+        <v>0.6537545506248952</v>
       </c>
       <c r="U20">
-        <v>0.07509410488470122</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V20">
         <v>0.34</v>
       </c>
       <c r="W20">
-        <v>0.0495621092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>12.98293190871462</v>
+        <v>12.05874699376457</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08733260013899675</v>
+        <v>0.08723244004894593</v>
       </c>
       <c r="C21">
-        <v>4496.026812821168</v>
+        <v>4451.346713410662</v>
       </c>
       <c r="D21">
-        <v>4855.514486518547</v>
+        <v>4867.017948881587</v>
       </c>
       <c r="E21">
-        <v>-1751.568503657242</v>
+        <v>-1695.384941883696</v>
       </c>
       <c r="F21">
-        <v>1067.487673697378</v>
+        <v>1123.671235470924</v>
       </c>
       <c r="G21">
         <v>708</v>
@@ -3015,28 +3015,28 @@
         <v>985.9625</v>
       </c>
       <c r="M21">
-        <v>81.76326284230268</v>
+        <v>86.06659246558176</v>
       </c>
       <c r="N21">
-        <v>904.1992371576973</v>
+        <v>899.8959075344183</v>
       </c>
       <c r="O21">
-        <v>307.4277406336171</v>
+        <v>305.9646085617022</v>
       </c>
       <c r="P21">
-        <v>596.7714965240802</v>
+        <v>593.931298972716</v>
       </c>
       <c r="Q21">
-        <v>802.6714965240802</v>
+        <v>799.831298972716</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09596012269932744</v>
+        <v>0.09640252275520669</v>
       </c>
       <c r="T21">
-        <v>0.6537545506248952</v>
+        <v>0.659520506411356</v>
       </c>
       <c r="U21">
         <v>0.07659410488470123</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.05874699376457</v>
+        <v>11.45580964407634</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08723244004894593</v>
+        <v>0.08713227995889508</v>
       </c>
       <c r="C22">
-        <v>4451.346713410662</v>
+        <v>4406.721250393709</v>
       </c>
       <c r="D22">
-        <v>4867.017948881587</v>
+        <v>4878.576047638179</v>
       </c>
       <c r="E22">
-        <v>-1695.384941883696</v>
+        <v>-1639.20138011015</v>
       </c>
       <c r="F22">
-        <v>1123.671235470924</v>
+        <v>1179.854797244471</v>
       </c>
       <c r="G22">
         <v>708</v>
@@ -3097,28 +3097,28 @@
         <v>985.9625</v>
       </c>
       <c r="M22">
-        <v>86.06659246558176</v>
+        <v>90.36992208886087</v>
       </c>
       <c r="N22">
-        <v>899.8959075344183</v>
+        <v>895.5925779111391</v>
       </c>
       <c r="O22">
-        <v>305.9646085617022</v>
+        <v>304.5014764897873</v>
       </c>
       <c r="P22">
-        <v>593.931298972716</v>
+        <v>591.0911014213518</v>
       </c>
       <c r="Q22">
-        <v>799.831298972716</v>
+        <v>796.9911014213518</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09640252275520669</v>
+        <v>0.09685612281250061</v>
       </c>
       <c r="T22">
-        <v>0.659520506411356</v>
+        <v>0.6654324357620309</v>
       </c>
       <c r="U22">
         <v>0.07659410488470123</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.45580964407634</v>
+        <v>10.91029489912033</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08713227995889508</v>
+        <v>0.08703211986884422</v>
       </c>
       <c r="C23">
-        <v>4406.721250393709</v>
+        <v>4362.150813945193</v>
       </c>
       <c r="D23">
-        <v>4878.576047638179</v>
+        <v>4890.18917296321</v>
       </c>
       <c r="E23">
-        <v>-1639.20138011015</v>
+        <v>-1583.017818336604</v>
       </c>
       <c r="F23">
-        <v>1179.85479724447</v>
+        <v>1236.038359018017</v>
       </c>
       <c r="G23">
         <v>708</v>
@@ -3179,28 +3179,28 @@
         <v>985.9625</v>
       </c>
       <c r="M23">
-        <v>90.36992208886086</v>
+        <v>94.67325171213994</v>
       </c>
       <c r="N23">
-        <v>895.5925779111391</v>
+        <v>891.28924828786</v>
       </c>
       <c r="O23">
-        <v>304.5014764897873</v>
+        <v>303.0383444178725</v>
       </c>
       <c r="P23">
-        <v>591.0911014213518</v>
+        <v>588.2509038699875</v>
       </c>
       <c r="Q23">
-        <v>796.9911014213518</v>
+        <v>794.1509038699875</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09685612281250061</v>
+        <v>0.09732135364049437</v>
       </c>
       <c r="T23">
-        <v>0.6654324357620308</v>
+        <v>0.6714959530447744</v>
       </c>
       <c r="U23">
         <v>0.07659410488470123</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.91029489912033</v>
+        <v>10.41437240370577</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08703211986884422</v>
+        <v>0.08693195977879337</v>
       </c>
       <c r="C24">
-        <v>4362.150813945193</v>
+        <v>4317.635797964007</v>
       </c>
       <c r="D24">
-        <v>4890.18917296321</v>
+        <v>4901.85771875557</v>
       </c>
       <c r="E24">
-        <v>-1583.017818336604</v>
+        <v>-1526.834256563057</v>
       </c>
       <c r="F24">
-        <v>1236.038359018017</v>
+        <v>1292.221920791563</v>
       </c>
       <c r="G24">
         <v>708</v>
@@ -3261,28 +3261,28 @@
         <v>985.9625</v>
       </c>
       <c r="M24">
-        <v>94.67325171213994</v>
+        <v>98.97658133541904</v>
       </c>
       <c r="N24">
-        <v>891.28924828786</v>
+        <v>886.9859186645809</v>
       </c>
       <c r="O24">
-        <v>303.0383444178725</v>
+        <v>301.5752123459575</v>
       </c>
       <c r="P24">
-        <v>588.2509038699875</v>
+        <v>585.4107063186234</v>
       </c>
       <c r="Q24">
-        <v>794.1509038699875</v>
+        <v>791.3107063186234</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09732135364049437</v>
+        <v>0.09779866838609835</v>
       </c>
       <c r="T24">
-        <v>0.6714959530447744</v>
+        <v>0.6777169642829138</v>
       </c>
       <c r="U24">
         <v>0.07659410488470123</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.41437240370577</v>
+        <v>9.961573603544645</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08693195977879337</v>
+        <v>0.08710107968874253</v>
       </c>
       <c r="C25">
-        <v>4317.635797964007</v>
+        <v>4241.782181088249</v>
       </c>
       <c r="D25">
-        <v>4901.85771875557</v>
+        <v>4882.187663653358</v>
       </c>
       <c r="E25">
-        <v>-1526.834256563057</v>
+        <v>-1470.650694789511</v>
       </c>
       <c r="F25">
-        <v>1292.221920791563</v>
+        <v>1348.405482565109</v>
       </c>
       <c r="G25">
         <v>708</v>
@@ -3343,45 +3343,45 @@
         <v>985.9625</v>
       </c>
       <c r="M25">
-        <v>98.97658133541904</v>
+        <v>105.5722002790588</v>
       </c>
       <c r="N25">
-        <v>886.9859186645809</v>
+        <v>880.3902997209411</v>
       </c>
       <c r="O25">
-        <v>301.5752123459575</v>
+        <v>299.33270190512</v>
       </c>
       <c r="P25">
-        <v>585.4107063186234</v>
+        <v>581.0575978158211</v>
       </c>
       <c r="Q25">
-        <v>791.3107063186234</v>
+        <v>786.957597815821</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09779866838609835</v>
+        <v>0.09828854404606036</v>
       </c>
       <c r="T25">
-        <v>0.6777169642829138</v>
+        <v>0.6841016863431097</v>
       </c>
       <c r="U25">
-        <v>0.07659410488470123</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V25">
         <v>0.34</v>
       </c>
       <c r="W25">
-        <v>0.0505521092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.961573603544645</v>
+        <v>9.339224695457771</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08710107968874252</v>
+        <v>0.0870121395986917</v>
       </c>
       <c r="C26">
-        <v>4241.782181088251</v>
+        <v>4195.923371530858</v>
       </c>
       <c r="D26">
-        <v>4882.18766365336</v>
+        <v>4892.512415869513</v>
       </c>
       <c r="E26">
-        <v>-1470.650694789511</v>
+        <v>-1414.467133015965</v>
       </c>
       <c r="F26">
-        <v>1348.405482565109</v>
+        <v>1404.589044338655</v>
       </c>
       <c r="G26">
         <v>708</v>
@@ -3425,28 +3425,28 @@
         <v>985.9625</v>
       </c>
       <c r="M26">
-        <v>105.5722002790588</v>
+        <v>109.9710419573529</v>
       </c>
       <c r="N26">
-        <v>880.3902997209411</v>
+        <v>875.9914580426471</v>
       </c>
       <c r="O26">
-        <v>299.33270190512</v>
+        <v>297.8370957345001</v>
       </c>
       <c r="P26">
-        <v>581.0575978158211</v>
+        <v>578.154362308147</v>
       </c>
       <c r="Q26">
-        <v>786.957597815821</v>
+        <v>784.054362308147</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09828854404606034</v>
+        <v>0.09879148305695465</v>
       </c>
       <c r="T26">
-        <v>0.6841016863431096</v>
+        <v>0.690656667658244</v>
       </c>
       <c r="U26">
         <v>0.07829410488470122</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.339224695457773</v>
+        <v>8.965655707639463</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0870121395986917</v>
+        <v>0.08692319950864083</v>
       </c>
       <c r="C27">
-        <v>4195.923371530858</v>
+        <v>4150.108323676236</v>
       </c>
       <c r="D27">
-        <v>4892.512415869513</v>
+        <v>4902.880929788437</v>
       </c>
       <c r="E27">
-        <v>-1414.467133015965</v>
+        <v>-1358.283571242419</v>
       </c>
       <c r="F27">
-        <v>1404.589044338655</v>
+        <v>1460.772606112201</v>
       </c>
       <c r="G27">
         <v>708</v>
@@ -3507,28 +3507,28 @@
         <v>985.9625</v>
       </c>
       <c r="M27">
-        <v>109.9710419573529</v>
+        <v>114.369883635647</v>
       </c>
       <c r="N27">
-        <v>875.9914580426471</v>
+        <v>871.5926163643529</v>
       </c>
       <c r="O27">
-        <v>297.8370957345001</v>
+        <v>296.34148956388</v>
       </c>
       <c r="P27">
-        <v>578.154362308147</v>
+        <v>575.2511268004729</v>
       </c>
       <c r="Q27">
-        <v>784.054362308147</v>
+        <v>781.1511268004729</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09879148305695465</v>
+        <v>0.09930801501408934</v>
       </c>
       <c r="T27">
-        <v>0.690656667658244</v>
+        <v>0.6973888106305441</v>
       </c>
       <c r="U27">
         <v>0.07829410488470122</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.965655707639463</v>
+        <v>8.620822795807175</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08692319950864083</v>
+        <v>0.08683425941858999</v>
       </c>
       <c r="C28">
-        <v>4150.108323676236</v>
+        <v>4104.337316342762</v>
       </c>
       <c r="D28">
-        <v>4902.880929788437</v>
+        <v>4913.293484228509</v>
       </c>
       <c r="E28">
-        <v>-1358.283571242419</v>
+        <v>-1302.100009468872</v>
       </c>
       <c r="F28">
-        <v>1460.772606112201</v>
+        <v>1516.956167885748</v>
       </c>
       <c r="G28">
         <v>708</v>
@@ -3589,28 +3589,28 @@
         <v>985.9625</v>
       </c>
       <c r="M28">
-        <v>114.369883635647</v>
+        <v>118.7687253139412</v>
       </c>
       <c r="N28">
-        <v>871.5926163643529</v>
+        <v>867.1937746860588</v>
       </c>
       <c r="O28">
-        <v>296.34148956388</v>
+        <v>294.84588339326</v>
       </c>
       <c r="P28">
-        <v>575.2511268004729</v>
+        <v>572.3478912927987</v>
       </c>
       <c r="Q28">
-        <v>781.1511268004729</v>
+        <v>778.2478912927987</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09930801501408934</v>
+        <v>0.09983869853169347</v>
       </c>
       <c r="T28">
-        <v>0.6973888106305441</v>
+        <v>0.7043053958760579</v>
       </c>
       <c r="U28">
         <v>0.07829410488470122</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.620822795807175</v>
+        <v>8.301533062629129</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08683425941858999</v>
+        <v>0.08674531932853916</v>
       </c>
       <c r="C29">
-        <v>4104.337316342762</v>
+        <v>4058.610630722438</v>
       </c>
       <c r="D29">
-        <v>4913.293484228509</v>
+        <v>4923.750360381732</v>
       </c>
       <c r="E29">
-        <v>-1302.100009468872</v>
+        <v>-1245.916447695326</v>
       </c>
       <c r="F29">
-        <v>1516.956167885748</v>
+        <v>1573.139729659294</v>
       </c>
       <c r="G29">
         <v>708</v>
@@ -3671,28 +3671,28 @@
         <v>985.9625</v>
       </c>
       <c r="M29">
-        <v>118.7687253139412</v>
+        <v>123.1675669922353</v>
       </c>
       <c r="N29">
-        <v>867.1937746860588</v>
+        <v>862.7949330077647</v>
       </c>
       <c r="O29">
-        <v>294.84588339326</v>
+        <v>293.35027722264</v>
       </c>
       <c r="P29">
-        <v>572.3478912927987</v>
+        <v>569.4446557851247</v>
       </c>
       <c r="Q29">
-        <v>778.2478912927987</v>
+        <v>775.3446557851247</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09983869853169347</v>
+        <v>0.10038412325812</v>
       </c>
       <c r="T29">
-        <v>0.7043053958760579</v>
+        <v>0.7114141084895027</v>
       </c>
       <c r="U29">
         <v>0.07829410488470122</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.301533062629129</v>
+        <v>8.005049738963805</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08674531932853916</v>
+        <v>0.0866563792384883</v>
       </c>
       <c r="C30">
-        <v>4058.610630722438</v>
+        <v>4012.928550406199</v>
       </c>
       <c r="D30">
-        <v>4923.750360381732</v>
+        <v>4934.251841839039</v>
       </c>
       <c r="E30">
-        <v>-1245.916447695326</v>
+        <v>-1189.73288592178</v>
       </c>
       <c r="F30">
-        <v>1573.139729659294</v>
+        <v>1629.32329143284</v>
       </c>
       <c r="G30">
         <v>708</v>
@@ -3753,28 +3753,28 @@
         <v>985.9625</v>
       </c>
       <c r="M30">
-        <v>123.1675669922353</v>
+        <v>127.5664086705294</v>
       </c>
       <c r="N30">
-        <v>862.7949330077647</v>
+        <v>858.3960913294706</v>
       </c>
       <c r="O30">
-        <v>293.35027722264</v>
+        <v>291.85467105202</v>
       </c>
       <c r="P30">
-        <v>569.4446557851247</v>
+        <v>566.5414202774505</v>
       </c>
       <c r="Q30">
-        <v>775.3446557851247</v>
+        <v>772.4414202774504</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.10038412325812</v>
+        <v>0.1009449120613472</v>
       </c>
       <c r="T30">
-        <v>0.7114141084895027</v>
+        <v>0.7187230665286783</v>
       </c>
       <c r="U30">
         <v>0.07829410488470122</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.005049738963805</v>
+        <v>7.7290135410685</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0866563792384883</v>
+        <v>0.08672583914843746</v>
       </c>
       <c r="C31">
-        <v>4012.928550406199</v>
+        <v>3948.539778379127</v>
       </c>
       <c r="D31">
-        <v>4934.251841839039</v>
+        <v>4926.046631585513</v>
       </c>
       <c r="E31">
-        <v>-1189.73288592178</v>
+        <v>-1133.549324148234</v>
       </c>
       <c r="F31">
-        <v>1629.32329143284</v>
+        <v>1685.506853206386</v>
       </c>
       <c r="G31">
         <v>708</v>
@@ -3835,45 +3835,45 @@
         <v>985.9625</v>
       </c>
       <c r="M31">
-        <v>127.5664086705294</v>
+        <v>133.3136558313886</v>
       </c>
       <c r="N31">
-        <v>858.3960913294707</v>
+        <v>852.6488441686113</v>
       </c>
       <c r="O31">
-        <v>291.85467105202</v>
+        <v>289.9006070173278</v>
       </c>
       <c r="P31">
-        <v>566.5414202774507</v>
+        <v>562.7482371512834</v>
       </c>
       <c r="Q31">
-        <v>772.4414202774507</v>
+        <v>768.6482371512834</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1009449120613472</v>
+        <v>0.1015217234018095</v>
       </c>
       <c r="T31">
-        <v>0.7187230665286783</v>
+        <v>0.7262408519404019</v>
       </c>
       <c r="U31">
-        <v>0.07829410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V31">
         <v>0.34</v>
       </c>
       <c r="W31">
-        <v>0.05167410922390279</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.729013541068503</v>
+        <v>7.395810233026822</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08672583914843746</v>
+        <v>0.08664217905838661</v>
       </c>
       <c r="C32">
-        <v>3948.539778379127</v>
+        <v>3902.242242411398</v>
       </c>
       <c r="D32">
-        <v>4926.046631585513</v>
+        <v>4935.93265739133</v>
       </c>
       <c r="E32">
-        <v>-1133.549324148234</v>
+        <v>-1077.365762374688</v>
       </c>
       <c r="F32">
-        <v>1685.506853206386</v>
+        <v>1741.690414979932</v>
       </c>
       <c r="G32">
         <v>708</v>
@@ -3917,28 +3917,28 @@
         <v>985.9625</v>
       </c>
       <c r="M32">
-        <v>133.3136558313886</v>
+        <v>137.7574443591016</v>
       </c>
       <c r="N32">
-        <v>852.6488441686113</v>
+        <v>848.2050556408984</v>
       </c>
       <c r="O32">
-        <v>289.9006070173278</v>
+        <v>288.3897189179055</v>
       </c>
       <c r="P32">
-        <v>562.7482371512834</v>
+        <v>559.8153367229929</v>
       </c>
       <c r="Q32">
-        <v>768.6482371512834</v>
+        <v>765.7153367229929</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1015217234018095</v>
+        <v>0.1021152539115605</v>
       </c>
       <c r="T32">
-        <v>0.7262408519404019</v>
+        <v>0.7339765441756535</v>
       </c>
       <c r="U32">
         <v>0.07909410488470123</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.395810233026822</v>
+        <v>7.157235709380797</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08664217905838661</v>
+        <v>0.08655851896833577</v>
       </c>
       <c r="C33">
-        <v>3902.242242411398</v>
+        <v>3855.984466538617</v>
       </c>
       <c r="D33">
-        <v>4935.93265739133</v>
+        <v>4945.858443292096</v>
       </c>
       <c r="E33">
-        <v>-1077.365762374688</v>
+        <v>-1021.182200601141</v>
       </c>
       <c r="F33">
-        <v>1741.690414979932</v>
+        <v>1797.873976753479</v>
       </c>
       <c r="G33">
         <v>708</v>
@@ -3999,28 +3999,28 @@
         <v>985.9625</v>
       </c>
       <c r="M33">
-        <v>137.7574443591016</v>
+        <v>142.2012328868146</v>
       </c>
       <c r="N33">
-        <v>848.2050556408984</v>
+        <v>843.7612671131855</v>
       </c>
       <c r="O33">
-        <v>288.3897189179055</v>
+        <v>286.8788308184831</v>
       </c>
       <c r="P33">
-        <v>559.8153367229929</v>
+        <v>556.8824362947023</v>
       </c>
       <c r="Q33">
-        <v>765.7153367229929</v>
+        <v>762.7824362947023</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1021152539115605</v>
+        <v>0.1027262412010101</v>
       </c>
       <c r="T33">
-        <v>0.7339765441756535</v>
+        <v>0.7419397567707655</v>
       </c>
       <c r="U33">
         <v>0.07909410488470123</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.157235709380797</v>
+        <v>6.933572093462645</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08655851896833577</v>
+        <v>0.08647485887828492</v>
       </c>
       <c r="C34">
-        <v>3855.984466538617</v>
+        <v>3809.766691107706</v>
       </c>
       <c r="D34">
-        <v>4945.858443292096</v>
+        <v>4955.824229634731</v>
       </c>
       <c r="E34">
-        <v>-1021.182200601141</v>
+        <v>-964.9986388275952</v>
       </c>
       <c r="F34">
-        <v>1797.873976753479</v>
+        <v>1854.057538527025</v>
       </c>
       <c r="G34">
         <v>708</v>
@@ -4081,28 +4081,28 @@
         <v>985.9625</v>
       </c>
       <c r="M34">
-        <v>142.2012328868146</v>
+        <v>146.6450214145275</v>
       </c>
       <c r="N34">
-        <v>843.7612671131855</v>
+        <v>839.3174785854725</v>
       </c>
       <c r="O34">
-        <v>286.8788308184831</v>
+        <v>285.3679427190607</v>
       </c>
       <c r="P34">
-        <v>556.8824362947023</v>
+        <v>553.9495358664118</v>
       </c>
       <c r="Q34">
-        <v>762.7824362947023</v>
+        <v>759.8495358664118</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1027262412010101</v>
+        <v>0.1033554669170104</v>
       </c>
       <c r="T34">
-        <v>0.7419397567707655</v>
+        <v>0.7501406772045376</v>
       </c>
       <c r="U34">
         <v>0.07909410488470123</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.933572093462645</v>
+        <v>6.723463848206203</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08647485887828492</v>
+        <v>0.08639119878823408</v>
       </c>
       <c r="C35">
-        <v>3809.766691107706</v>
+        <v>3763.58915840666</v>
       </c>
       <c r="D35">
-        <v>4955.824229634731</v>
+        <v>4965.830258707231</v>
       </c>
       <c r="E35">
-        <v>-964.9986388275952</v>
+        <v>-908.815077054049</v>
       </c>
       <c r="F35">
-        <v>1854.057538527025</v>
+        <v>1910.241100300571</v>
       </c>
       <c r="G35">
         <v>708</v>
@@ -4163,28 +4163,28 @@
         <v>985.9625</v>
       </c>
       <c r="M35">
-        <v>146.6450214145275</v>
+        <v>151.0888099422405</v>
       </c>
       <c r="N35">
-        <v>839.3174785854725</v>
+        <v>834.8736900577595</v>
       </c>
       <c r="O35">
-        <v>285.3679427190607</v>
+        <v>283.8570546196382</v>
       </c>
       <c r="P35">
-        <v>553.9495358664118</v>
+        <v>551.0166354381213</v>
       </c>
       <c r="Q35">
-        <v>759.8495358664118</v>
+        <v>756.9166354381213</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1033554669170104</v>
+        <v>0.1040037600789502</v>
       </c>
       <c r="T35">
-        <v>0.7501406772045376</v>
+        <v>0.7585901103787271</v>
       </c>
       <c r="U35">
         <v>0.07909410488470123</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.723463848206203</v>
+        <v>6.525714911494255</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08639119878823408</v>
+        <v>0.08630753869818324</v>
       </c>
       <c r="C36">
-        <v>3763.58915840666</v>
+        <v>3717.452112684205</v>
       </c>
       <c r="D36">
-        <v>4965.830258707231</v>
+        <v>4975.876774758322</v>
       </c>
       <c r="E36">
-        <v>-908.815077054049</v>
+        <v>-852.6315152805028</v>
       </c>
       <c r="F36">
-        <v>1910.241100300571</v>
+        <v>1966.424662074117</v>
       </c>
       <c r="G36">
         <v>708</v>
@@ -4245,28 +4245,28 @@
         <v>985.9625</v>
       </c>
       <c r="M36">
-        <v>151.0888099422405</v>
+        <v>155.5325984699534</v>
       </c>
       <c r="N36">
-        <v>834.8736900577595</v>
+        <v>830.4299015300465</v>
       </c>
       <c r="O36">
-        <v>283.8570546196382</v>
+        <v>282.3461665202158</v>
       </c>
       <c r="P36">
-        <v>551.0166354381213</v>
+        <v>548.0837350098307</v>
       </c>
       <c r="Q36">
-        <v>756.9166354381213</v>
+        <v>753.9837350098306</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1040037600789502</v>
+        <v>0.1046720007227958</v>
       </c>
       <c r="T36">
-        <v>0.7585901103787271</v>
+        <v>0.7672995261121224</v>
       </c>
       <c r="U36">
         <v>0.07909410488470123</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.525714911494255</v>
+        <v>6.339265914022991</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08630753869818324</v>
+        <v>0.08622387860813238</v>
       </c>
       <c r="C37">
-        <v>3717.452112684205</v>
+        <v>3671.355800169658</v>
       </c>
       <c r="D37">
-        <v>4975.876774758322</v>
+        <v>4985.964024017322</v>
       </c>
       <c r="E37">
-        <v>-852.6315152805028</v>
+        <v>-796.4479535069563</v>
       </c>
       <c r="F37">
-        <v>1966.424662074117</v>
+        <v>2022.608223847664</v>
       </c>
       <c r="G37">
         <v>708</v>
@@ -4327,28 +4327,28 @@
         <v>985.9625</v>
       </c>
       <c r="M37">
-        <v>155.5325984699534</v>
+        <v>159.9763869976664</v>
       </c>
       <c r="N37">
-        <v>830.4299015300465</v>
+        <v>825.9861130023336</v>
       </c>
       <c r="O37">
-        <v>282.3461665202158</v>
+        <v>280.8352784207934</v>
       </c>
       <c r="P37">
-        <v>548.0837350098307</v>
+        <v>545.1508345815402</v>
       </c>
       <c r="Q37">
-        <v>753.9837350098306</v>
+        <v>751.0508345815401</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1046720007227958</v>
+        <v>0.1053611238867615</v>
       </c>
       <c r="T37">
-        <v>0.7672995261121224</v>
+        <v>0.7762811110871862</v>
       </c>
       <c r="U37">
         <v>0.07909410488470123</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.339265914022991</v>
+        <v>6.163175194189018</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08622387860813238</v>
+        <v>0.08638441851808154</v>
       </c>
       <c r="C38">
-        <v>3671.355800169659</v>
+        <v>3595.851186593749</v>
       </c>
       <c r="D38">
-        <v>4985.964024017322</v>
+        <v>4966.642972214959</v>
       </c>
       <c r="E38">
-        <v>-796.4479535069568</v>
+        <v>-740.2643917334103</v>
       </c>
       <c r="F38">
-        <v>2022.608223847663</v>
+        <v>2078.79178562121</v>
       </c>
       <c r="G38">
         <v>708</v>
@@ -4409,45 +4409,45 @@
         <v>985.9625</v>
       </c>
       <c r="M38">
-        <v>159.9763869976663</v>
+        <v>166.4989673110005</v>
       </c>
       <c r="N38">
-        <v>825.9861130023337</v>
+        <v>819.4635326889995</v>
       </c>
       <c r="O38">
-        <v>280.8352784207935</v>
+        <v>278.6176011142599</v>
       </c>
       <c r="P38">
-        <v>545.1508345815403</v>
+        <v>540.8459315747397</v>
       </c>
       <c r="Q38">
-        <v>751.0508345815402</v>
+        <v>746.7459315747396</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1053611238867615</v>
+        <v>0.1060721239765675</v>
       </c>
       <c r="T38">
-        <v>0.7762811110871861</v>
+        <v>0.7855478257439981</v>
       </c>
       <c r="U38">
-        <v>0.07909410488470123</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V38">
         <v>0.34</v>
       </c>
       <c r="W38">
-        <v>0.0522021092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.16317519418902</v>
+        <v>5.921733425279077</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08638441851808154</v>
+        <v>0.08630735842803071</v>
       </c>
       <c r="C39">
-        <v>3595.851186593749</v>
+        <v>3548.923119414746</v>
       </c>
       <c r="D39">
-        <v>4966.642972214959</v>
+        <v>4975.898466809502</v>
       </c>
       <c r="E39">
-        <v>-740.2643917334103</v>
+        <v>-684.0808299598643</v>
       </c>
       <c r="F39">
-        <v>2078.79178562121</v>
+        <v>2134.975347394756</v>
       </c>
       <c r="G39">
         <v>708</v>
@@ -4491,28 +4491,28 @@
         <v>985.9625</v>
       </c>
       <c r="M39">
-        <v>166.4989673110005</v>
+        <v>170.998939400487</v>
       </c>
       <c r="N39">
-        <v>819.4635326889995</v>
+        <v>814.9635605995129</v>
       </c>
       <c r="O39">
-        <v>278.6176011142599</v>
+        <v>277.0876106038344</v>
       </c>
       <c r="P39">
-        <v>540.8459315747397</v>
+        <v>537.8759499956784</v>
       </c>
       <c r="Q39">
-        <v>746.7459315747396</v>
+        <v>743.7759499956784</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1060721239765675</v>
+        <v>0.1068060595531413</v>
       </c>
       <c r="T39">
-        <v>0.7855478257439981</v>
+        <v>0.795113466680062</v>
       </c>
       <c r="U39">
         <v>0.08009410488470123</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.921733425279077</v>
+        <v>5.765898335140152</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08630735842803071</v>
+        <v>0.08623029833797985</v>
       </c>
       <c r="C40">
-        <v>3548.923119414746</v>
+        <v>3502.02961244738</v>
       </c>
       <c r="D40">
-        <v>4975.898466809502</v>
+        <v>4985.188521615682</v>
       </c>
       <c r="E40">
-        <v>-684.0808299598643</v>
+        <v>-627.8972681863179</v>
       </c>
       <c r="F40">
-        <v>2134.975347394756</v>
+        <v>2191.158909168302</v>
       </c>
       <c r="G40">
         <v>708</v>
@@ -4573,28 +4573,28 @@
         <v>985.9625</v>
       </c>
       <c r="M40">
-        <v>170.998939400487</v>
+        <v>175.4989114899735</v>
       </c>
       <c r="N40">
-        <v>814.9635605995129</v>
+        <v>810.4635885100265</v>
       </c>
       <c r="O40">
-        <v>277.0876106038344</v>
+        <v>275.557620093409</v>
       </c>
       <c r="P40">
-        <v>537.8759499956784</v>
+        <v>534.9059684166175</v>
       </c>
       <c r="Q40">
-        <v>743.7759499956784</v>
+        <v>740.8059684166175</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1068060595531413</v>
+        <v>0.1075640585912422</v>
       </c>
       <c r="T40">
-        <v>0.795113466680062</v>
+        <v>0.8049927351878001</v>
       </c>
       <c r="U40">
         <v>0.08009410488470123</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.765898335140152</v>
+        <v>5.618054788085277</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08623029833797985</v>
+        <v>0.086153238247929</v>
       </c>
       <c r="C41">
-        <v>3502.02961244738</v>
+        <v>3455.170859626562</v>
       </c>
       <c r="D41">
-        <v>4985.188521615682</v>
+        <v>4994.51333056841</v>
       </c>
       <c r="E41">
-        <v>-627.8972681863179</v>
+        <v>-571.7137064127719</v>
       </c>
       <c r="F41">
-        <v>2191.158909168302</v>
+        <v>2247.342470941848</v>
       </c>
       <c r="G41">
         <v>708</v>
@@ -4655,28 +4655,28 @@
         <v>985.9625</v>
       </c>
       <c r="M41">
-        <v>175.4989114899735</v>
+        <v>179.99888357946</v>
       </c>
       <c r="N41">
-        <v>810.4635885100265</v>
+        <v>805.96361642054</v>
       </c>
       <c r="O41">
-        <v>275.557620093409</v>
+        <v>274.0276295829836</v>
       </c>
       <c r="P41">
-        <v>534.9059684166175</v>
+        <v>531.9359868375564</v>
       </c>
       <c r="Q41">
-        <v>740.8059684166175</v>
+        <v>737.8359868375563</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1075640585912422</v>
+        <v>0.1083473242639465</v>
       </c>
       <c r="T41">
-        <v>0.8049927351878001</v>
+        <v>0.8152013126457962</v>
       </c>
       <c r="U41">
         <v>0.08009410488470123</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.618054788085277</v>
+        <v>5.477603418383146</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.086153238247929</v>
+        <v>0.08607617815787816</v>
       </c>
       <c r="C42">
-        <v>3455.170859626562</v>
+        <v>3408.34705634095</v>
       </c>
       <c r="D42">
-        <v>4994.51333056841</v>
+        <v>5003.873089056345</v>
       </c>
       <c r="E42">
-        <v>-571.7137064127719</v>
+        <v>-515.5301446392255</v>
       </c>
       <c r="F42">
-        <v>2247.342470941848</v>
+        <v>2303.526032715395</v>
       </c>
       <c r="G42">
         <v>708</v>
@@ -4737,28 +4737,28 @@
         <v>985.9625</v>
       </c>
       <c r="M42">
-        <v>179.99888357946</v>
+        <v>184.4988556689465</v>
       </c>
       <c r="N42">
-        <v>805.96361642054</v>
+        <v>801.4636443310535</v>
       </c>
       <c r="O42">
-        <v>274.0276295829836</v>
+        <v>272.4976390725582</v>
       </c>
       <c r="P42">
-        <v>531.9359868375564</v>
+        <v>528.9660052584952</v>
       </c>
       <c r="Q42">
-        <v>737.8359868375563</v>
+        <v>734.8660052584952</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1083473242639465</v>
+        <v>0.1091571413153865</v>
       </c>
       <c r="T42">
-        <v>0.8152013126457962</v>
+        <v>0.8257559435769447</v>
       </c>
       <c r="U42">
         <v>0.08009410488470123</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.477603418383146</v>
+        <v>5.344003335007947</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08607617815787816</v>
+        <v>0.08599911806782731</v>
       </c>
       <c r="C43">
-        <v>3408.34705634095</v>
+        <v>3361.558399446592</v>
       </c>
       <c r="D43">
-        <v>5003.873089056345</v>
+        <v>5013.267993935533</v>
       </c>
       <c r="E43">
-        <v>-515.5301446392255</v>
+        <v>-459.346582865679</v>
       </c>
       <c r="F43">
-        <v>2303.526032715395</v>
+        <v>2359.709594488941</v>
       </c>
       <c r="G43">
         <v>708</v>
@@ -4819,28 +4819,28 @@
         <v>985.9625</v>
       </c>
       <c r="M43">
-        <v>184.4988556689465</v>
+        <v>188.998827758433</v>
       </c>
       <c r="N43">
-        <v>801.4636443310535</v>
+        <v>796.9636722415669</v>
       </c>
       <c r="O43">
-        <v>272.4976390725582</v>
+        <v>270.9676485621328</v>
       </c>
       <c r="P43">
-        <v>528.9660052584952</v>
+        <v>525.9960236794341</v>
       </c>
       <c r="Q43">
-        <v>734.8660052584952</v>
+        <v>731.8960236794341</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1091571413153865</v>
+        <v>0.1099948830927382</v>
       </c>
       <c r="T43">
-        <v>0.8257559435769447</v>
+        <v>0.8366745272988225</v>
       </c>
       <c r="U43">
         <v>0.08009410488470123</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.344003335007947</v>
+        <v>5.2167651603649</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08599911806782731</v>
+        <v>0.08592205797777647</v>
       </c>
       <c r="C44">
-        <v>3361.558399446592</v>
+        <v>3314.805087280727</v>
       </c>
       <c r="D44">
-        <v>5013.267993935533</v>
+        <v>5022.698243543214</v>
       </c>
       <c r="E44">
-        <v>-459.3465828656795</v>
+        <v>-403.163021092133</v>
       </c>
       <c r="F44">
-        <v>2359.709594488941</v>
+        <v>2415.893156262487</v>
       </c>
       <c r="G44">
         <v>708</v>
@@ -4901,28 +4901,28 @@
         <v>985.9625</v>
       </c>
       <c r="M44">
-        <v>188.998827758433</v>
+        <v>193.4987998479195</v>
       </c>
       <c r="N44">
-        <v>796.963672241567</v>
+        <v>792.4637001520805</v>
       </c>
       <c r="O44">
-        <v>270.9676485621328</v>
+        <v>269.4376580517074</v>
       </c>
       <c r="P44">
-        <v>525.9960236794342</v>
+        <v>523.0260421003732</v>
       </c>
       <c r="Q44">
-        <v>731.8960236794342</v>
+        <v>728.9260421003731</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1099948830927382</v>
+        <v>0.110862019318418</v>
       </c>
       <c r="T44">
-        <v>0.8366745272988224</v>
+        <v>0.8479762192214678</v>
       </c>
       <c r="U44">
         <v>0.08009410488470123</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.216765160364901</v>
+        <v>5.095445040356414</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08592205797777647</v>
+        <v>0.08584499788772562</v>
       </c>
       <c r="C45">
-        <v>3314.805087280727</v>
+        <v>3268.08731967574</v>
       </c>
       <c r="D45">
-        <v>5022.698243543214</v>
+        <v>5032.164037711773</v>
       </c>
       <c r="E45">
-        <v>-403.163021092133</v>
+        <v>-346.979459318587</v>
       </c>
       <c r="F45">
-        <v>2415.893156262487</v>
+        <v>2472.076718036033</v>
       </c>
       <c r="G45">
         <v>708</v>
@@ -4983,28 +4983,28 @@
         <v>985.9625</v>
       </c>
       <c r="M45">
-        <v>193.4987998479195</v>
+        <v>197.998771937406</v>
       </c>
       <c r="N45">
-        <v>792.4637001520805</v>
+        <v>787.963728062594</v>
       </c>
       <c r="O45">
-        <v>269.4376580517074</v>
+        <v>267.907667541282</v>
       </c>
       <c r="P45">
-        <v>523.0260421003732</v>
+        <v>520.056060521312</v>
       </c>
       <c r="Q45">
-        <v>728.9260421003731</v>
+        <v>725.956060521312</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.110862019318418</v>
+        <v>0.111760124695015</v>
       </c>
       <c r="T45">
-        <v>0.8479762192214678</v>
+        <v>0.8596815429984934</v>
       </c>
       <c r="U45">
         <v>0.08009410488470123</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.095445040356414</v>
+        <v>4.979639471257405</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08584499788772562</v>
+        <v>0.08576793779767479</v>
       </c>
       <c r="C46">
-        <v>3268.08731967574</v>
+        <v>3221.405297973276</v>
       </c>
       <c r="D46">
-        <v>5032.164037711773</v>
+        <v>5041.665577782856</v>
       </c>
       <c r="E46">
-        <v>-346.979459318587</v>
+        <v>-290.7958975450406</v>
       </c>
       <c r="F46">
-        <v>2472.076718036033</v>
+        <v>2528.26027980958</v>
       </c>
       <c r="G46">
         <v>708</v>
@@ -5065,28 +5065,28 @@
         <v>985.9625</v>
       </c>
       <c r="M46">
-        <v>197.998771937406</v>
+        <v>202.4987440268925</v>
       </c>
       <c r="N46">
-        <v>787.963728062594</v>
+        <v>783.4637559731075</v>
       </c>
       <c r="O46">
-        <v>267.907667541282</v>
+        <v>266.3776770308565</v>
       </c>
       <c r="P46">
-        <v>520.056060521312</v>
+        <v>517.0860789422509</v>
       </c>
       <c r="Q46">
-        <v>725.956060521312</v>
+        <v>722.9860789422509</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.111760124695015</v>
+        <v>0.1126908884489428</v>
       </c>
       <c r="T46">
-        <v>0.8596815429984934</v>
+        <v>0.8718125149128655</v>
       </c>
       <c r="U46">
         <v>0.08009410488470123</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.979639471257405</v>
+        <v>4.868980816340573</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08576793779767479</v>
+        <v>0.08569087770762393</v>
       </c>
       <c r="C47">
-        <v>3221.405297973276</v>
+        <v>3174.759225038533</v>
       </c>
       <c r="D47">
-        <v>5041.665577782856</v>
+        <v>5051.203066621659</v>
       </c>
       <c r="E47">
-        <v>-290.7958975450406</v>
+        <v>-234.6123357714946</v>
       </c>
       <c r="F47">
-        <v>2528.26027980958</v>
+        <v>2584.443841583126</v>
       </c>
       <c r="G47">
         <v>708</v>
@@ -5147,28 +5147,28 @@
         <v>985.9625</v>
       </c>
       <c r="M47">
-        <v>202.4987440268925</v>
+        <v>206.998716116379</v>
       </c>
       <c r="N47">
-        <v>783.4637559731075</v>
+        <v>778.963783883621</v>
       </c>
       <c r="O47">
-        <v>266.3776770308565</v>
+        <v>264.8476865204311</v>
       </c>
       <c r="P47">
-        <v>517.0860789422509</v>
+        <v>514.1160973631899</v>
       </c>
       <c r="Q47">
-        <v>722.9860789422509</v>
+        <v>720.0160973631898</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1126908884489428</v>
+        <v>0.1136561249344975</v>
       </c>
       <c r="T47">
-        <v>0.8718125149128655</v>
+        <v>0.8843927820833252</v>
       </c>
       <c r="U47">
         <v>0.08009410488470123</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.868980816340573</v>
+        <v>4.763133407289692</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08569087770762393</v>
+        <v>0.0856138176175731</v>
       </c>
       <c r="C48">
-        <v>3174.759225038533</v>
+        <v>3128.14930527467</v>
       </c>
       <c r="D48">
-        <v>5051.203066621659</v>
+        <v>5060.776708631342</v>
       </c>
       <c r="E48">
-        <v>-234.6123357714946</v>
+        <v>-178.4287739979482</v>
       </c>
       <c r="F48">
-        <v>2584.443841583126</v>
+        <v>2640.627403356672</v>
       </c>
       <c r="G48">
         <v>708</v>
@@ -5229,28 +5229,28 @@
         <v>985.9625</v>
       </c>
       <c r="M48">
-        <v>206.998716116379</v>
+        <v>211.4986882058655</v>
       </c>
       <c r="N48">
-        <v>778.963783883621</v>
+        <v>774.4638117941345</v>
       </c>
       <c r="O48">
-        <v>264.8476865204311</v>
+        <v>263.3176960100058</v>
       </c>
       <c r="P48">
-        <v>514.1160973631899</v>
+        <v>511.1461157841287</v>
       </c>
       <c r="Q48">
-        <v>720.0160973631898</v>
+        <v>717.0461157841287</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1136561249344975</v>
+        <v>0.114657785438375</v>
       </c>
       <c r="T48">
-        <v>0.8843927820833252</v>
+        <v>0.8974477763168213</v>
       </c>
       <c r="U48">
         <v>0.08009410488470123</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.763133407289692</v>
+        <v>4.661790143304804</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0856138176175731</v>
+        <v>0.08553675752752224</v>
       </c>
       <c r="C49">
-        <v>3128.14930527467</v>
+        <v>3081.575744637437</v>
       </c>
       <c r="D49">
-        <v>5060.776708631342</v>
+        <v>5070.386709767656</v>
       </c>
       <c r="E49">
-        <v>-178.4287739979482</v>
+        <v>-122.2452122244017</v>
       </c>
       <c r="F49">
-        <v>2640.627403356672</v>
+        <v>2696.810965130218</v>
       </c>
       <c r="G49">
         <v>708</v>
@@ -5311,28 +5311,28 @@
         <v>985.9625</v>
       </c>
       <c r="M49">
-        <v>211.4986882058655</v>
+        <v>215.9986602953521</v>
       </c>
       <c r="N49">
-        <v>774.4638117941345</v>
+        <v>769.9638397046479</v>
       </c>
       <c r="O49">
-        <v>263.3176960100058</v>
+        <v>261.7877054995803</v>
       </c>
       <c r="P49">
-        <v>511.1461157841287</v>
+        <v>508.1761342050676</v>
       </c>
       <c r="Q49">
-        <v>717.0461157841287</v>
+        <v>714.0761342050675</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.114657785438375</v>
+        <v>0.1156979713462479</v>
       </c>
       <c r="T49">
-        <v>0.8974477763168213</v>
+        <v>0.9110048857131441</v>
       </c>
       <c r="U49">
         <v>0.08009410488470123</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.661790143304804</v>
+        <v>4.564669515319286</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08553675752752224</v>
+        <v>0.0862681974374714</v>
       </c>
       <c r="C50">
-        <v>3081.575744637438</v>
+        <v>2935.620700549124</v>
       </c>
       <c r="D50">
-        <v>5070.386709767656</v>
+        <v>4980.615227452888</v>
       </c>
       <c r="E50">
-        <v>-122.2452122244022</v>
+        <v>-66.06165045085618</v>
       </c>
       <c r="F50">
-        <v>2696.810965130218</v>
+        <v>2752.994526903764</v>
       </c>
       <c r="G50">
         <v>708</v>
@@ -5393,45 +5393,45 @@
         <v>985.9625</v>
       </c>
       <c r="M50">
-        <v>215.998660295352</v>
+        <v>227.3811187020979</v>
       </c>
       <c r="N50">
-        <v>769.963839704648</v>
+        <v>758.581381297902</v>
       </c>
       <c r="O50">
-        <v>261.7877054995803</v>
+        <v>257.9176696412867</v>
       </c>
       <c r="P50">
-        <v>508.1761342050676</v>
+        <v>500.6637116566153</v>
       </c>
       <c r="Q50">
-        <v>714.0761342050675</v>
+        <v>706.5637116566153</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1156979713462479</v>
+        <v>0.116778948858351</v>
       </c>
       <c r="T50">
-        <v>0.911004885713144</v>
+        <v>0.9250936464583422</v>
       </c>
       <c r="U50">
-        <v>0.08009410488470123</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V50">
         <v>0.34</v>
       </c>
       <c r="W50">
-        <v>0.0528621092239028</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.564669515319288</v>
+        <v>4.336166985314875</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0862681974374714</v>
+        <v>0.08620763734742054</v>
       </c>
       <c r="C51">
-        <v>2935.620700549124</v>
+        <v>2886.748954952172</v>
       </c>
       <c r="D51">
-        <v>4980.615227452888</v>
+        <v>4987.927043629482</v>
       </c>
       <c r="E51">
-        <v>-66.06165045085618</v>
+        <v>-9.878088677309734</v>
       </c>
       <c r="F51">
-        <v>2752.994526903764</v>
+        <v>2809.17808867731</v>
       </c>
       <c r="G51">
         <v>708</v>
@@ -5475,28 +5475,28 @@
         <v>985.9625</v>
       </c>
       <c r="M51">
-        <v>227.3811187020979</v>
+        <v>232.0215496960183</v>
       </c>
       <c r="N51">
-        <v>758.581381297902</v>
+        <v>753.9409503039817</v>
       </c>
       <c r="O51">
-        <v>257.9176696412867</v>
+        <v>256.3399231033538</v>
       </c>
       <c r="P51">
-        <v>500.6637116566153</v>
+        <v>497.6010272006279</v>
       </c>
       <c r="Q51">
-        <v>706.5637116566153</v>
+        <v>703.501027200628</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.116778948858351</v>
+        <v>0.1179031654709383</v>
       </c>
       <c r="T51">
-        <v>0.9250936464583422</v>
+        <v>0.9397459576333483</v>
       </c>
       <c r="U51">
         <v>0.08259410488470123</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.336166985314875</v>
+        <v>4.249443645608579</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08620763734742054</v>
+        <v>0.0861470772573697</v>
       </c>
       <c r="C52">
-        <v>2886.748954952172</v>
+        <v>2837.898709212105</v>
       </c>
       <c r="D52">
-        <v>4987.927043629482</v>
+        <v>4995.260359662961</v>
       </c>
       <c r="E52">
-        <v>-9.878088677309734</v>
+        <v>46.30547309623671</v>
       </c>
       <c r="F52">
-        <v>2809.17808867731</v>
+        <v>2865.361650450857</v>
       </c>
       <c r="G52">
         <v>708</v>
@@ -5557,28 +5557,28 @@
         <v>985.9625</v>
       </c>
       <c r="M52">
-        <v>232.0215496960183</v>
+        <v>236.6619806899387</v>
       </c>
       <c r="N52">
-        <v>753.9409503039817</v>
+        <v>749.3005193100613</v>
       </c>
       <c r="O52">
-        <v>256.3399231033538</v>
+        <v>254.7621765654209</v>
       </c>
       <c r="P52">
-        <v>497.6010272006279</v>
+        <v>494.5383427446404</v>
       </c>
       <c r="Q52">
-        <v>703.501027200628</v>
+        <v>700.4383427446404</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1179031654709383</v>
+        <v>0.1190732684758761</v>
       </c>
       <c r="T52">
-        <v>0.9397459576333483</v>
+        <v>0.9549963223257018</v>
       </c>
       <c r="U52">
         <v>0.08259410488470123</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.249443645608579</v>
+        <v>4.166121221184881</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0861470772573697</v>
+        <v>0.08608651716731885</v>
       </c>
       <c r="C53">
-        <v>2837.898709212105</v>
+        <v>2789.070058296668</v>
       </c>
       <c r="D53">
-        <v>4995.260359662961</v>
+        <v>5002.615270521071</v>
       </c>
       <c r="E53">
-        <v>46.30547309623671</v>
+        <v>102.4890348697827</v>
       </c>
       <c r="F53">
-        <v>2865.361650450857</v>
+        <v>2921.545212224403</v>
       </c>
       <c r="G53">
         <v>708</v>
@@ -5639,28 +5639,28 @@
         <v>985.9625</v>
       </c>
       <c r="M53">
-        <v>236.6619806899387</v>
+        <v>241.302411683859</v>
       </c>
       <c r="N53">
-        <v>749.3005193100613</v>
+        <v>744.6600883161409</v>
       </c>
       <c r="O53">
-        <v>254.7621765654209</v>
+        <v>253.1844300274879</v>
       </c>
       <c r="P53">
-        <v>494.5383427446404</v>
+        <v>491.475658288653</v>
       </c>
       <c r="Q53">
-        <v>700.4383427446404</v>
+        <v>697.375658288653</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1190732684758761</v>
+        <v>0.1202921257726862</v>
       </c>
       <c r="T53">
-        <v>0.9549963223257018</v>
+        <v>0.9708821188802365</v>
       </c>
       <c r="U53">
         <v>0.08259410488470123</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.166121221184881</v>
+        <v>4.086003505392863</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08608651716731885</v>
+        <v>0.08602595707726801</v>
       </c>
       <c r="C54">
-        <v>2789.070058296668</v>
+        <v>2740.263097733739</v>
       </c>
       <c r="D54">
-        <v>5002.615270521071</v>
+        <v>5009.991871731689</v>
       </c>
       <c r="E54">
-        <v>102.4890348697827</v>
+        <v>158.6725966433291</v>
       </c>
       <c r="F54">
-        <v>2921.545212224403</v>
+        <v>2977.728773997949</v>
       </c>
       <c r="G54">
         <v>708</v>
@@ -5721,28 +5721,28 @@
         <v>985.9625</v>
       </c>
       <c r="M54">
-        <v>241.302411683859</v>
+        <v>245.9428426777794</v>
       </c>
       <c r="N54">
-        <v>744.6600883161409</v>
+        <v>740.0196573222206</v>
       </c>
       <c r="O54">
-        <v>253.1844300274879</v>
+        <v>251.606683489555</v>
       </c>
       <c r="P54">
-        <v>491.475658288653</v>
+        <v>488.4129738326656</v>
       </c>
       <c r="Q54">
-        <v>697.375658288653</v>
+        <v>694.3129738326655</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1202921257726862</v>
+        <v>0.1215628493374458</v>
       </c>
       <c r="T54">
-        <v>0.9708821188802365</v>
+        <v>0.9874439067775173</v>
       </c>
       <c r="U54">
         <v>0.08259410488470123</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.086003505392863</v>
+        <v>4.008909099630735</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08602595707726801</v>
+        <v>0.08721279698721716</v>
       </c>
       <c r="C55">
-        <v>2740.263097733739</v>
+        <v>2543.368029706994</v>
       </c>
       <c r="D55">
-        <v>5009.991871731689</v>
+        <v>4869.280365478489</v>
       </c>
       <c r="E55">
-        <v>158.6725966433291</v>
+        <v>214.8561584168751</v>
       </c>
       <c r="F55">
-        <v>2977.728773997949</v>
+        <v>3033.912335771495</v>
       </c>
       <c r="G55">
         <v>708</v>
@@ -5803,45 +5803,45 @@
         <v>985.9625</v>
       </c>
       <c r="M55">
-        <v>245.9428426777794</v>
+        <v>261.2019668468999</v>
       </c>
       <c r="N55">
-        <v>740.0196573222206</v>
+        <v>724.7605331531</v>
       </c>
       <c r="O55">
-        <v>251.606683489555</v>
+        <v>246.418581272054</v>
       </c>
       <c r="P55">
-        <v>488.4129738326656</v>
+        <v>478.341951881046</v>
       </c>
       <c r="Q55">
-        <v>694.3129738326655</v>
+        <v>684.2419518810459</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1215628493374458</v>
+        <v>0.1228888217528471</v>
       </c>
       <c r="T55">
-        <v>0.9874439067775173</v>
+        <v>1.004725772409463</v>
       </c>
       <c r="U55">
-        <v>0.08259410488470123</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V55">
         <v>0.34</v>
       </c>
       <c r="W55">
-        <v>0.0545121092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.008909099630735</v>
+        <v>3.774713153587809</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08721279698721716</v>
+        <v>0.08717533689716631</v>
       </c>
       <c r="C56">
-        <v>2543.368029706994</v>
+        <v>2491.504820720963</v>
       </c>
       <c r="D56">
-        <v>4869.280365478489</v>
+        <v>4873.600718266005</v>
       </c>
       <c r="E56">
-        <v>214.8561584168751</v>
+        <v>271.0397201904216</v>
       </c>
       <c r="F56">
-        <v>3033.912335771495</v>
+        <v>3090.095897545042</v>
       </c>
       <c r="G56">
         <v>708</v>
@@ -5885,28 +5885,28 @@
         <v>985.9625</v>
       </c>
       <c r="M56">
-        <v>261.2019668468999</v>
+        <v>266.0390403070278</v>
       </c>
       <c r="N56">
-        <v>724.7605331531</v>
+        <v>719.9234596929722</v>
       </c>
       <c r="O56">
-        <v>246.418581272054</v>
+        <v>244.7739762956106</v>
       </c>
       <c r="P56">
-        <v>478.341951881046</v>
+        <v>475.1494833973616</v>
       </c>
       <c r="Q56">
-        <v>684.2419518810459</v>
+        <v>681.0494833973617</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1228888217528471</v>
+        <v>0.1242737262755995</v>
       </c>
       <c r="T56">
-        <v>1.004725772409463</v>
+        <v>1.022775720958383</v>
       </c>
       <c r="U56">
         <v>0.08609410488470122</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.774713153587809</v>
+        <v>3.706082005340757</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08717533689716631</v>
+        <v>0.08713787680711549</v>
       </c>
       <c r="C57">
-        <v>2491.504820720963</v>
+        <v>2439.649285158002</v>
       </c>
       <c r="D57">
-        <v>4873.600718266005</v>
+        <v>4877.928744476591</v>
       </c>
       <c r="E57">
-        <v>271.0397201904216</v>
+        <v>327.223281963968</v>
       </c>
       <c r="F57">
-        <v>3090.095897545042</v>
+        <v>3146.279459318588</v>
       </c>
       <c r="G57">
         <v>708</v>
@@ -5967,28 +5967,28 @@
         <v>985.9625</v>
       </c>
       <c r="M57">
-        <v>266.0390403070278</v>
+        <v>270.8761137671556</v>
       </c>
       <c r="N57">
-        <v>719.9234596929722</v>
+        <v>715.0863862328445</v>
       </c>
       <c r="O57">
-        <v>244.7739762956106</v>
+        <v>243.1293713191671</v>
       </c>
       <c r="P57">
-        <v>475.1494833973616</v>
+        <v>471.9570149136773</v>
       </c>
       <c r="Q57">
-        <v>681.0494833973617</v>
+        <v>677.8570149136773</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1242737262755995</v>
+        <v>0.1257215810039316</v>
       </c>
       <c r="T57">
-        <v>1.022775720958383</v>
+        <v>1.041646121714073</v>
       </c>
       <c r="U57">
         <v>0.08609410488470122</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.706082005340757</v>
+        <v>3.6399019695311</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08713787680711549</v>
+        <v>0.08710041671706462</v>
       </c>
       <c r="C58">
-        <v>2439.649285158002</v>
+        <v>2387.801443479561</v>
       </c>
       <c r="D58">
-        <v>4877.928744476591</v>
+        <v>4882.264464571695</v>
       </c>
       <c r="E58">
-        <v>327.223281963968</v>
+        <v>383.406843737514</v>
       </c>
       <c r="F58">
-        <v>3146.279459318588</v>
+        <v>3202.463021092134</v>
       </c>
       <c r="G58">
         <v>708</v>
@@ -6049,28 +6049,28 @@
         <v>985.9625</v>
       </c>
       <c r="M58">
-        <v>270.8761137671556</v>
+        <v>275.7131872272834</v>
       </c>
       <c r="N58">
-        <v>715.0863862328445</v>
+        <v>710.2493127727166</v>
       </c>
       <c r="O58">
-        <v>243.1293713191671</v>
+        <v>241.4847663427237</v>
       </c>
       <c r="P58">
-        <v>471.9570149136773</v>
+        <v>468.7645464299929</v>
       </c>
       <c r="Q58">
-        <v>677.8570149136773</v>
+        <v>674.6645464299929</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1257215810039316</v>
+        <v>0.1272367778126512</v>
       </c>
       <c r="T58">
-        <v>1.041646121714073</v>
+        <v>1.061394215528167</v>
       </c>
       <c r="U58">
         <v>0.08609410488470122</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.6399019695311</v>
+        <v>3.576044040241081</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08710041671706462</v>
+        <v>0.08706295662701377</v>
       </c>
       <c r="C59">
-        <v>2387.801443479561</v>
+        <v>2335.961316219883</v>
       </c>
       <c r="D59">
-        <v>4882.264464571695</v>
+        <v>4886.607899085563</v>
       </c>
       <c r="E59">
-        <v>383.406843737514</v>
+        <v>439.5904055110605</v>
       </c>
       <c r="F59">
-        <v>3202.463021092134</v>
+        <v>3258.646582865681</v>
       </c>
       <c r="G59">
         <v>708</v>
@@ -6131,28 +6131,28 @@
         <v>985.9625</v>
       </c>
       <c r="M59">
-        <v>275.7131872272834</v>
+        <v>280.5502606874111</v>
       </c>
       <c r="N59">
-        <v>710.2493127727166</v>
+        <v>705.4122393125888</v>
       </c>
       <c r="O59">
-        <v>241.4847663427237</v>
+        <v>239.8401613662802</v>
       </c>
       <c r="P59">
-        <v>468.7645464299929</v>
+        <v>465.5720779463086</v>
       </c>
       <c r="Q59">
-        <v>674.6645464299929</v>
+        <v>671.4720779463086</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1272367778126512</v>
+        <v>0.1288241268503575</v>
       </c>
       <c r="T59">
-        <v>1.061394215528167</v>
+        <v>1.082082694761979</v>
       </c>
       <c r="U59">
         <v>0.08609410488470122</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.576044040241081</v>
+        <v>3.514388108512786</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08706295662701379</v>
+        <v>0.08811581653696293</v>
       </c>
       <c r="C60">
-        <v>2335.961316219882</v>
+        <v>2160.572450880269</v>
       </c>
       <c r="D60">
-        <v>4886.607899085561</v>
+        <v>4767.402595519495</v>
       </c>
       <c r="E60">
-        <v>439.5904055110595</v>
+        <v>495.773967284606</v>
       </c>
       <c r="F60">
-        <v>3258.64658286568</v>
+        <v>3314.830144639226</v>
       </c>
       <c r="G60">
         <v>708</v>
@@ -6213,45 +6213,45 @@
         <v>985.9625</v>
       </c>
       <c r="M60">
-        <v>280.550260687411</v>
+        <v>294.6688585525287</v>
       </c>
       <c r="N60">
-        <v>705.412239312589</v>
+        <v>691.2936414474713</v>
       </c>
       <c r="O60">
-        <v>239.8401613662803</v>
+        <v>235.0398380921403</v>
       </c>
       <c r="P60">
-        <v>465.5720779463087</v>
+        <v>456.253803355331</v>
       </c>
       <c r="Q60">
-        <v>671.4720779463087</v>
+        <v>662.153803355331</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1288241268503575</v>
+        <v>0.1304889075484397</v>
       </c>
       <c r="T60">
-        <v>1.082082694761979</v>
+        <v>1.103780368104758</v>
       </c>
       <c r="U60">
-        <v>0.08609410488470122</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V60">
         <v>0.34</v>
       </c>
       <c r="W60">
-        <v>0.05682210922390279</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.514388108512788</v>
+        <v>3.346001694387528</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08811581653696293</v>
+        <v>0.0880968364469121</v>
       </c>
       <c r="C61">
-        <v>2160.572450880269</v>
+        <v>2106.486324637217</v>
       </c>
       <c r="D61">
-        <v>4767.402595519495</v>
+        <v>4769.50003104999</v>
       </c>
       <c r="E61">
-        <v>495.773967284606</v>
+        <v>551.9575290581524</v>
       </c>
       <c r="F61">
-        <v>3314.830144639226</v>
+        <v>3371.013706412773</v>
       </c>
       <c r="G61">
         <v>708</v>
@@ -6295,28 +6295,28 @@
         <v>985.9625</v>
       </c>
       <c r="M61">
-        <v>294.6688585525287</v>
+        <v>299.6632459856224</v>
       </c>
       <c r="N61">
-        <v>691.2936414474713</v>
+        <v>686.2992540143775</v>
       </c>
       <c r="O61">
-        <v>235.0398380921403</v>
+        <v>233.3417463648884</v>
       </c>
       <c r="P61">
-        <v>456.253803355331</v>
+        <v>452.9575076494891</v>
       </c>
       <c r="Q61">
-        <v>662.153803355331</v>
+        <v>658.8575076494891</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1304889075484397</v>
+        <v>0.132236927281426</v>
       </c>
       <c r="T61">
-        <v>1.103780368104758</v>
+        <v>1.126562925114677</v>
       </c>
       <c r="U61">
         <v>0.08889410488470123</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.346001694387528</v>
+        <v>3.290234999481069</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0880968364469121</v>
+        <v>0.08807785635686126</v>
       </c>
       <c r="C62">
-        <v>2106.486324637217</v>
+        <v>2052.40204475475</v>
       </c>
       <c r="D62">
-        <v>4769.50003104999</v>
+        <v>4771.599312941069</v>
       </c>
       <c r="E62">
-        <v>551.9575290581524</v>
+        <v>608.1410908316984</v>
       </c>
       <c r="F62">
-        <v>3371.013706412773</v>
+        <v>3427.197268186319</v>
       </c>
       <c r="G62">
         <v>708</v>
@@ -6377,28 +6377,28 @@
         <v>985.9625</v>
       </c>
       <c r="M62">
-        <v>299.6632459856224</v>
+        <v>304.6576334187161</v>
       </c>
       <c r="N62">
-        <v>686.2992540143775</v>
+        <v>681.3048665812839</v>
       </c>
       <c r="O62">
-        <v>233.3417463648884</v>
+        <v>231.6436546376366</v>
       </c>
       <c r="P62">
-        <v>452.9575076494891</v>
+        <v>449.6612119436473</v>
       </c>
       <c r="Q62">
-        <v>658.8575076494891</v>
+        <v>655.5612119436473</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.132236927281426</v>
+        <v>0.1340745890520014</v>
       </c>
       <c r="T62">
-        <v>1.126562925114677</v>
+        <v>1.150513818381514</v>
       </c>
       <c r="U62">
         <v>0.08889410488470123</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.290234999481069</v>
+        <v>3.236296720801052</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08807785635686126</v>
+        <v>0.0880588762668104</v>
       </c>
       <c r="C63">
-        <v>2052.40204475475</v>
+        <v>1998.319613671951</v>
       </c>
       <c r="D63">
-        <v>4771.599312941069</v>
+        <v>4773.700443631816</v>
       </c>
       <c r="E63">
-        <v>608.1410908316984</v>
+        <v>664.3246526052449</v>
       </c>
       <c r="F63">
-        <v>3427.197268186319</v>
+        <v>3483.380829959865</v>
       </c>
       <c r="G63">
         <v>708</v>
@@ -6459,28 +6459,28 @@
         <v>985.9625</v>
       </c>
       <c r="M63">
-        <v>304.6576334187161</v>
+        <v>309.6520208518099</v>
       </c>
       <c r="N63">
-        <v>681.3048665812839</v>
+        <v>676.3104791481901</v>
       </c>
       <c r="O63">
-        <v>231.6436546376366</v>
+        <v>229.9455629103846</v>
       </c>
       <c r="P63">
-        <v>449.6612119436473</v>
+        <v>446.3649162378055</v>
       </c>
       <c r="Q63">
-        <v>655.5612119436473</v>
+        <v>652.2649162378054</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1340745890520014</v>
+        <v>0.1360089698631333</v>
       </c>
       <c r="T63">
-        <v>1.150513818381514</v>
+        <v>1.175725284978184</v>
       </c>
       <c r="U63">
         <v>0.08889410488470123</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.236296720801052</v>
+        <v>3.184098386594583</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0880588762668104</v>
+        <v>0.08803989617675956</v>
       </c>
       <c r="C64">
-        <v>1998.319613671951</v>
+        <v>1944.2390338322</v>
       </c>
       <c r="D64">
-        <v>4773.700443631816</v>
+        <v>4775.803425565611</v>
       </c>
       <c r="E64">
-        <v>664.3246526052449</v>
+        <v>720.5082143787909</v>
       </c>
       <c r="F64">
-        <v>3483.380829959865</v>
+        <v>3539.564391733411</v>
       </c>
       <c r="G64">
         <v>708</v>
@@ -6541,28 +6541,28 @@
         <v>985.9625</v>
       </c>
       <c r="M64">
-        <v>309.6520208518099</v>
+        <v>314.6464082849035</v>
       </c>
       <c r="N64">
-        <v>676.3104791481901</v>
+        <v>671.3160917150965</v>
       </c>
       <c r="O64">
-        <v>229.9455629103846</v>
+        <v>228.2474711831328</v>
       </c>
       <c r="P64">
-        <v>446.3649162378055</v>
+        <v>443.0686205319637</v>
       </c>
       <c r="Q64">
-        <v>652.2649162378054</v>
+        <v>648.9686205319637</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1360089698631333</v>
+        <v>0.1380479117991913</v>
       </c>
       <c r="T64">
-        <v>1.175725284978184</v>
+        <v>1.202299533553053</v>
       </c>
       <c r="U64">
         <v>0.08889410488470123</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.184098386594583</v>
+        <v>3.133557142362923</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08803989617675956</v>
+        <v>0.08802091608670871</v>
       </c>
       <c r="C65">
-        <v>1944.2390338322</v>
+        <v>1890.160307683188</v>
       </c>
       <c r="D65">
-        <v>4775.803425565611</v>
+        <v>4777.908261190146</v>
       </c>
       <c r="E65">
-        <v>720.5082143787909</v>
+        <v>776.6917761523373</v>
       </c>
       <c r="F65">
-        <v>3539.564391733411</v>
+        <v>3595.747953506957</v>
       </c>
       <c r="G65">
         <v>708</v>
@@ -6623,28 +6623,28 @@
         <v>985.9625</v>
       </c>
       <c r="M65">
-        <v>314.6464082849035</v>
+        <v>319.6407957179973</v>
       </c>
       <c r="N65">
-        <v>671.3160917150965</v>
+        <v>666.3217042820027</v>
       </c>
       <c r="O65">
-        <v>228.2474711831328</v>
+        <v>226.5493794558809</v>
       </c>
       <c r="P65">
-        <v>443.0686205319637</v>
+        <v>439.7723248261217</v>
       </c>
       <c r="Q65">
-        <v>648.9686205319637</v>
+        <v>645.6723248261217</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1380479117991913</v>
+        <v>0.1402001282872526</v>
       </c>
       <c r="T65">
-        <v>1.202299533553053</v>
+        <v>1.23035012927097</v>
       </c>
       <c r="U65">
         <v>0.08889410488470123</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.133557142362923</v>
+        <v>3.084595312013502</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08802091608670871</v>
+        <v>0.08800193599665787</v>
       </c>
       <c r="C66">
-        <v>1890.160307683188</v>
+        <v>1836.083437676924</v>
       </c>
       <c r="D66">
-        <v>4777.908261190146</v>
+        <v>4780.014952957427</v>
       </c>
       <c r="E66">
-        <v>776.6917761523373</v>
+        <v>832.8753379258833</v>
       </c>
       <c r="F66">
-        <v>3595.747953506957</v>
+        <v>3651.931515280503</v>
       </c>
       <c r="G66">
         <v>708</v>
@@ -6705,28 +6705,28 @@
         <v>985.9625</v>
       </c>
       <c r="M66">
-        <v>319.6407957179973</v>
+        <v>324.635183151091</v>
       </c>
       <c r="N66">
-        <v>666.3217042820027</v>
+        <v>661.327316848909</v>
       </c>
       <c r="O66">
-        <v>226.5493794558809</v>
+        <v>224.8512877286291</v>
       </c>
       <c r="P66">
-        <v>439.7723248261217</v>
+        <v>436.4760291202799</v>
       </c>
       <c r="Q66">
-        <v>645.6723248261217</v>
+        <v>642.3760291202799</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1402001282872526</v>
+        <v>0.1424753285746316</v>
       </c>
       <c r="T66">
-        <v>1.23035012927097</v>
+        <v>1.260003616172769</v>
       </c>
       <c r="U66">
         <v>0.08889410488470123</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.084595312013502</v>
+        <v>3.037139999520987</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08800193599665787</v>
+        <v>0.09138063590660703</v>
       </c>
       <c r="C67">
-        <v>1836.083437676924</v>
+        <v>1432.021318878315</v>
       </c>
       <c r="D67">
-        <v>4780.014952957427</v>
+        <v>4432.136395932364</v>
       </c>
       <c r="E67">
-        <v>832.8753379258833</v>
+        <v>889.0588996994297</v>
       </c>
       <c r="F67">
-        <v>3651.931515280503</v>
+        <v>3708.11507705405</v>
       </c>
       <c r="G67">
         <v>708</v>
@@ -6787,45 +6787,45 @@
         <v>985.9625</v>
       </c>
       <c r="M67">
-        <v>324.635183151091</v>
+        <v>358.5528681852063</v>
       </c>
       <c r="N67">
-        <v>661.327316848909</v>
+        <v>627.4096318147937</v>
       </c>
       <c r="O67">
-        <v>224.8512877286291</v>
+        <v>213.3192748170299</v>
       </c>
       <c r="P67">
-        <v>436.4760291202799</v>
+        <v>414.0903569977638</v>
       </c>
       <c r="Q67">
-        <v>642.3760291202799</v>
+        <v>619.9903569977638</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1424753285746316</v>
+        <v>0.1448843641730329</v>
       </c>
       <c r="T67">
-        <v>1.260003616172769</v>
+        <v>1.291401425833496</v>
       </c>
       <c r="U67">
-        <v>0.08889410488470123</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V67">
         <v>0.34</v>
       </c>
       <c r="W67">
-        <v>0.0586701092239028</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.037139999520987</v>
+        <v>2.74983855237413</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09138063590660703</v>
+        <v>0.09141313581655619</v>
       </c>
       <c r="C68">
-        <v>1432.021318878315</v>
+        <v>1372.737197129794</v>
       </c>
       <c r="D68">
-        <v>4432.136395932364</v>
+        <v>4429.03583595739</v>
       </c>
       <c r="E68">
-        <v>889.0588996994297</v>
+        <v>945.2424614729762</v>
       </c>
       <c r="F68">
-        <v>3708.11507705405</v>
+        <v>3764.298638827596</v>
       </c>
       <c r="G68">
         <v>708</v>
@@ -6869,28 +6869,28 @@
         <v>985.9625</v>
       </c>
       <c r="M68">
-        <v>358.5528681852063</v>
+        <v>363.9854874001336</v>
       </c>
       <c r="N68">
-        <v>627.4096318147937</v>
+        <v>621.9770125998664</v>
       </c>
       <c r="O68">
-        <v>213.3192748170299</v>
+        <v>211.4721842839546</v>
       </c>
       <c r="P68">
-        <v>414.0903569977638</v>
+        <v>410.5048283159118</v>
       </c>
       <c r="Q68">
-        <v>619.9903569977638</v>
+        <v>616.4048283159118</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1448843641730329</v>
+        <v>0.147439401928913</v>
       </c>
       <c r="T68">
-        <v>1.291401425833496</v>
+        <v>1.324702133049419</v>
       </c>
       <c r="U68">
         <v>0.09669410488470123</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.74983855237413</v>
+        <v>2.708796185920785</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09141313581655619</v>
+        <v>0.09144563572650533</v>
       </c>
       <c r="C69">
-        <v>1372.737197129794</v>
+        <v>1313.457410424591</v>
       </c>
       <c r="D69">
-        <v>4429.03583595739</v>
+        <v>4425.939611025733</v>
       </c>
       <c r="E69">
-        <v>945.2424614729762</v>
+        <v>1001.426023246522</v>
       </c>
       <c r="F69">
-        <v>3764.298638827596</v>
+        <v>3820.482200601142</v>
       </c>
       <c r="G69">
         <v>708</v>
@@ -6951,28 +6951,28 @@
         <v>985.9625</v>
       </c>
       <c r="M69">
-        <v>363.9854874001336</v>
+        <v>369.418106615061</v>
       </c>
       <c r="N69">
-        <v>621.9770125998664</v>
+        <v>616.544393384939</v>
       </c>
       <c r="O69">
-        <v>211.4721842839546</v>
+        <v>209.6250937508793</v>
       </c>
       <c r="P69">
-        <v>410.5048283159118</v>
+        <v>406.9192996340597</v>
       </c>
       <c r="Q69">
-        <v>616.4048283159118</v>
+        <v>612.8192996340597</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.147439401928913</v>
+        <v>0.1501541295445357</v>
       </c>
       <c r="T69">
-        <v>1.324702133049419</v>
+        <v>1.360084134466337</v>
       </c>
       <c r="U69">
         <v>0.09669410488470123</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.708796185920785</v>
+        <v>2.668960947892538</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09144563572650533</v>
+        <v>0.09147813563645449</v>
       </c>
       <c r="C70">
-        <v>1313.457410424591</v>
+        <v>1254.1819496775</v>
       </c>
       <c r="D70">
-        <v>4425.939611025733</v>
+        <v>4422.847712052188</v>
       </c>
       <c r="E70">
-        <v>1001.426023246522</v>
+        <v>1057.609585020069</v>
       </c>
       <c r="F70">
-        <v>3820.482200601142</v>
+        <v>3876.665762374689</v>
       </c>
       <c r="G70">
         <v>708</v>
@@ -7033,28 +7033,28 @@
         <v>985.9625</v>
       </c>
       <c r="M70">
-        <v>369.418106615061</v>
+        <v>374.8507258299884</v>
       </c>
       <c r="N70">
-        <v>616.544393384939</v>
+        <v>611.1117741700116</v>
       </c>
       <c r="O70">
-        <v>209.6250937508793</v>
+        <v>207.778003217804</v>
       </c>
       <c r="P70">
-        <v>406.9192996340597</v>
+        <v>403.3337709522076</v>
       </c>
       <c r="Q70">
-        <v>612.8192996340597</v>
+        <v>609.2337709522076</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1501541295445357</v>
+        <v>0.1530440008772953</v>
       </c>
       <c r="T70">
-        <v>1.360084134466337</v>
+        <v>1.397748845652089</v>
       </c>
       <c r="U70">
         <v>0.09669410488470123</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.668960947892538</v>
+        <v>2.63028035444482</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09147813563645449</v>
+        <v>0.09151063554640364</v>
       </c>
       <c r="C71">
-        <v>1254.1819496775</v>
+        <v>1194.910805828695</v>
       </c>
       <c r="D71">
-        <v>4422.847712052188</v>
+        <v>4419.760129976929</v>
       </c>
       <c r="E71">
-        <v>1057.609585020069</v>
+        <v>1113.793146793615</v>
       </c>
       <c r="F71">
-        <v>3876.665762374689</v>
+        <v>3932.849324148235</v>
       </c>
       <c r="G71">
         <v>708</v>
@@ -7115,28 +7115,28 @@
         <v>985.9625</v>
       </c>
       <c r="M71">
-        <v>374.8507258299884</v>
+        <v>380.2833450449157</v>
       </c>
       <c r="N71">
-        <v>611.1117741700116</v>
+        <v>605.6791549550842</v>
       </c>
       <c r="O71">
-        <v>207.778003217804</v>
+        <v>205.9309126847286</v>
       </c>
       <c r="P71">
-        <v>403.3337709522076</v>
+        <v>399.7482422703555</v>
       </c>
       <c r="Q71">
-        <v>609.2337709522076</v>
+        <v>605.6482422703555</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1530440008772953</v>
+        <v>0.1561265302989056</v>
       </c>
       <c r="T71">
-        <v>1.397748845652089</v>
+        <v>1.437924537583557</v>
       </c>
       <c r="U71">
         <v>0.09669410488470123</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.63028035444482</v>
+        <v>2.592704920809894</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09151063554640364</v>
+        <v>0.0915431354563528</v>
       </c>
       <c r="C72">
-        <v>1194.910805828695</v>
+        <v>1135.643969843621</v>
       </c>
       <c r="D72">
-        <v>4419.760129976929</v>
+        <v>4416.676855765402</v>
       </c>
       <c r="E72">
-        <v>1113.793146793615</v>
+        <v>1169.976708567161</v>
       </c>
       <c r="F72">
-        <v>3932.849324148235</v>
+        <v>3989.032885921781</v>
       </c>
       <c r="G72">
         <v>708</v>
@@ -7197,28 +7197,28 @@
         <v>985.9625</v>
       </c>
       <c r="M72">
-        <v>380.2833450449157</v>
+        <v>385.7159642598431</v>
       </c>
       <c r="N72">
-        <v>605.6791549550842</v>
+        <v>600.2465357401568</v>
       </c>
       <c r="O72">
-        <v>205.9309126847286</v>
+        <v>204.0838221516533</v>
       </c>
       <c r="P72">
-        <v>399.7482422703555</v>
+        <v>396.1627135885035</v>
       </c>
       <c r="Q72">
-        <v>605.6482422703555</v>
+        <v>602.0627135885035</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1561265302989056</v>
+        <v>0.159421647956489</v>
       </c>
       <c r="T72">
-        <v>1.437924537583557</v>
+        <v>1.48087096688961</v>
       </c>
       <c r="U72">
         <v>0.09669410488470123</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.592704920809894</v>
+        <v>2.556187950094261</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09154313545635279</v>
+        <v>0.09157563536630195</v>
       </c>
       <c r="C73">
-        <v>1135.643969843623</v>
+        <v>1076.381432712928</v>
       </c>
       <c r="D73">
-        <v>4416.676855765404</v>
+        <v>4413.597880408254</v>
       </c>
       <c r="E73">
-        <v>1169.976708567161</v>
+        <v>1226.160270340707</v>
       </c>
       <c r="F73">
-        <v>3989.032885921781</v>
+        <v>4045.216447695327</v>
       </c>
       <c r="G73">
         <v>708</v>
@@ -7279,28 +7279,28 @@
         <v>985.9625</v>
       </c>
       <c r="M73">
-        <v>385.7159642598431</v>
+        <v>391.1485834747705</v>
       </c>
       <c r="N73">
-        <v>600.2465357401568</v>
+        <v>594.8139165252295</v>
       </c>
       <c r="O73">
-        <v>204.0838221516533</v>
+        <v>202.236731618578</v>
       </c>
       <c r="P73">
-        <v>396.1627135885035</v>
+        <v>392.5771849066515</v>
       </c>
       <c r="Q73">
-        <v>602.0627135885035</v>
+        <v>598.4771849066515</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1594216479564889</v>
+        <v>0.1629521311610426</v>
       </c>
       <c r="T73">
-        <v>1.480870966889609</v>
+        <v>1.526884998288951</v>
       </c>
       <c r="U73">
         <v>0.09669410488470123</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.556187950094261</v>
+        <v>2.520685339676286</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09157563536630195</v>
+        <v>0.09348715527625109</v>
       </c>
       <c r="C74">
-        <v>1076.381432712928</v>
+        <v>846.3584098130586</v>
       </c>
       <c r="D74">
-        <v>4413.597880408254</v>
+        <v>4239.758419281931</v>
       </c>
       <c r="E74">
-        <v>1226.160270340707</v>
+        <v>1282.343832114253</v>
       </c>
       <c r="F74">
-        <v>4045.216447695327</v>
+        <v>4101.400009468873</v>
       </c>
       <c r="G74">
         <v>708</v>
@@ -7361,45 +7361,45 @@
         <v>985.9625</v>
       </c>
       <c r="M74">
-        <v>391.1485834747705</v>
+        <v>412.5766627266264</v>
       </c>
       <c r="N74">
-        <v>594.8139165252295</v>
+        <v>573.3858372733737</v>
       </c>
       <c r="O74">
-        <v>202.236731618578</v>
+        <v>194.9511846729471</v>
       </c>
       <c r="P74">
-        <v>392.5771849066515</v>
+        <v>378.4346526004266</v>
       </c>
       <c r="Q74">
-        <v>598.4771849066515</v>
+        <v>584.3346526004266</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1629521311610426</v>
+        <v>0.1667441316400076</v>
       </c>
       <c r="T74">
-        <v>1.526884998288951</v>
+        <v>1.576307476458615</v>
       </c>
       <c r="U74">
-        <v>0.09669410488470123</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V74">
         <v>0.34</v>
       </c>
       <c r="W74">
-        <v>0.06381810922390281</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.520685339676286</v>
+        <v>2.389767985140012</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09348715527625109</v>
+        <v>0.09354539518620025</v>
       </c>
       <c r="C75">
-        <v>846.3584098130586</v>
+        <v>785.0930462189835</v>
       </c>
       <c r="D75">
-        <v>4239.758419281931</v>
+        <v>4234.676617461403</v>
       </c>
       <c r="E75">
-        <v>1282.343832114253</v>
+        <v>1338.527393887799</v>
       </c>
       <c r="F75">
-        <v>4101.400009468873</v>
+        <v>4157.58357124242</v>
       </c>
       <c r="G75">
         <v>708</v>
@@ -7443,28 +7443,28 @@
         <v>985.9625</v>
       </c>
       <c r="M75">
-        <v>412.5766627266264</v>
+        <v>418.2283978324706</v>
       </c>
       <c r="N75">
-        <v>573.3858372733737</v>
+        <v>567.7341021675294</v>
       </c>
       <c r="O75">
-        <v>194.9511846729471</v>
+        <v>193.02959473696</v>
       </c>
       <c r="P75">
-        <v>378.4346526004266</v>
+        <v>374.7045074305694</v>
       </c>
       <c r="Q75">
-        <v>584.3346526004266</v>
+        <v>580.6045074305694</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1667441316400076</v>
+        <v>0.1708278244635084</v>
       </c>
       <c r="T75">
-        <v>1.576307476458615</v>
+        <v>1.629531683718253</v>
       </c>
       <c r="U75">
         <v>0.1005941048847012</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.389767985140012</v>
+        <v>2.35747382317866</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09354539518620025</v>
+        <v>0.0936036350961494</v>
       </c>
       <c r="C76">
-        <v>785.0930462189835</v>
+        <v>723.8398502017335</v>
       </c>
       <c r="D76">
-        <v>4234.676617461403</v>
+        <v>4229.606983217699</v>
       </c>
       <c r="E76">
-        <v>1338.527393887799</v>
+        <v>1394.710955661345</v>
       </c>
       <c r="F76">
-        <v>4157.58357124242</v>
+        <v>4213.767133015966</v>
       </c>
       <c r="G76">
         <v>708</v>
@@ -7525,28 +7525,28 @@
         <v>985.9625</v>
       </c>
       <c r="M76">
-        <v>418.2283978324706</v>
+        <v>423.8801329383148</v>
       </c>
       <c r="N76">
-        <v>567.7341021675294</v>
+        <v>562.0823670616852</v>
       </c>
       <c r="O76">
-        <v>193.02959473696</v>
+        <v>191.108004800973</v>
       </c>
       <c r="P76">
-        <v>374.7045074305694</v>
+        <v>370.9743622607122</v>
       </c>
       <c r="Q76">
-        <v>580.6045074305694</v>
+        <v>576.8743622607121</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1708278244635084</v>
+        <v>0.1752382127128892</v>
       </c>
       <c r="T76">
-        <v>1.629531683718253</v>
+        <v>1.687013827558661</v>
       </c>
       <c r="U76">
         <v>0.1005941048847012</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.35747382317866</v>
+        <v>2.326040838869611</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0936036350961494</v>
+        <v>0.09366187500609856</v>
       </c>
       <c r="C77">
-        <v>723.8398502017335</v>
+        <v>662.5987781135282</v>
       </c>
       <c r="D77">
-        <v>4229.606983217699</v>
+        <v>4224.54947290304</v>
       </c>
       <c r="E77">
-        <v>1394.710955661345</v>
+        <v>1450.894517434891</v>
       </c>
       <c r="F77">
-        <v>4213.767133015966</v>
+        <v>4269.950694789512</v>
       </c>
       <c r="G77">
         <v>708</v>
@@ -7607,28 +7607,28 @@
         <v>985.9625</v>
       </c>
       <c r="M77">
-        <v>423.8801329383148</v>
+        <v>429.531868044159</v>
       </c>
       <c r="N77">
-        <v>562.0823670616852</v>
+        <v>556.430631955841</v>
       </c>
       <c r="O77">
-        <v>191.108004800973</v>
+        <v>189.1864148649859</v>
       </c>
       <c r="P77">
-        <v>370.9743622607122</v>
+        <v>367.244217090855</v>
       </c>
       <c r="Q77">
-        <v>576.8743622607121</v>
+        <v>573.144217090855</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1752382127128892</v>
+        <v>0.1800161333163852</v>
       </c>
       <c r="T77">
-        <v>1.687013827558661</v>
+        <v>1.749286150052438</v>
       </c>
       <c r="U77">
         <v>0.1005941048847012</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.326040838869611</v>
+        <v>2.295435038358169</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09366187500609856</v>
+        <v>0.0937201149160477</v>
       </c>
       <c r="C78">
-        <v>662.5987781135282</v>
+        <v>601.3697865151098</v>
       </c>
       <c r="D78">
-        <v>4224.54947290304</v>
+        <v>4219.504043078168</v>
       </c>
       <c r="E78">
-        <v>1450.894517434891</v>
+        <v>1507.078079208438</v>
       </c>
       <c r="F78">
-        <v>4269.950694789512</v>
+        <v>4326.134256563058</v>
       </c>
       <c r="G78">
         <v>708</v>
@@ -7689,28 +7689,28 @@
         <v>985.9625</v>
       </c>
       <c r="M78">
-        <v>429.531868044159</v>
+        <v>435.1836031500033</v>
       </c>
       <c r="N78">
-        <v>556.430631955841</v>
+        <v>550.7788968499967</v>
       </c>
       <c r="O78">
-        <v>189.1864148649859</v>
+        <v>187.2648249289989</v>
       </c>
       <c r="P78">
-        <v>367.244217090855</v>
+        <v>363.5140719209978</v>
       </c>
       <c r="Q78">
-        <v>573.144217090855</v>
+        <v>569.4140719209978</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1800161333163852</v>
+        <v>0.1852095252767068</v>
       </c>
       <c r="T78">
-        <v>1.749286150052438</v>
+        <v>1.81697345711089</v>
       </c>
       <c r="U78">
         <v>0.1005941048847012</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.295435038358169</v>
+        <v>2.265624193704166</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0937201149160477</v>
+        <v>0.09377835482599686</v>
       </c>
       <c r="C79">
-        <v>601.3697865151098</v>
+        <v>540.1528321744909</v>
       </c>
       <c r="D79">
-        <v>4219.504043078168</v>
+        <v>4214.470650511095</v>
       </c>
       <c r="E79">
-        <v>1507.078079208438</v>
+        <v>1563.261640981984</v>
       </c>
       <c r="F79">
-        <v>4326.134256563058</v>
+        <v>4382.317818336604</v>
       </c>
       <c r="G79">
         <v>708</v>
@@ -7771,28 +7771,28 @@
         <v>985.9625</v>
       </c>
       <c r="M79">
-        <v>435.1836031500033</v>
+        <v>440.8353382558474</v>
       </c>
       <c r="N79">
-        <v>550.7788968499967</v>
+        <v>545.1271617441525</v>
       </c>
       <c r="O79">
-        <v>187.2648249289989</v>
+        <v>185.3432349930119</v>
       </c>
       <c r="P79">
-        <v>363.5140719209978</v>
+        <v>359.7839267511407</v>
       </c>
       <c r="Q79">
-        <v>569.4140719209978</v>
+        <v>565.6839267511407</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1852095252767068</v>
+        <v>0.1908750437788758</v>
       </c>
       <c r="T79">
-        <v>1.81697345711089</v>
+        <v>1.890814155720111</v>
       </c>
       <c r="U79">
         <v>0.1005941048847012</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.265624193704166</v>
+        <v>2.236577729682318</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09377835482599686</v>
+        <v>0.09383659473594602</v>
       </c>
       <c r="C80">
-        <v>540.1528321744909</v>
+        <v>478.9478720657244</v>
       </c>
       <c r="D80">
-        <v>4214.470650511095</v>
+        <v>4209.449252175875</v>
       </c>
       <c r="E80">
-        <v>1563.261640981984</v>
+        <v>1619.44520275553</v>
       </c>
       <c r="F80">
-        <v>4382.317818336604</v>
+        <v>4438.50138011015</v>
       </c>
       <c r="G80">
         <v>708</v>
@@ -7853,28 +7853,28 @@
         <v>985.9625</v>
       </c>
       <c r="M80">
-        <v>440.8353382558474</v>
+        <v>446.4870733616916</v>
       </c>
       <c r="N80">
-        <v>545.1271617441525</v>
+        <v>539.4754266383084</v>
       </c>
       <c r="O80">
-        <v>185.3432349930119</v>
+        <v>183.4216450570248</v>
       </c>
       <c r="P80">
-        <v>359.7839267511407</v>
+        <v>356.0537815812835</v>
       </c>
       <c r="Q80">
-        <v>565.6839267511407</v>
+        <v>561.9537815812835</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1908750437788758</v>
+        <v>0.1970801354717277</v>
       </c>
       <c r="T80">
-        <v>1.890814155720111</v>
+        <v>1.971687301815924</v>
       </c>
       <c r="U80">
         <v>0.1005941048847012</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.236577729682318</v>
+        <v>2.20826661918001</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09383659473594602</v>
+        <v>0.09389483464589517</v>
       </c>
       <c r="C81">
-        <v>478.9478720657244</v>
+        <v>417.7548633676734</v>
       </c>
       <c r="D81">
-        <v>4209.449252175875</v>
+        <v>4204.43980525137</v>
       </c>
       <c r="E81">
-        <v>1619.44520275553</v>
+        <v>1675.628764529076</v>
       </c>
       <c r="F81">
-        <v>4438.50138011015</v>
+        <v>4494.684941883696</v>
       </c>
       <c r="G81">
         <v>708</v>
@@ -7935,28 +7935,28 @@
         <v>985.9625</v>
       </c>
       <c r="M81">
-        <v>446.4870733616916</v>
+        <v>452.1388084675357</v>
       </c>
       <c r="N81">
-        <v>539.4754266383084</v>
+        <v>533.8236915324642</v>
       </c>
       <c r="O81">
-        <v>183.4216450570248</v>
+        <v>181.5000551210378</v>
       </c>
       <c r="P81">
-        <v>356.0537815812835</v>
+        <v>352.3236364114264</v>
       </c>
       <c r="Q81">
-        <v>561.9537815812835</v>
+        <v>558.2236364114264</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1970801354717277</v>
+        <v>0.2039057363338647</v>
       </c>
       <c r="T81">
-        <v>1.971687301815924</v>
+        <v>2.060647762521318</v>
       </c>
       <c r="U81">
         <v>0.1005941048847012</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.20826661918001</v>
+        <v>2.18066328644026</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09389483464589517</v>
+        <v>0.09395307455584433</v>
       </c>
       <c r="C82">
-        <v>417.7548633676734</v>
+        <v>356.5737634627922</v>
       </c>
       <c r="D82">
-        <v>4204.43980525137</v>
+        <v>4199.442267120035</v>
       </c>
       <c r="E82">
-        <v>1675.628764529076</v>
+        <v>1731.812326302623</v>
       </c>
       <c r="F82">
-        <v>4494.684941883696</v>
+        <v>4550.868503657243</v>
       </c>
       <c r="G82">
         <v>708</v>
@@ -8017,28 +8017,28 @@
         <v>985.9625</v>
       </c>
       <c r="M82">
-        <v>452.1388084675357</v>
+        <v>457.79054357338</v>
       </c>
       <c r="N82">
-        <v>533.8236915324642</v>
+        <v>528.17195642662</v>
       </c>
       <c r="O82">
-        <v>181.5000551210378</v>
+        <v>179.5784651850508</v>
       </c>
       <c r="P82">
-        <v>352.3236364114264</v>
+        <v>348.5934912415692</v>
       </c>
       <c r="Q82">
-        <v>558.2236364114264</v>
+        <v>554.4934912415691</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2039057363338647</v>
+        <v>0.2114498214972793</v>
       </c>
       <c r="T82">
-        <v>2.060647762521318</v>
+        <v>2.158972482248334</v>
       </c>
       <c r="U82">
         <v>0.1005941048847012</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.18066328644026</v>
+        <v>2.153741517471862</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09395307455584433</v>
+        <v>0.09401131446579349</v>
       </c>
       <c r="C83">
-        <v>356.5737634627922</v>
+        <v>295.4045299359268</v>
       </c>
       <c r="D83">
-        <v>4199.442267120035</v>
+        <v>4194.456595366716</v>
       </c>
       <c r="E83">
-        <v>1731.812326302623</v>
+        <v>1787.995888076169</v>
       </c>
       <c r="F83">
-        <v>4550.868503657243</v>
+        <v>4607.052065430789</v>
       </c>
       <c r="G83">
         <v>708</v>
@@ -8099,28 +8099,28 @@
         <v>985.9625</v>
       </c>
       <c r="M83">
-        <v>457.79054357338</v>
+        <v>463.4422786792242</v>
       </c>
       <c r="N83">
-        <v>528.17195642662</v>
+        <v>522.5202213207758</v>
       </c>
       <c r="O83">
-        <v>179.5784651850508</v>
+        <v>177.6568752490638</v>
       </c>
       <c r="P83">
-        <v>348.5934912415692</v>
+        <v>344.863346071712</v>
       </c>
       <c r="Q83">
-        <v>554.4934912415691</v>
+        <v>550.763346071712</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2114498214972793</v>
+        <v>0.2198321383455178</v>
       </c>
       <c r="T83">
-        <v>2.158972482248334</v>
+        <v>2.268222170833906</v>
       </c>
       <c r="U83">
         <v>0.1005941048847012</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.153741517471862</v>
+        <v>2.127476377014888</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09401131446579349</v>
+        <v>0.09406955437574263</v>
       </c>
       <c r="C84">
-        <v>295.4045299359268</v>
+        <v>234.2471205731081</v>
       </c>
       <c r="D84">
-        <v>4194.456595366716</v>
+        <v>4189.482747777443</v>
       </c>
       <c r="E84">
-        <v>1787.995888076169</v>
+        <v>1844.179449849715</v>
       </c>
       <c r="F84">
-        <v>4607.052065430789</v>
+        <v>4663.235627204335</v>
       </c>
       <c r="G84">
         <v>708</v>
@@ -8181,28 +8181,28 @@
         <v>985.9625</v>
       </c>
       <c r="M84">
-        <v>463.4422786792242</v>
+        <v>469.0940137850684</v>
       </c>
       <c r="N84">
-        <v>522.5202213207758</v>
+        <v>516.8684862149316</v>
       </c>
       <c r="O84">
-        <v>177.6568752490638</v>
+        <v>175.7352853130768</v>
       </c>
       <c r="P84">
-        <v>344.863346071712</v>
+        <v>341.1332009018549</v>
       </c>
       <c r="Q84">
-        <v>550.763346071712</v>
+        <v>547.0332009018548</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2198321383455178</v>
+        <v>0.2292006101170784</v>
       </c>
       <c r="T84">
-        <v>2.268222170833906</v>
+        <v>2.390324763958957</v>
       </c>
       <c r="U84">
         <v>0.1005941048847012</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.127476377014888</v>
+        <v>2.101844131508685</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09406955437574263</v>
+        <v>0.09412779428569179</v>
       </c>
       <c r="C85">
-        <v>234.2471205731081</v>
+        <v>173.1014933603556</v>
       </c>
       <c r="D85">
-        <v>4189.482747777443</v>
+        <v>4184.520682338238</v>
       </c>
       <c r="E85">
-        <v>1844.179449849715</v>
+        <v>1900.363011623262</v>
       </c>
       <c r="F85">
-        <v>4663.235627204335</v>
+        <v>4719.419188977882</v>
       </c>
       <c r="G85">
         <v>708</v>
@@ -8263,28 +8263,28 @@
         <v>985.9625</v>
       </c>
       <c r="M85">
-        <v>469.0940137850684</v>
+        <v>474.7457488909126</v>
       </c>
       <c r="N85">
-        <v>516.8684862149316</v>
+        <v>511.2167511090873</v>
       </c>
       <c r="O85">
-        <v>175.7352853130768</v>
+        <v>173.8136953770897</v>
       </c>
       <c r="P85">
-        <v>341.1332009018549</v>
+        <v>337.4030557319976</v>
       </c>
       <c r="Q85">
-        <v>547.0332009018548</v>
+        <v>543.3030557319976</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2292006101170784</v>
+        <v>0.2397401408600841</v>
       </c>
       <c r="T85">
-        <v>2.390324763958957</v>
+        <v>2.52769018122464</v>
       </c>
       <c r="U85">
         <v>0.1005941048847012</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.101844131508685</v>
+        <v>2.076822177562152</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09412779428569179</v>
+        <v>0.09418603419564094</v>
       </c>
       <c r="C86">
-        <v>173.1014933603565</v>
+        <v>111.9676064825107</v>
       </c>
       <c r="D86">
-        <v>4184.520682338238</v>
+        <v>4179.570357233938</v>
       </c>
       <c r="E86">
-        <v>1900.363011623261</v>
+        <v>1956.546573396807</v>
       </c>
       <c r="F86">
-        <v>4719.419188977881</v>
+        <v>4775.602750751427</v>
       </c>
       <c r="G86">
         <v>708</v>
@@ -8345,28 +8345,28 @@
         <v>985.9625</v>
       </c>
       <c r="M86">
-        <v>474.7457488909125</v>
+        <v>480.3974839967567</v>
       </c>
       <c r="N86">
-        <v>511.2167511090875</v>
+        <v>505.5650160032433</v>
       </c>
       <c r="O86">
-        <v>173.8136953770897</v>
+        <v>171.8921054411027</v>
       </c>
       <c r="P86">
-        <v>337.4030557319977</v>
+        <v>333.6729105621405</v>
       </c>
       <c r="Q86">
-        <v>543.3030557319977</v>
+        <v>539.5729105621406</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.239740140860084</v>
+        <v>0.2516849423688238</v>
       </c>
       <c r="T86">
-        <v>2.527690181224639</v>
+        <v>2.683370987459079</v>
       </c>
       <c r="U86">
         <v>0.1005941048847012</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.076822177562153</v>
+        <v>2.052388975473186</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09418603419564094</v>
+        <v>0.0942442741055901</v>
       </c>
       <c r="C87">
-        <v>111.9676064825107</v>
+        <v>50.84541832204013</v>
       </c>
       <c r="D87">
-        <v>4179.570357233938</v>
+        <v>4174.631730847014</v>
       </c>
       <c r="E87">
-        <v>1956.546573396807</v>
+        <v>2012.730135170354</v>
       </c>
       <c r="F87">
-        <v>4775.602750751427</v>
+        <v>4831.786312524974</v>
       </c>
       <c r="G87">
         <v>708</v>
@@ -8427,28 +8427,28 @@
         <v>985.9625</v>
       </c>
       <c r="M87">
-        <v>480.3974839967567</v>
+        <v>486.049219102601</v>
       </c>
       <c r="N87">
-        <v>505.5650160032433</v>
+        <v>499.913280897399</v>
       </c>
       <c r="O87">
-        <v>171.8921054411027</v>
+        <v>169.9705155051157</v>
       </c>
       <c r="P87">
-        <v>333.6729105621405</v>
+        <v>329.9427653922833</v>
       </c>
       <c r="Q87">
-        <v>539.5729105621406</v>
+        <v>535.8427653922834</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2516849423688238</v>
+        <v>0.2653361440930978</v>
       </c>
       <c r="T87">
-        <v>2.683370987459079</v>
+        <v>2.861291908869867</v>
       </c>
       <c r="U87">
         <v>0.1005941048847012</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.052388975473186</v>
+        <v>2.028523987386289</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.0942442741055901</v>
+        <v>0.09430251401553924</v>
       </c>
       <c r="C88">
-        <v>50.84541832204013</v>
+        <v>-10.265112542108</v>
       </c>
       <c r="D88">
-        <v>4174.631730847014</v>
+        <v>4169.704761756412</v>
       </c>
       <c r="E88">
-        <v>2012.730135170354</v>
+        <v>2068.9136969439</v>
       </c>
       <c r="F88">
-        <v>4831.786312524974</v>
+        <v>4887.96987429852</v>
       </c>
       <c r="G88">
         <v>708</v>
@@ -8509,28 +8509,28 @@
         <v>985.9625</v>
       </c>
       <c r="M88">
-        <v>486.049219102601</v>
+        <v>491.7009542084452</v>
       </c>
       <c r="N88">
-        <v>499.913280897399</v>
+        <v>494.2615457915548</v>
       </c>
       <c r="O88">
-        <v>169.9705155051157</v>
+        <v>168.0489255691286</v>
       </c>
       <c r="P88">
-        <v>329.9427653922833</v>
+        <v>326.2126202224262</v>
       </c>
       <c r="Q88">
-        <v>535.8427653922834</v>
+        <v>532.1126202224261</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2653361440930978</v>
+        <v>0.2810875306980294</v>
       </c>
       <c r="T88">
-        <v>2.861291908869867</v>
+        <v>3.06658527972847</v>
       </c>
       <c r="U88">
         <v>0.1005941048847012</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.028523987386289</v>
+        <v>2.005207619715182</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09430251401553924</v>
+        <v>0.1026081139254884</v>
       </c>
       <c r="C89">
-        <v>-10.265112542108</v>
+        <v>-667.1504210444755</v>
       </c>
       <c r="D89">
-        <v>4169.704761756412</v>
+        <v>3569.003015027591</v>
       </c>
       <c r="E89">
-        <v>2068.9136969439</v>
+        <v>2125.097258717446</v>
       </c>
       <c r="F89">
-        <v>4887.96987429852</v>
+        <v>4944.153436072066</v>
       </c>
       <c r="G89">
         <v>708</v>
@@ -8591,45 +8591,45 @@
         <v>985.9625</v>
       </c>
       <c r="M89">
-        <v>491.7009542084452</v>
+        <v>567.5596681065127</v>
       </c>
       <c r="N89">
-        <v>494.2615457915548</v>
+        <v>418.4028318934872</v>
       </c>
       <c r="O89">
-        <v>168.0489255691286</v>
+        <v>142.2569628437857</v>
       </c>
       <c r="P89">
-        <v>326.2126202224262</v>
+        <v>276.1458690497016</v>
       </c>
       <c r="Q89">
-        <v>532.1126202224261</v>
+        <v>482.0458690497015</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2810875306980294</v>
+        <v>0.2994641484037829</v>
       </c>
       <c r="T89">
-        <v>3.06658527972847</v>
+        <v>3.30609421239684</v>
       </c>
       <c r="U89">
-        <v>0.1005941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V89">
         <v>0.34</v>
       </c>
       <c r="W89">
-        <v>0.06639210922390279</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.005207619715182</v>
+        <v>1.737196202276597</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1026081139254884</v>
+        <v>0.1027600738354376</v>
       </c>
       <c r="C90">
-        <v>-667.1504210444755</v>
+        <v>-732.7164125283452</v>
       </c>
       <c r="D90">
-        <v>3569.003015027591</v>
+        <v>3559.620585317267</v>
       </c>
       <c r="E90">
-        <v>2125.097258717446</v>
+        <v>2181.280820490992</v>
       </c>
       <c r="F90">
-        <v>4944.153436072066</v>
+        <v>5000.336997845612</v>
       </c>
       <c r="G90">
         <v>708</v>
@@ -8673,28 +8673,28 @@
         <v>985.9625</v>
       </c>
       <c r="M90">
-        <v>567.5596681065127</v>
+        <v>574.0092097895413</v>
       </c>
       <c r="N90">
-        <v>418.4028318934872</v>
+        <v>411.9532902104587</v>
       </c>
       <c r="O90">
-        <v>142.2569628437857</v>
+        <v>140.064118671556</v>
       </c>
       <c r="P90">
-        <v>276.1458690497016</v>
+        <v>271.8891715389027</v>
       </c>
       <c r="Q90">
-        <v>482.0458690497015</v>
+        <v>477.7891715389027</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2994641484037829</v>
+        <v>0.3211819693287644</v>
       </c>
       <c r="T90">
-        <v>3.30609421239684</v>
+        <v>3.589150223732186</v>
       </c>
       <c r="U90">
         <v>0.1147941048847012</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.737196202276597</v>
+        <v>1.717677143824051</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1027600738354376</v>
+        <v>0.1029120337453867</v>
       </c>
       <c r="C91">
-        <v>-732.7164125283452</v>
+        <v>-798.2332030590878</v>
       </c>
       <c r="D91">
-        <v>3559.620585317267</v>
+        <v>3550.287356560071</v>
       </c>
       <c r="E91">
-        <v>2181.280820490992</v>
+        <v>2237.464382264539</v>
       </c>
       <c r="F91">
-        <v>5000.336997845612</v>
+        <v>5056.520559619159</v>
       </c>
       <c r="G91">
         <v>708</v>
@@ -8755,28 +8755,28 @@
         <v>985.9625</v>
       </c>
       <c r="M91">
-        <v>574.0092097895413</v>
+        <v>580.4587514725699</v>
       </c>
       <c r="N91">
-        <v>411.9532902104587</v>
+        <v>405.50374852743</v>
       </c>
       <c r="O91">
-        <v>140.064118671556</v>
+        <v>137.8712744993262</v>
       </c>
       <c r="P91">
-        <v>271.8891715389027</v>
+        <v>267.6324740281038</v>
       </c>
       <c r="Q91">
-        <v>477.7891715389027</v>
+        <v>473.5324740281038</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3211819693287644</v>
+        <v>0.347243354438742</v>
       </c>
       <c r="T91">
-        <v>3.589150223732186</v>
+        <v>3.928817437334601</v>
       </c>
       <c r="U91">
         <v>0.1147941048847012</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.717677143824051</v>
+        <v>1.698591842226006</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1029120337453867</v>
+        <v>0.1030639936553359</v>
       </c>
       <c r="C92">
-        <v>-798.2332030590878</v>
+        <v>-863.7011786353241</v>
       </c>
       <c r="D92">
-        <v>3550.287356560071</v>
+        <v>3541.00294275738</v>
       </c>
       <c r="E92">
-        <v>2237.464382264539</v>
+        <v>2293.647944038085</v>
       </c>
       <c r="F92">
-        <v>5056.520559619159</v>
+        <v>5112.704121392705</v>
       </c>
       <c r="G92">
         <v>708</v>
@@ -8837,28 +8837,28 @@
         <v>985.9625</v>
       </c>
       <c r="M92">
-        <v>580.4587514725699</v>
+        <v>586.9082931555985</v>
       </c>
       <c r="N92">
-        <v>405.50374852743</v>
+        <v>399.0542068444015</v>
       </c>
       <c r="O92">
-        <v>137.8712744993262</v>
+        <v>135.6784303270965</v>
       </c>
       <c r="P92">
-        <v>267.6324740281038</v>
+        <v>263.375776517305</v>
       </c>
       <c r="Q92">
-        <v>473.5324740281038</v>
+        <v>469.275776517305</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.347243354438742</v>
+        <v>0.3790961584620482</v>
       </c>
       <c r="T92">
-        <v>3.928817437334601</v>
+        <v>4.343966253959776</v>
       </c>
       <c r="U92">
         <v>0.1147941048847012</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.698591842226006</v>
+        <v>1.67992599780594</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1030639936553359</v>
+        <v>0.103215953565285</v>
       </c>
       <c r="C93">
-        <v>-863.7011786353241</v>
+        <v>-929.1207212284835</v>
       </c>
       <c r="D93">
-        <v>3541.00294275738</v>
+        <v>3531.766961937768</v>
       </c>
       <c r="E93">
-        <v>2293.647944038085</v>
+        <v>2349.831505811631</v>
       </c>
       <c r="F93">
-        <v>5112.704121392705</v>
+        <v>5168.887683166251</v>
       </c>
       <c r="G93">
         <v>708</v>
@@ -8919,28 +8919,28 @@
         <v>985.9625</v>
       </c>
       <c r="M93">
-        <v>586.9082931555985</v>
+        <v>593.357834838627</v>
       </c>
       <c r="N93">
-        <v>399.0542068444015</v>
+        <v>392.604665161373</v>
       </c>
       <c r="O93">
-        <v>135.6784303270965</v>
+        <v>133.4855861548668</v>
       </c>
       <c r="P93">
-        <v>263.375776517305</v>
+        <v>259.1190790065061</v>
       </c>
       <c r="Q93">
-        <v>469.275776517305</v>
+        <v>465.0190790065061</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3790961584620482</v>
+        <v>0.4189121634911809</v>
       </c>
       <c r="T93">
-        <v>4.343966253959776</v>
+        <v>4.862902274741245</v>
       </c>
       <c r="U93">
         <v>0.1147941048847012</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.67992599780594</v>
+        <v>1.661665932612397</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.103215953565285</v>
+        <v>0.1033679134752342</v>
       </c>
       <c r="C94">
-        <v>-929.1207212284835</v>
+        <v>-994.4922088351832</v>
       </c>
       <c r="D94">
-        <v>3531.766961937768</v>
+        <v>3522.579036104615</v>
       </c>
       <c r="E94">
-        <v>2349.831505811631</v>
+        <v>2406.015067585178</v>
       </c>
       <c r="F94">
-        <v>5168.887683166251</v>
+        <v>5225.071244939798</v>
       </c>
       <c r="G94">
         <v>708</v>
@@ -9001,28 +9001,28 @@
         <v>985.9625</v>
       </c>
       <c r="M94">
-        <v>593.357834838627</v>
+        <v>599.8073765216557</v>
       </c>
       <c r="N94">
-        <v>392.604665161373</v>
+        <v>386.1551234783443</v>
       </c>
       <c r="O94">
-        <v>133.4855861548668</v>
+        <v>131.2927419826371</v>
       </c>
       <c r="P94">
-        <v>259.1190790065061</v>
+        <v>254.8623814957072</v>
       </c>
       <c r="Q94">
-        <v>465.0190790065061</v>
+        <v>460.7623814957072</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4189121634911809</v>
+        <v>0.4701041699572086</v>
       </c>
       <c r="T94">
-        <v>4.862902274741245</v>
+        <v>5.530105730031704</v>
       </c>
       <c r="U94">
         <v>0.1147941048847012</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.661665932612397</v>
+        <v>1.643798556992909</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1033679134752342</v>
+        <v>0.1035198733851833</v>
       </c>
       <c r="C95">
-        <v>-994.4922088351832</v>
+        <v>-1059.8160155288</v>
       </c>
       <c r="D95">
-        <v>3522.579036104615</v>
+        <v>3513.438791184545</v>
       </c>
       <c r="E95">
-        <v>2406.015067585178</v>
+        <v>2462.198629358724</v>
       </c>
       <c r="F95">
-        <v>5225.071244939798</v>
+        <v>5281.254806713344</v>
       </c>
       <c r="G95">
         <v>708</v>
@@ -9083,28 +9083,28 @@
         <v>985.9625</v>
       </c>
       <c r="M95">
-        <v>599.8073765216557</v>
+        <v>606.2569182046842</v>
       </c>
       <c r="N95">
-        <v>386.1551234783443</v>
+        <v>379.7055817953158</v>
       </c>
       <c r="O95">
-        <v>131.2927419826371</v>
+        <v>129.0998978104074</v>
       </c>
       <c r="P95">
-        <v>254.8623814957072</v>
+        <v>250.6056839849084</v>
       </c>
       <c r="Q95">
-        <v>460.7623814957072</v>
+        <v>456.5056839849084</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4701041699572086</v>
+        <v>0.5383601785785789</v>
       </c>
       <c r="T95">
-        <v>5.530105730031704</v>
+        <v>6.41971033708565</v>
       </c>
       <c r="U95">
         <v>0.1147941048847012</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.643798556992909</v>
+        <v>1.626311338301495</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1035198733851833</v>
+        <v>0.1036718332951325</v>
       </c>
       <c r="C96">
-        <v>-1059.8160155288</v>
+        <v>-1125.092511510238</v>
       </c>
       <c r="D96">
-        <v>3513.438791184545</v>
+        <v>3504.345856976652</v>
       </c>
       <c r="E96">
-        <v>2462.198629358724</v>
+        <v>2518.38219113227</v>
       </c>
       <c r="F96">
-        <v>5281.254806713344</v>
+        <v>5337.43836848689</v>
       </c>
       <c r="G96">
         <v>708</v>
@@ -9165,28 +9165,28 @@
         <v>985.9625</v>
       </c>
       <c r="M96">
-        <v>606.2569182046842</v>
+        <v>612.7064598877126</v>
       </c>
       <c r="N96">
-        <v>379.7055817953158</v>
+        <v>373.2560401122873</v>
       </c>
       <c r="O96">
-        <v>129.0998978104074</v>
+        <v>126.9070536381777</v>
       </c>
       <c r="P96">
-        <v>250.6056839849084</v>
+        <v>246.3489864741096</v>
       </c>
       <c r="Q96">
-        <v>456.5056839849084</v>
+        <v>452.2489864741096</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5383601785785789</v>
+        <v>0.6339185906484974</v>
       </c>
       <c r="T96">
-        <v>6.41971033708565</v>
+        <v>7.665156786961177</v>
       </c>
       <c r="U96">
         <v>0.1147941048847012</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.626311338301495</v>
+        <v>1.609192271582532</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1036718332951325</v>
+        <v>0.1038237932050817</v>
       </c>
       <c r="C97">
-        <v>-1125.092511510238</v>
+        <v>-1190.322063157913</v>
       </c>
       <c r="D97">
-        <v>3504.345856976652</v>
+        <v>3495.299867102524</v>
       </c>
       <c r="E97">
-        <v>2518.38219113227</v>
+        <v>2574.565752905817</v>
       </c>
       <c r="F97">
-        <v>5337.43836848689</v>
+        <v>5393.621930260437</v>
       </c>
       <c r="G97">
         <v>708</v>
@@ -9247,28 +9247,28 @@
         <v>985.9625</v>
       </c>
       <c r="M97">
-        <v>612.7064598877126</v>
+        <v>619.1560015707413</v>
       </c>
       <c r="N97">
-        <v>373.2560401122873</v>
+        <v>366.8064984292587</v>
       </c>
       <c r="O97">
-        <v>126.9070536381777</v>
+        <v>124.714209465948</v>
       </c>
       <c r="P97">
-        <v>246.3489864741096</v>
+        <v>242.0922889633107</v>
       </c>
       <c r="Q97">
-        <v>452.2489864741096</v>
+        <v>447.9922889633107</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6339185906484974</v>
+        <v>0.7772562087533753</v>
       </c>
       <c r="T97">
-        <v>7.665156786961177</v>
+        <v>9.533326461774466</v>
       </c>
       <c r="U97">
         <v>0.1147941048847012</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.609192271582532</v>
+        <v>1.592429852086881</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1038237932050816</v>
+        <v>0.1039757531150308</v>
       </c>
       <c r="C98">
-        <v>-1190.322063157911</v>
+        <v>-1255.505033076948</v>
       </c>
       <c r="D98">
-        <v>3495.299867102525</v>
+        <v>3486.300458957034</v>
       </c>
       <c r="E98">
-        <v>2574.565752905816</v>
+        <v>2630.749314679362</v>
       </c>
       <c r="F98">
-        <v>5393.621930260436</v>
+        <v>5449.805492033982</v>
       </c>
       <c r="G98">
         <v>708</v>
@@ -9329,28 +9329,28 @@
         <v>985.9625</v>
       </c>
       <c r="M98">
-        <v>619.1560015707412</v>
+        <v>625.6055432537697</v>
       </c>
       <c r="N98">
-        <v>366.8064984292588</v>
+        <v>360.3569567462303</v>
       </c>
       <c r="O98">
-        <v>124.714209465948</v>
+        <v>122.5213652937183</v>
       </c>
       <c r="P98">
-        <v>242.0922889633108</v>
+        <v>237.8355914525119</v>
       </c>
       <c r="Q98">
-        <v>447.9922889633108</v>
+        <v>443.7355914525119</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7772562087533732</v>
+        <v>1.016152238928169</v>
       </c>
       <c r="T98">
-        <v>9.53332646177444</v>
+        <v>12.64694258646324</v>
       </c>
       <c r="U98">
         <v>0.1147941048847012</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.592429852086881</v>
+        <v>1.576013049488047</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1039757531150308</v>
+        <v>0.10412771302498</v>
       </c>
       <c r="C99">
-        <v>-1255.505033076948</v>
+        <v>-1320.641780147644</v>
       </c>
       <c r="D99">
-        <v>3486.300458957034</v>
+        <v>3477.347273659884</v>
       </c>
       <c r="E99">
-        <v>2630.749314679362</v>
+        <v>2686.932876452908</v>
       </c>
       <c r="F99">
-        <v>5449.805492033982</v>
+        <v>5505.989053807528</v>
       </c>
       <c r="G99">
         <v>708</v>
@@ -9411,28 +9411,28 @@
         <v>985.9625</v>
       </c>
       <c r="M99">
-        <v>625.6055432537697</v>
+        <v>632.0550849367983</v>
       </c>
       <c r="N99">
-        <v>360.3569567462303</v>
+        <v>353.9074150632017</v>
       </c>
       <c r="O99">
-        <v>122.5213652937183</v>
+        <v>120.3285211214886</v>
       </c>
       <c r="P99">
-        <v>237.8355914525119</v>
+        <v>233.5788939417131</v>
       </c>
       <c r="Q99">
-        <v>443.7355914525119</v>
+        <v>439.4788939417131</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.016152238928169</v>
+        <v>1.493944299277759</v>
       </c>
       <c r="T99">
-        <v>12.64694258646324</v>
+        <v>18.87417483584085</v>
       </c>
       <c r="U99">
         <v>0.1147941048847012</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.576013049488047</v>
+        <v>1.559931283676945</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.10412771302498</v>
+        <v>0.1042796729349291</v>
       </c>
       <c r="C100">
-        <v>-1320.641780147644</v>
+        <v>-1385.732659573171</v>
       </c>
       <c r="D100">
-        <v>3477.347273659884</v>
+        <v>3468.439956007903</v>
       </c>
       <c r="E100">
-        <v>2686.932876452908</v>
+        <v>2743.116438226455</v>
       </c>
       <c r="F100">
-        <v>5505.989053807528</v>
+        <v>5562.172615581075</v>
       </c>
       <c r="G100">
         <v>708</v>
@@ -9493,28 +9493,28 @@
         <v>985.9625</v>
       </c>
       <c r="M100">
-        <v>632.0550849367983</v>
+        <v>638.5046266198269</v>
       </c>
       <c r="N100">
-        <v>353.9074150632017</v>
+        <v>347.4578733801731</v>
       </c>
       <c r="O100">
-        <v>120.3285211214886</v>
+        <v>118.1356769492589</v>
       </c>
       <c r="P100">
-        <v>233.5788939417131</v>
+        <v>229.3221964309142</v>
       </c>
       <c r="Q100">
-        <v>439.4788939417131</v>
+        <v>435.2221964309142</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.493944299277759</v>
+        <v>2.927320480326531</v>
       </c>
       <c r="T100">
-        <v>18.87417483584085</v>
+        <v>37.55587158397365</v>
       </c>
       <c r="U100">
         <v>0.1147941048847012</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.559931283676945</v>
+        <v>1.544174402023642</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1042796729349291</v>
-      </c>
-      <c r="C101">
-        <v>-1385.732659573171</v>
-      </c>
-      <c r="D101">
-        <v>3468.439956007903</v>
-      </c>
-      <c r="E101">
-        <v>2743.116438226455</v>
-      </c>
-      <c r="F101">
-        <v>5562.172615581075</v>
-      </c>
-      <c r="G101">
-        <v>708</v>
-      </c>
-      <c r="H101">
-        <v>2799.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1191.8625</v>
-      </c>
-      <c r="K101">
-        <v>205.9</v>
-      </c>
-      <c r="L101">
-        <v>985.9625</v>
-      </c>
-      <c r="M101">
-        <v>638.5046266198269</v>
-      </c>
-      <c r="N101">
-        <v>347.4578733801731</v>
-      </c>
-      <c r="O101">
-        <v>118.1356769492589</v>
-      </c>
-      <c r="P101">
-        <v>229.3221964309142</v>
-      </c>
-      <c r="Q101">
-        <v>435.2221964309142</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.927320480326531</v>
-      </c>
-      <c r="T101">
-        <v>37.55587158397365</v>
-      </c>
-      <c r="U101">
-        <v>0.1147941048847012</v>
-      </c>
-      <c r="V101">
-        <v>0.34</v>
-      </c>
-      <c r="W101">
-        <v>0.07576410922390281</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.544174402023642</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
